--- a/Docs/Balance/귀살_밸런스.xlsx
+++ b/Docs/Balance/귀살_밸런스.xlsx
@@ -39,23 +39,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">몬스터 체력</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">·</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="WenQuanYi Zen Hei"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">피해에 곱하는 배율</t>
+          <t xml:space="preserve">몬스터 체력에 곱하는 배율</t>
         </r>
         <r>
           <rPr>
@@ -87,11 +71,35 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">로 조정</t>
+          <t xml:space="preserve">로 조정 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">피해는 옆 열 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">MonsterDamageMult)</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -225,7 +233,7 @@
             <rFont val="WenQuanYi Zen Hei"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">실제 </t>
+          <t xml:space="preserve">실제 체력 </t>
         </r>
         <r>
           <rPr>
@@ -265,7 +273,39 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">MonsterMult (</t>
+          <t xml:space="preserve">MonsterMult, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">실제 피해 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">= BaseDamage × </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">레벨표 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">MonsterDamageMult (</t>
         </r>
         <r>
           <rPr>
@@ -297,7 +337,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">EliteHealthMult)</t>
+          <t xml:space="preserve">EliteHealthMult / EliteDamageMult)</t>
         </r>
       </text>
     </comment>
@@ -814,7 +854,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="445">
   <si>
     <r>
       <rPr>
@@ -2342,7 +2382,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">몬스터 레벨 배율 </t>
+      <t xml:space="preserve">몬스터 체력 레벨 배율 </t>
     </r>
     <r>
       <rPr>
@@ -2394,6 +2434,77 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">MonsterDamageGrowth</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">몬스터 피해 레벨 배율 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 값 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">^ (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">몬스터 레벨 − </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">체력 성장보다 낮게 두어 후반 생존력 유지</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">ArmorPerEnemyLevel</t>
   </si>
   <si>
@@ -3081,6 +3192,9 @@
   </si>
   <si>
     <t xml:space="preserve">MonsterMult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MonsterDamageMult</t>
   </si>
   <si>
     <t xml:space="preserve">PlayerHealth</t>
@@ -7402,11 +7516,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="10044627"/>
-        <c:axId val="82262866"/>
+        <c:axId val="96354353"/>
+        <c:axId val="80361097"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="10044627"/>
+        <c:axId val="96354353"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7472,7 +7586,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82262866"/>
+        <c:crossAx val="80361097"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7480,7 +7594,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="82262866"/>
+        <c:axId val="80361097"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7556,7 +7670,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10044627"/>
+        <c:crossAx val="96354353"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7873,151 +7987,151 @@
                   <c:v>34.0246153846154</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>35.4285714285714</c:v>
+                  <c:v>36.4036697247706</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>35.9861707841031</c:v>
+                  <c:v>37.9943208749928</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>35.9358434932415</c:v>
+                  <c:v>38.9854379533375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>35.4364880518534</c:v>
+                  <c:v>39.5017897689953</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>34.603310881308</c:v>
+                  <c:v>39.6346728832911</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>33.5239447176972</c:v>
+                  <c:v>39.4552013638967</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>32.2668677933018</c:v>
+                  <c:v>39.0209180392235</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>30.8863694927617</c:v>
+                  <c:v>38.3794777205322</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>29.4257780384969</c:v>
+                  <c:v>37.5709068085302</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>27.91972201722</c:v>
+                  <c:v>36.6291075322812</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>26.3958058991341</c:v>
+                  <c:v>35.582929335245</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>24.8759023548265</c:v>
+                  <c:v>34.4569743949059</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>23.3771776959493</c:v>
+                  <c:v>33.2722292353914</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>21.9129217510485</c:v>
+                  <c:v>32.0465759824427</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>20.4932286221376</c:v>
+                  <c:v>30.7952160989627</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>19.1255602497432</c:v>
+                  <c:v>29.5310277412351</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>17.8152157827143</c:v>
+                  <c:v>28.2648709817528</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>16.565723976138</c:v>
+                  <c:v>27.0058509168914</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>15.3791719332503</c:v>
+                  <c:v>25.7615459852384</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>14.2564807487238</c:v>
+                  <c:v>24.5382070442596</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>13.1976365890693</c:v>
+                  <c:v>23.3409315367907</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>12.201884215585</c:v>
+                  <c:v>22.1738162185507</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>11.2678887649895</c:v>
+                  <c:v>21.040091289625</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>10.393870656113</c:v>
+                  <c:v>19.9422383002183</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>9.57771772430439</c:v>
+                  <c:v>18.8820938356159</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>8.81707805535706</c:v>
+                  <c:v>17.860940695916</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>8.10943646750958</c:v>
+                  <c:v>16.8795880519835</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>7.45217715158711</c:v>
+                  <c:v>15.9384418661773</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>6.84263460941751</c:v>
+                  <c:v>15.0375667049959</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>6.27813471695185</c:v>
+                  <c:v>14.1767399339744</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>5.7560274714641</c:v>
+                  <c:v>13.3554991679725</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>5.27371275419897</c:v>
+                  <c:v>12.5731837487209</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>4.82866024475833</c:v>
+                  <c:v>11.828970933369</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>4.41842445635905</c:v>
+                  <c:v>11.1219074006493</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>4.04065571772002</c:v>
+                  <c:v>10.450936613467</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>3.69310780428821</c:v>
+                  <c:v>9.81492251688255</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>3.37364281588511</c:v>
+                  <c:v>9.21266999750191</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>3.08023380718522</c:v>
+                  <c:v>8.64294248330606</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>2.81096559963231</c:v>
+                  <c:v>8.10447702120471</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2.56403413666705</c:v>
+                  <c:v>7.59599713243833</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2.33774468694856</c:v>
+                  <c:v>7.1162237128456</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2.13050915128287</c:v>
+                  <c:v>6.66388421548947</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1.9408426870899</c:v>
+                  <c:v>6.23772032679159</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1.76735982846739</c:v>
+                  <c:v>5.83649432380862</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1.60877024940169</c:v>
+                  <c:v>5.4589942792867</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1.46387429170148</c:v>
+                  <c:v>5.10403826237905</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1.33155835715923</c:v>
+                  <c:v>4.7704776661668</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1.21079024473378</c:v>
+                  <c:v>4.45719977817063</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1.10061449772095</c:v>
+                  <c:v>4.16312969669178</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8404,11 +8518,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="42453765"/>
-        <c:axId val="8727658"/>
+        <c:axId val="21459630"/>
+        <c:axId val="78736989"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="42453765"/>
+        <c:axId val="21459630"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8474,7 +8588,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8727658"/>
+        <c:crossAx val="78736989"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8482,7 +8596,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="8727658"/>
+        <c:axId val="78736989"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8558,7 +8672,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42453765"/>
+        <c:crossAx val="21459630"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9050,7 +9164,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -9091,10 +9205,12 @@
       <c r="A3" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C3" s="11"/>
+      <c r="B3" s="12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>40</v>
+      </c>
       <c r="D3" s="13" t="s">
         <v>43</v>
       </c>
@@ -9104,7 +9220,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="14" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="13" t="s">
@@ -9115,25 +9231,23 @@
       <c r="A5" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="15" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="C5" s="11" t="s">
+      <c r="B5" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="13" t="s">
         <v>47</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>49</v>
-      </c>
-      <c r="B6" s="15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>47</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>50</v>
@@ -9144,12 +9258,12 @@
         <v>51</v>
       </c>
       <c r="B7" s="15" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>52</v>
       </c>
     </row>
@@ -9158,12 +9272,12 @@
         <v>53</v>
       </c>
       <c r="B8" s="15" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>54</v>
       </c>
     </row>
@@ -9172,10 +9286,10 @@
         <v>55</v>
       </c>
       <c r="B9" s="15" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>56</v>
@@ -9186,10 +9300,10 @@
         <v>57</v>
       </c>
       <c r="B10" s="15" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>58</v>
@@ -9200,10 +9314,10 @@
         <v>59</v>
       </c>
       <c r="B11" s="15" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>60</v>
@@ -9214,10 +9328,10 @@
         <v>61</v>
       </c>
       <c r="B12" s="15" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>62</v>
@@ -9228,10 +9342,10 @@
         <v>63</v>
       </c>
       <c r="B13" s="15" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>64</v>
@@ -9245,7 +9359,7 @@
         <v>0.4</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>66</v>
@@ -9256,10 +9370,10 @@
         <v>67</v>
       </c>
       <c r="B15" s="15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>68</v>
@@ -9270,10 +9384,10 @@
         <v>69</v>
       </c>
       <c r="B16" s="15" t="n">
-        <v>0.03</v>
+        <v>0.5</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>70</v>
@@ -9284,10 +9398,10 @@
         <v>71</v>
       </c>
       <c r="B17" s="15" t="n">
-        <v>0.45</v>
+        <v>0.03</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>72</v>
@@ -9297,10 +9411,12 @@
       <c r="A18" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="C18" s="11"/>
+      <c r="B18" s="15" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>49</v>
+      </c>
       <c r="D18" s="13" t="s">
         <v>74</v>
       </c>
@@ -9310,7 +9426,7 @@
         <v>75</v>
       </c>
       <c r="B19" s="14" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="13" t="s">
@@ -9322,7 +9438,7 @@
         <v>77</v>
       </c>
       <c r="B20" s="14" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="13" t="s">
@@ -9334,7 +9450,7 @@
         <v>79</v>
       </c>
       <c r="B21" s="14" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="13" t="s">
@@ -9346,23 +9462,23 @@
         <v>81</v>
       </c>
       <c r="B22" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C22" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="11"/>
+      <c r="D22" s="13" t="s">
         <v>82</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="11"/>
       <c r="D23" s="13" t="s">
         <v>85</v>
       </c>
@@ -9372,7 +9488,7 @@
         <v>86</v>
       </c>
       <c r="B24" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="13" t="s">
@@ -9383,12 +9499,10 @@
       <c r="A25" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>40</v>
-      </c>
+      <c r="C25" s="11"/>
       <c r="D25" s="13" t="s">
         <v>89</v>
       </c>
@@ -9398,7 +9512,7 @@
         <v>90</v>
       </c>
       <c r="B26" s="12" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>40</v>
@@ -9411,25 +9525,25 @@
       <c r="A27" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="14" t="n">
-        <v>2</v>
+      <c r="B27" s="12" t="n">
+        <v>1.5</v>
       </c>
       <c r="C27" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="13" t="s">
         <v>93</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>95</v>
-      </c>
-      <c r="B28" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>93</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>96</v>
@@ -9440,9 +9554,11 @@
         <v>97</v>
       </c>
       <c r="B29" s="14" t="n">
-        <v>250</v>
-      </c>
-      <c r="C29" s="11"/>
+        <v>3</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>95</v>
+      </c>
       <c r="D29" s="13" t="s">
         <v>98</v>
       </c>
@@ -9452,7 +9568,7 @@
         <v>99</v>
       </c>
       <c r="B30" s="14" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="13" t="s">
@@ -9463,8 +9579,8 @@
       <c r="A31" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="B31" s="12" t="n">
-        <v>1.5</v>
+      <c r="B31" s="14" t="n">
+        <v>100</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="13" t="s">
@@ -9475,12 +9591,10 @@
       <c r="A32" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="B32" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>93</v>
-      </c>
+      <c r="B32" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C32" s="11"/>
       <c r="D32" s="13" t="s">
         <v>104</v>
       </c>
@@ -9489,11 +9603,11 @@
       <c r="A33" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="B33" s="12" t="n">
-        <v>0.2</v>
+      <c r="B33" s="14" t="n">
+        <v>5</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>106</v>
@@ -9503,11 +9617,11 @@
       <c r="A34" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="B34" s="14" t="n">
-        <v>50</v>
+      <c r="B34" s="12" t="n">
+        <v>0.2</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>108</v>
@@ -9518,9 +9632,11 @@
         <v>109</v>
       </c>
       <c r="B35" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="C35" s="11"/>
+        <v>50</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>95</v>
+      </c>
       <c r="D35" s="13" t="s">
         <v>110</v>
       </c>
@@ -9530,11 +9646,23 @@
         <v>111</v>
       </c>
       <c r="B36" s="14" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="13" t="s">
         <v>112</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" s="11"/>
+      <c r="D37" s="13" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -9553,37 +9681,42 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>119</v>
+        <v>121</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9594,24 +9727,28 @@
         <f aca="false">상수!$B$2^(A2-1)</f>
         <v>1</v>
       </c>
-      <c r="C2" s="18" t="n">
-        <f aca="false">IF(A2&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A2,"")</f>
+      <c r="C2" s="17" t="n">
+        <f aca="false">상수!$B$3^(A2-1)</f>
+        <v>1</v>
+      </c>
+      <c r="D2" s="18" t="n">
+        <f aca="false">IF(A2&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A2,"")</f>
         <v>110</v>
       </c>
-      <c r="D2" s="18" t="n">
-        <f aca="false">IF(A2&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A2,"")</f>
+      <c r="E2" s="18" t="n">
+        <f aca="false">IF(A2&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A2,"")</f>
         <v>102</v>
       </c>
-      <c r="E2" s="19" t="n">
-        <f aca="false">IF(A2&lt;상수!$B$34,ROUND(상수!$B$30*A2^상수!$B$31,0),"")</f>
+      <c r="F2" s="19" t="n">
+        <f aca="false">IF(A2&lt;상수!$B$35,ROUND(상수!$B$31*A2^상수!$B$32,0),"")</f>
         <v>100</v>
       </c>
-      <c r="F2" s="19" t="n">
+      <c r="G2" s="19" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="G2" s="18" t="n">
-        <f aca="false">상수!$B$3*A2+상수!$B$4</f>
+      <c r="H2" s="18" t="n">
+        <f aca="false">상수!$B$4*A2+상수!$B$5</f>
         <v>65</v>
       </c>
     </row>
@@ -9623,24 +9760,28 @@
         <f aca="false">상수!$B$2^(A3-1)</f>
         <v>1.12</v>
       </c>
-      <c r="C3" s="18" t="n">
-        <f aca="false">IF(A3&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A3,"")</f>
+      <c r="C3" s="17" t="n">
+        <f aca="false">상수!$B$3^(A3-1)</f>
+        <v>1.09</v>
+      </c>
+      <c r="D3" s="18" t="n">
+        <f aca="false">IF(A3&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A3,"")</f>
         <v>120</v>
       </c>
-      <c r="D3" s="18" t="n">
-        <f aca="false">IF(A3&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A3,"")</f>
+      <c r="E3" s="18" t="n">
+        <f aca="false">IF(A3&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A3,"")</f>
         <v>104</v>
       </c>
-      <c r="E3" s="19" t="n">
-        <f aca="false">IF(A3&lt;상수!$B$34,ROUND(상수!$B$30*A3^상수!$B$31,0),"")</f>
+      <c r="F3" s="19" t="n">
+        <f aca="false">IF(A3&lt;상수!$B$35,ROUND(상수!$B$31*A3^상수!$B$32,0),"")</f>
         <v>283</v>
       </c>
-      <c r="F3" s="19" t="n">
-        <f aca="false">IF(A3&lt;=상수!$B$34,F2+E2,"")</f>
+      <c r="G3" s="19" t="n">
+        <f aca="false">IF(A3&lt;=상수!$B$35,G2+F2,"")</f>
         <v>100</v>
       </c>
-      <c r="G3" s="18" t="n">
-        <f aca="false">상수!$B$3*A3+상수!$B$4</f>
+      <c r="H3" s="18" t="n">
+        <f aca="false">상수!$B$4*A3+상수!$B$5</f>
         <v>80</v>
       </c>
     </row>
@@ -9652,24 +9793,28 @@
         <f aca="false">상수!$B$2^(A4-1)</f>
         <v>1.2544</v>
       </c>
-      <c r="C4" s="18" t="n">
-        <f aca="false">IF(A4&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A4,"")</f>
+      <c r="C4" s="17" t="n">
+        <f aca="false">상수!$B$3^(A4-1)</f>
+        <v>1.1881</v>
+      </c>
+      <c r="D4" s="18" t="n">
+        <f aca="false">IF(A4&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A4,"")</f>
         <v>130</v>
       </c>
-      <c r="D4" s="18" t="n">
-        <f aca="false">IF(A4&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A4,"")</f>
+      <c r="E4" s="18" t="n">
+        <f aca="false">IF(A4&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A4,"")</f>
         <v>106</v>
       </c>
-      <c r="E4" s="19" t="n">
-        <f aca="false">IF(A4&lt;상수!$B$34,ROUND(상수!$B$30*A4^상수!$B$31,0),"")</f>
+      <c r="F4" s="19" t="n">
+        <f aca="false">IF(A4&lt;상수!$B$35,ROUND(상수!$B$31*A4^상수!$B$32,0),"")</f>
         <v>520</v>
       </c>
-      <c r="F4" s="19" t="n">
-        <f aca="false">IF(A4&lt;=상수!$B$34,F3+E3,"")</f>
+      <c r="G4" s="19" t="n">
+        <f aca="false">IF(A4&lt;=상수!$B$35,G3+F3,"")</f>
         <v>383</v>
       </c>
-      <c r="G4" s="18" t="n">
-        <f aca="false">상수!$B$3*A4+상수!$B$4</f>
+      <c r="H4" s="18" t="n">
+        <f aca="false">상수!$B$4*A4+상수!$B$5</f>
         <v>95</v>
       </c>
     </row>
@@ -9681,24 +9826,28 @@
         <f aca="false">상수!$B$2^(A5-1)</f>
         <v>1.404928</v>
       </c>
-      <c r="C5" s="18" t="n">
-        <f aca="false">IF(A5&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A5,"")</f>
+      <c r="C5" s="17" t="n">
+        <f aca="false">상수!$B$3^(A5-1)</f>
+        <v>1.295029</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <f aca="false">IF(A5&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A5,"")</f>
         <v>140</v>
       </c>
-      <c r="D5" s="18" t="n">
-        <f aca="false">IF(A5&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A5,"")</f>
+      <c r="E5" s="18" t="n">
+        <f aca="false">IF(A5&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A5,"")</f>
         <v>108</v>
       </c>
-      <c r="E5" s="19" t="n">
-        <f aca="false">IF(A5&lt;상수!$B$34,ROUND(상수!$B$30*A5^상수!$B$31,0),"")</f>
+      <c r="F5" s="19" t="n">
+        <f aca="false">IF(A5&lt;상수!$B$35,ROUND(상수!$B$31*A5^상수!$B$32,0),"")</f>
         <v>800</v>
       </c>
-      <c r="F5" s="19" t="n">
-        <f aca="false">IF(A5&lt;=상수!$B$34,F4+E4,"")</f>
+      <c r="G5" s="19" t="n">
+        <f aca="false">IF(A5&lt;=상수!$B$35,G4+F4,"")</f>
         <v>903</v>
       </c>
-      <c r="G5" s="18" t="n">
-        <f aca="false">상수!$B$3*A5+상수!$B$4</f>
+      <c r="H5" s="18" t="n">
+        <f aca="false">상수!$B$4*A5+상수!$B$5</f>
         <v>110</v>
       </c>
     </row>
@@ -9710,24 +9859,28 @@
         <f aca="false">상수!$B$2^(A6-1)</f>
         <v>1.57351936</v>
       </c>
-      <c r="C6" s="18" t="n">
-        <f aca="false">IF(A6&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A6,"")</f>
+      <c r="C6" s="17" t="n">
+        <f aca="false">상수!$B$3^(A6-1)</f>
+        <v>1.41158161</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <f aca="false">IF(A6&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A6,"")</f>
         <v>150</v>
       </c>
-      <c r="D6" s="18" t="n">
-        <f aca="false">IF(A6&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A6,"")</f>
+      <c r="E6" s="18" t="n">
+        <f aca="false">IF(A6&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A6,"")</f>
         <v>110</v>
       </c>
-      <c r="E6" s="19" t="n">
-        <f aca="false">IF(A6&lt;상수!$B$34,ROUND(상수!$B$30*A6^상수!$B$31,0),"")</f>
+      <c r="F6" s="19" t="n">
+        <f aca="false">IF(A6&lt;상수!$B$35,ROUND(상수!$B$31*A6^상수!$B$32,0),"")</f>
         <v>1118</v>
       </c>
-      <c r="F6" s="19" t="n">
-        <f aca="false">IF(A6&lt;=상수!$B$34,F5+E5,"")</f>
+      <c r="G6" s="19" t="n">
+        <f aca="false">IF(A6&lt;=상수!$B$35,G5+F5,"")</f>
         <v>1703</v>
       </c>
-      <c r="G6" s="18" t="n">
-        <f aca="false">상수!$B$3*A6+상수!$B$4</f>
+      <c r="H6" s="18" t="n">
+        <f aca="false">상수!$B$4*A6+상수!$B$5</f>
         <v>125</v>
       </c>
     </row>
@@ -9739,24 +9892,28 @@
         <f aca="false">상수!$B$2^(A7-1)</f>
         <v>1.7623416832</v>
       </c>
-      <c r="C7" s="18" t="n">
-        <f aca="false">IF(A7&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A7,"")</f>
+      <c r="C7" s="17" t="n">
+        <f aca="false">상수!$B$3^(A7-1)</f>
+        <v>1.5386239549</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <f aca="false">IF(A7&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A7,"")</f>
         <v>160</v>
       </c>
-      <c r="D7" s="18" t="n">
-        <f aca="false">IF(A7&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A7,"")</f>
+      <c r="E7" s="18" t="n">
+        <f aca="false">IF(A7&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A7,"")</f>
         <v>112</v>
       </c>
-      <c r="E7" s="19" t="n">
-        <f aca="false">IF(A7&lt;상수!$B$34,ROUND(상수!$B$30*A7^상수!$B$31,0),"")</f>
+      <c r="F7" s="19" t="n">
+        <f aca="false">IF(A7&lt;상수!$B$35,ROUND(상수!$B$31*A7^상수!$B$32,0),"")</f>
         <v>1470</v>
       </c>
-      <c r="F7" s="19" t="n">
-        <f aca="false">IF(A7&lt;=상수!$B$34,F6+E6,"")</f>
+      <c r="G7" s="19" t="n">
+        <f aca="false">IF(A7&lt;=상수!$B$35,G6+F6,"")</f>
         <v>2821</v>
       </c>
-      <c r="G7" s="18" t="n">
-        <f aca="false">상수!$B$3*A7+상수!$B$4</f>
+      <c r="H7" s="18" t="n">
+        <f aca="false">상수!$B$4*A7+상수!$B$5</f>
         <v>140</v>
       </c>
     </row>
@@ -9768,24 +9925,28 @@
         <f aca="false">상수!$B$2^(A8-1)</f>
         <v>1.973822685184</v>
       </c>
-      <c r="C8" s="18" t="n">
-        <f aca="false">IF(A8&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A8,"")</f>
+      <c r="C8" s="17" t="n">
+        <f aca="false">상수!$B$3^(A8-1)</f>
+        <v>1.677100110841</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <f aca="false">IF(A8&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A8,"")</f>
         <v>170</v>
       </c>
-      <c r="D8" s="18" t="n">
-        <f aca="false">IF(A8&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A8,"")</f>
+      <c r="E8" s="18" t="n">
+        <f aca="false">IF(A8&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A8,"")</f>
         <v>114</v>
       </c>
-      <c r="E8" s="19" t="n">
-        <f aca="false">IF(A8&lt;상수!$B$34,ROUND(상수!$B$30*A8^상수!$B$31,0),"")</f>
+      <c r="F8" s="19" t="n">
+        <f aca="false">IF(A8&lt;상수!$B$35,ROUND(상수!$B$31*A8^상수!$B$32,0),"")</f>
         <v>1852</v>
       </c>
-      <c r="F8" s="19" t="n">
-        <f aca="false">IF(A8&lt;=상수!$B$34,F7+E7,"")</f>
+      <c r="G8" s="19" t="n">
+        <f aca="false">IF(A8&lt;=상수!$B$35,G7+F7,"")</f>
         <v>4291</v>
       </c>
-      <c r="G8" s="18" t="n">
-        <f aca="false">상수!$B$3*A8+상수!$B$4</f>
+      <c r="H8" s="18" t="n">
+        <f aca="false">상수!$B$4*A8+상수!$B$5</f>
         <v>155</v>
       </c>
     </row>
@@ -9797,24 +9958,28 @@
         <f aca="false">상수!$B$2^(A9-1)</f>
         <v>2.21068140740608</v>
       </c>
-      <c r="C9" s="18" t="n">
-        <f aca="false">IF(A9&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A9,"")</f>
+      <c r="C9" s="17" t="n">
+        <f aca="false">상수!$B$3^(A9-1)</f>
+        <v>1.82803912081669</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <f aca="false">IF(A9&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A9,"")</f>
         <v>180</v>
       </c>
-      <c r="D9" s="18" t="n">
-        <f aca="false">IF(A9&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A9,"")</f>
+      <c r="E9" s="18" t="n">
+        <f aca="false">IF(A9&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A9,"")</f>
         <v>116</v>
       </c>
-      <c r="E9" s="19" t="n">
-        <f aca="false">IF(A9&lt;상수!$B$34,ROUND(상수!$B$30*A9^상수!$B$31,0),"")</f>
+      <c r="F9" s="19" t="n">
+        <f aca="false">IF(A9&lt;상수!$B$35,ROUND(상수!$B$31*A9^상수!$B$32,0),"")</f>
         <v>2263</v>
       </c>
-      <c r="F9" s="19" t="n">
-        <f aca="false">IF(A9&lt;=상수!$B$34,F8+E8,"")</f>
+      <c r="G9" s="19" t="n">
+        <f aca="false">IF(A9&lt;=상수!$B$35,G8+F8,"")</f>
         <v>6143</v>
       </c>
-      <c r="G9" s="18" t="n">
-        <f aca="false">상수!$B$3*A9+상수!$B$4</f>
+      <c r="H9" s="18" t="n">
+        <f aca="false">상수!$B$4*A9+상수!$B$5</f>
         <v>170</v>
       </c>
     </row>
@@ -9826,24 +9991,28 @@
         <f aca="false">상수!$B$2^(A10-1)</f>
         <v>2.47596317629481</v>
       </c>
-      <c r="C10" s="18" t="n">
-        <f aca="false">IF(A10&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A10,"")</f>
+      <c r="C10" s="17" t="n">
+        <f aca="false">상수!$B$3^(A10-1)</f>
+        <v>1.99256264169019</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <f aca="false">IF(A10&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A10,"")</f>
         <v>190</v>
       </c>
-      <c r="D10" s="18" t="n">
-        <f aca="false">IF(A10&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A10,"")</f>
+      <c r="E10" s="18" t="n">
+        <f aca="false">IF(A10&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A10,"")</f>
         <v>118</v>
       </c>
-      <c r="E10" s="19" t="n">
-        <f aca="false">IF(A10&lt;상수!$B$34,ROUND(상수!$B$30*A10^상수!$B$31,0),"")</f>
+      <c r="F10" s="19" t="n">
+        <f aca="false">IF(A10&lt;상수!$B$35,ROUND(상수!$B$31*A10^상수!$B$32,0),"")</f>
         <v>2700</v>
       </c>
-      <c r="F10" s="19" t="n">
-        <f aca="false">IF(A10&lt;=상수!$B$34,F9+E9,"")</f>
+      <c r="G10" s="19" t="n">
+        <f aca="false">IF(A10&lt;=상수!$B$35,G9+F9,"")</f>
         <v>8406</v>
       </c>
-      <c r="G10" s="18" t="n">
-        <f aca="false">상수!$B$3*A10+상수!$B$4</f>
+      <c r="H10" s="18" t="n">
+        <f aca="false">상수!$B$4*A10+상수!$B$5</f>
         <v>185</v>
       </c>
     </row>
@@ -9855,24 +10024,28 @@
         <f aca="false">상수!$B$2^(A11-1)</f>
         <v>2.77307875745019</v>
       </c>
-      <c r="C11" s="18" t="n">
-        <f aca="false">IF(A11&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A11,"")</f>
+      <c r="C11" s="17" t="n">
+        <f aca="false">상수!$B$3^(A11-1)</f>
+        <v>2.17189327944231</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <f aca="false">IF(A11&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A11,"")</f>
         <v>200</v>
       </c>
-      <c r="D11" s="18" t="n">
-        <f aca="false">IF(A11&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A11,"")</f>
+      <c r="E11" s="18" t="n">
+        <f aca="false">IF(A11&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A11,"")</f>
         <v>120</v>
       </c>
-      <c r="E11" s="19" t="n">
-        <f aca="false">IF(A11&lt;상수!$B$34,ROUND(상수!$B$30*A11^상수!$B$31,0),"")</f>
+      <c r="F11" s="19" t="n">
+        <f aca="false">IF(A11&lt;상수!$B$35,ROUND(상수!$B$31*A11^상수!$B$32,0),"")</f>
         <v>3162</v>
       </c>
-      <c r="F11" s="19" t="n">
-        <f aca="false">IF(A11&lt;=상수!$B$34,F10+E10,"")</f>
+      <c r="G11" s="19" t="n">
+        <f aca="false">IF(A11&lt;=상수!$B$35,G10+F10,"")</f>
         <v>11106</v>
       </c>
-      <c r="G11" s="18" t="n">
-        <f aca="false">상수!$B$3*A11+상수!$B$4</f>
+      <c r="H11" s="18" t="n">
+        <f aca="false">상수!$B$4*A11+상수!$B$5</f>
         <v>200</v>
       </c>
     </row>
@@ -9884,24 +10057,28 @@
         <f aca="false">상수!$B$2^(A12-1)</f>
         <v>3.10584820834421</v>
       </c>
-      <c r="C12" s="18" t="n">
-        <f aca="false">IF(A12&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A12,"")</f>
+      <c r="C12" s="17" t="n">
+        <f aca="false">상수!$B$3^(A12-1)</f>
+        <v>2.36736367459212</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <f aca="false">IF(A12&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A12,"")</f>
         <v>210</v>
       </c>
-      <c r="D12" s="18" t="n">
-        <f aca="false">IF(A12&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A12,"")</f>
+      <c r="E12" s="18" t="n">
+        <f aca="false">IF(A12&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A12,"")</f>
         <v>122</v>
       </c>
-      <c r="E12" s="19" t="n">
-        <f aca="false">IF(A12&lt;상수!$B$34,ROUND(상수!$B$30*A12^상수!$B$31,0),"")</f>
+      <c r="F12" s="19" t="n">
+        <f aca="false">IF(A12&lt;상수!$B$35,ROUND(상수!$B$31*A12^상수!$B$32,0),"")</f>
         <v>3648</v>
       </c>
-      <c r="F12" s="19" t="n">
-        <f aca="false">IF(A12&lt;=상수!$B$34,F11+E11,"")</f>
+      <c r="G12" s="19" t="n">
+        <f aca="false">IF(A12&lt;=상수!$B$35,G11+F11,"")</f>
         <v>14268</v>
       </c>
-      <c r="G12" s="18" t="n">
-        <f aca="false">상수!$B$3*A12+상수!$B$4</f>
+      <c r="H12" s="18" t="n">
+        <f aca="false">상수!$B$4*A12+상수!$B$5</f>
         <v>215</v>
       </c>
     </row>
@@ -9913,24 +10090,28 @@
         <f aca="false">상수!$B$2^(A13-1)</f>
         <v>3.47854999334552</v>
       </c>
-      <c r="C13" s="18" t="n">
-        <f aca="false">IF(A13&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A13,"")</f>
+      <c r="C13" s="17" t="n">
+        <f aca="false">상수!$B$3^(A13-1)</f>
+        <v>2.58042640530541</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <f aca="false">IF(A13&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A13,"")</f>
         <v>220</v>
       </c>
-      <c r="D13" s="18" t="n">
-        <f aca="false">IF(A13&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A13,"")</f>
+      <c r="E13" s="18" t="n">
+        <f aca="false">IF(A13&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A13,"")</f>
         <v>124</v>
       </c>
-      <c r="E13" s="19" t="n">
-        <f aca="false">IF(A13&lt;상수!$B$34,ROUND(상수!$B$30*A13^상수!$B$31,0),"")</f>
+      <c r="F13" s="19" t="n">
+        <f aca="false">IF(A13&lt;상수!$B$35,ROUND(상수!$B$31*A13^상수!$B$32,0),"")</f>
         <v>4157</v>
       </c>
-      <c r="F13" s="19" t="n">
-        <f aca="false">IF(A13&lt;=상수!$B$34,F12+E12,"")</f>
+      <c r="G13" s="19" t="n">
+        <f aca="false">IF(A13&lt;=상수!$B$35,G12+F12,"")</f>
         <v>17916</v>
       </c>
-      <c r="G13" s="18" t="n">
-        <f aca="false">상수!$B$3*A13+상수!$B$4</f>
+      <c r="H13" s="18" t="n">
+        <f aca="false">상수!$B$4*A13+상수!$B$5</f>
         <v>230</v>
       </c>
     </row>
@@ -9942,24 +10123,28 @@
         <f aca="false">상수!$B$2^(A14-1)</f>
         <v>3.89597599254698</v>
       </c>
-      <c r="C14" s="18" t="n">
-        <f aca="false">IF(A14&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A14,"")</f>
+      <c r="C14" s="17" t="n">
+        <f aca="false">상수!$B$3^(A14-1)</f>
+        <v>2.8126647817829</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <f aca="false">IF(A14&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A14,"")</f>
         <v>230</v>
       </c>
-      <c r="D14" s="18" t="n">
-        <f aca="false">IF(A14&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A14,"")</f>
+      <c r="E14" s="18" t="n">
+        <f aca="false">IF(A14&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A14,"")</f>
         <v>126</v>
       </c>
-      <c r="E14" s="19" t="n">
-        <f aca="false">IF(A14&lt;상수!$B$34,ROUND(상수!$B$30*A14^상수!$B$31,0),"")</f>
+      <c r="F14" s="19" t="n">
+        <f aca="false">IF(A14&lt;상수!$B$35,ROUND(상수!$B$31*A14^상수!$B$32,0),"")</f>
         <v>4687</v>
       </c>
-      <c r="F14" s="19" t="n">
-        <f aca="false">IF(A14&lt;=상수!$B$34,F13+E13,"")</f>
+      <c r="G14" s="19" t="n">
+        <f aca="false">IF(A14&lt;=상수!$B$35,G13+F13,"")</f>
         <v>22073</v>
       </c>
-      <c r="G14" s="18" t="n">
-        <f aca="false">상수!$B$3*A14+상수!$B$4</f>
+      <c r="H14" s="18" t="n">
+        <f aca="false">상수!$B$4*A14+상수!$B$5</f>
         <v>245</v>
       </c>
     </row>
@@ -9971,24 +10156,28 @@
         <f aca="false">상수!$B$2^(A15-1)</f>
         <v>4.36349311165262</v>
       </c>
-      <c r="C15" s="18" t="n">
-        <f aca="false">IF(A15&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A15,"")</f>
+      <c r="C15" s="17" t="n">
+        <f aca="false">상수!$B$3^(A15-1)</f>
+        <v>3.06580461214336</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <f aca="false">IF(A15&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A15,"")</f>
         <v>240</v>
       </c>
-      <c r="D15" s="18" t="n">
-        <f aca="false">IF(A15&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A15,"")</f>
+      <c r="E15" s="18" t="n">
+        <f aca="false">IF(A15&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A15,"")</f>
         <v>128</v>
       </c>
-      <c r="E15" s="19" t="n">
-        <f aca="false">IF(A15&lt;상수!$B$34,ROUND(상수!$B$30*A15^상수!$B$31,0),"")</f>
+      <c r="F15" s="19" t="n">
+        <f aca="false">IF(A15&lt;상수!$B$35,ROUND(상수!$B$31*A15^상수!$B$32,0),"")</f>
         <v>5238</v>
       </c>
-      <c r="F15" s="19" t="n">
-        <f aca="false">IF(A15&lt;=상수!$B$34,F14+E14,"")</f>
+      <c r="G15" s="19" t="n">
+        <f aca="false">IF(A15&lt;=상수!$B$35,G14+F14,"")</f>
         <v>26760</v>
       </c>
-      <c r="G15" s="18" t="n">
-        <f aca="false">상수!$B$3*A15+상수!$B$4</f>
+      <c r="H15" s="18" t="n">
+        <f aca="false">상수!$B$4*A15+상수!$B$5</f>
         <v>260</v>
       </c>
     </row>
@@ -10000,24 +10189,28 @@
         <f aca="false">상수!$B$2^(A16-1)</f>
         <v>4.88711228505093</v>
       </c>
-      <c r="C16" s="18" t="n">
-        <f aca="false">IF(A16&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A16,"")</f>
+      <c r="C16" s="17" t="n">
+        <f aca="false">상수!$B$3^(A16-1)</f>
+        <v>3.34172702723626</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <f aca="false">IF(A16&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A16,"")</f>
         <v>250</v>
       </c>
-      <c r="D16" s="18" t="n">
-        <f aca="false">IF(A16&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A16,"")</f>
+      <c r="E16" s="18" t="n">
+        <f aca="false">IF(A16&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A16,"")</f>
         <v>130</v>
       </c>
-      <c r="E16" s="19" t="n">
-        <f aca="false">IF(A16&lt;상수!$B$34,ROUND(상수!$B$30*A16^상수!$B$31,0),"")</f>
+      <c r="F16" s="19" t="n">
+        <f aca="false">IF(A16&lt;상수!$B$35,ROUND(상수!$B$31*A16^상수!$B$32,0),"")</f>
         <v>5809</v>
       </c>
-      <c r="F16" s="19" t="n">
-        <f aca="false">IF(A16&lt;=상수!$B$34,F15+E15,"")</f>
+      <c r="G16" s="19" t="n">
+        <f aca="false">IF(A16&lt;=상수!$B$35,G15+F15,"")</f>
         <v>31998</v>
       </c>
-      <c r="G16" s="18" t="n">
-        <f aca="false">상수!$B$3*A16+상수!$B$4</f>
+      <c r="H16" s="18" t="n">
+        <f aca="false">상수!$B$4*A16+상수!$B$5</f>
         <v>275</v>
       </c>
     </row>
@@ -10029,24 +10222,28 @@
         <f aca="false">상수!$B$2^(A17-1)</f>
         <v>5.47356575925705</v>
       </c>
-      <c r="C17" s="18" t="n">
-        <f aca="false">IF(A17&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A17,"")</f>
+      <c r="C17" s="17" t="n">
+        <f aca="false">상수!$B$3^(A17-1)</f>
+        <v>3.64248245968752</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <f aca="false">IF(A17&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A17,"")</f>
         <v>260</v>
       </c>
-      <c r="D17" s="18" t="n">
-        <f aca="false">IF(A17&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A17,"")</f>
+      <c r="E17" s="18" t="n">
+        <f aca="false">IF(A17&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A17,"")</f>
         <v>132</v>
       </c>
-      <c r="E17" s="19" t="n">
-        <f aca="false">IF(A17&lt;상수!$B$34,ROUND(상수!$B$30*A17^상수!$B$31,0),"")</f>
+      <c r="F17" s="19" t="n">
+        <f aca="false">IF(A17&lt;상수!$B$35,ROUND(상수!$B$31*A17^상수!$B$32,0),"")</f>
         <v>6400</v>
       </c>
-      <c r="F17" s="19" t="n">
-        <f aca="false">IF(A17&lt;=상수!$B$34,F16+E16,"")</f>
+      <c r="G17" s="19" t="n">
+        <f aca="false">IF(A17&lt;=상수!$B$35,G16+F16,"")</f>
         <v>37807</v>
       </c>
-      <c r="G17" s="18" t="n">
-        <f aca="false">상수!$B$3*A17+상수!$B$4</f>
+      <c r="H17" s="18" t="n">
+        <f aca="false">상수!$B$4*A17+상수!$B$5</f>
         <v>290</v>
       </c>
     </row>
@@ -10058,24 +10255,28 @@
         <f aca="false">상수!$B$2^(A18-1)</f>
         <v>6.13039365036789</v>
       </c>
-      <c r="C18" s="18" t="n">
-        <f aca="false">IF(A18&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A18,"")</f>
+      <c r="C18" s="17" t="n">
+        <f aca="false">상수!$B$3^(A18-1)</f>
+        <v>3.9703058810594</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <f aca="false">IF(A18&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A18,"")</f>
         <v>270</v>
       </c>
-      <c r="D18" s="18" t="n">
-        <f aca="false">IF(A18&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A18,"")</f>
+      <c r="E18" s="18" t="n">
+        <f aca="false">IF(A18&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A18,"")</f>
         <v>134</v>
       </c>
-      <c r="E18" s="19" t="n">
-        <f aca="false">IF(A18&lt;상수!$B$34,ROUND(상수!$B$30*A18^상수!$B$31,0),"")</f>
+      <c r="F18" s="19" t="n">
+        <f aca="false">IF(A18&lt;상수!$B$35,ROUND(상수!$B$31*A18^상수!$B$32,0),"")</f>
         <v>7009</v>
       </c>
-      <c r="F18" s="19" t="n">
-        <f aca="false">IF(A18&lt;=상수!$B$34,F17+E17,"")</f>
+      <c r="G18" s="19" t="n">
+        <f aca="false">IF(A18&lt;=상수!$B$35,G17+F17,"")</f>
         <v>44207</v>
       </c>
-      <c r="G18" s="18" t="n">
-        <f aca="false">상수!$B$3*A18+상수!$B$4</f>
+      <c r="H18" s="18" t="n">
+        <f aca="false">상수!$B$4*A18+상수!$B$5</f>
         <v>305</v>
       </c>
     </row>
@@ -10087,24 +10288,28 @@
         <f aca="false">상수!$B$2^(A19-1)</f>
         <v>6.86604088841204</v>
       </c>
-      <c r="C19" s="18" t="n">
-        <f aca="false">IF(A19&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A19,"")</f>
+      <c r="C19" s="17" t="n">
+        <f aca="false">상수!$B$3^(A19-1)</f>
+        <v>4.32763341035475</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <f aca="false">IF(A19&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A19,"")</f>
         <v>280</v>
       </c>
-      <c r="D19" s="18" t="n">
-        <f aca="false">IF(A19&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A19,"")</f>
+      <c r="E19" s="18" t="n">
+        <f aca="false">IF(A19&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A19,"")</f>
         <v>136</v>
       </c>
-      <c r="E19" s="19" t="n">
-        <f aca="false">IF(A19&lt;상수!$B$34,ROUND(상수!$B$30*A19^상수!$B$31,0),"")</f>
+      <c r="F19" s="19" t="n">
+        <f aca="false">IF(A19&lt;상수!$B$35,ROUND(상수!$B$31*A19^상수!$B$32,0),"")</f>
         <v>7637</v>
       </c>
-      <c r="F19" s="19" t="n">
-        <f aca="false">IF(A19&lt;=상수!$B$34,F18+E18,"")</f>
+      <c r="G19" s="19" t="n">
+        <f aca="false">IF(A19&lt;=상수!$B$35,G18+F18,"")</f>
         <v>51216</v>
       </c>
-      <c r="G19" s="18" t="n">
-        <f aca="false">상수!$B$3*A19+상수!$B$4</f>
+      <c r="H19" s="18" t="n">
+        <f aca="false">상수!$B$4*A19+상수!$B$5</f>
         <v>320</v>
       </c>
     </row>
@@ -10116,24 +10321,28 @@
         <f aca="false">상수!$B$2^(A20-1)</f>
         <v>7.68996579502149</v>
       </c>
-      <c r="C20" s="18" t="n">
-        <f aca="false">IF(A20&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A20,"")</f>
+      <c r="C20" s="17" t="n">
+        <f aca="false">상수!$B$3^(A20-1)</f>
+        <v>4.71712041728668</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <f aca="false">IF(A20&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A20,"")</f>
         <v>290</v>
       </c>
-      <c r="D20" s="18" t="n">
-        <f aca="false">IF(A20&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A20,"")</f>
+      <c r="E20" s="18" t="n">
+        <f aca="false">IF(A20&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A20,"")</f>
         <v>138</v>
       </c>
-      <c r="E20" s="19" t="n">
-        <f aca="false">IF(A20&lt;상수!$B$34,ROUND(상수!$B$30*A20^상수!$B$31,0),"")</f>
+      <c r="F20" s="19" t="n">
+        <f aca="false">IF(A20&lt;상수!$B$35,ROUND(상수!$B$31*A20^상수!$B$32,0),"")</f>
         <v>8282</v>
       </c>
-      <c r="F20" s="19" t="n">
-        <f aca="false">IF(A20&lt;=상수!$B$34,F19+E19,"")</f>
+      <c r="G20" s="19" t="n">
+        <f aca="false">IF(A20&lt;=상수!$B$35,G19+F19,"")</f>
         <v>58853</v>
       </c>
-      <c r="G20" s="18" t="n">
-        <f aca="false">상수!$B$3*A20+상수!$B$4</f>
+      <c r="H20" s="18" t="n">
+        <f aca="false">상수!$B$4*A20+상수!$B$5</f>
         <v>335</v>
       </c>
     </row>
@@ -10145,24 +10354,28 @@
         <f aca="false">상수!$B$2^(A21-1)</f>
         <v>8.61276169042406</v>
       </c>
-      <c r="C21" s="18" t="n">
-        <f aca="false">IF(A21&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A21,"")</f>
+      <c r="C21" s="17" t="n">
+        <f aca="false">상수!$B$3^(A21-1)</f>
+        <v>5.14166125484248</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <f aca="false">IF(A21&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A21,"")</f>
         <v>300</v>
       </c>
-      <c r="D21" s="18" t="n">
-        <f aca="false">IF(A21&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A21,"")</f>
+      <c r="E21" s="18" t="n">
+        <f aca="false">IF(A21&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A21,"")</f>
         <v>140</v>
       </c>
-      <c r="E21" s="19" t="n">
-        <f aca="false">IF(A21&lt;상수!$B$34,ROUND(상수!$B$30*A21^상수!$B$31,0),"")</f>
+      <c r="F21" s="19" t="n">
+        <f aca="false">IF(A21&lt;상수!$B$35,ROUND(상수!$B$31*A21^상수!$B$32,0),"")</f>
         <v>8944</v>
       </c>
-      <c r="F21" s="19" t="n">
-        <f aca="false">IF(A21&lt;=상수!$B$34,F20+E20,"")</f>
+      <c r="G21" s="19" t="n">
+        <f aca="false">IF(A21&lt;=상수!$B$35,G20+F20,"")</f>
         <v>67135</v>
       </c>
-      <c r="G21" s="18" t="n">
-        <f aca="false">상수!$B$3*A21+상수!$B$4</f>
+      <c r="H21" s="18" t="n">
+        <f aca="false">상수!$B$4*A21+상수!$B$5</f>
         <v>350</v>
       </c>
     </row>
@@ -10174,24 +10387,28 @@
         <f aca="false">상수!$B$2^(A22-1)</f>
         <v>9.64629309327495</v>
       </c>
-      <c r="C22" s="18" t="n">
-        <f aca="false">IF(A22&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A22,"")</f>
+      <c r="C22" s="17" t="n">
+        <f aca="false">상수!$B$3^(A22-1)</f>
+        <v>5.6044107677783</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <f aca="false">IF(A22&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A22,"")</f>
         <v>310</v>
       </c>
-      <c r="D22" s="18" t="n">
-        <f aca="false">IF(A22&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A22,"")</f>
+      <c r="E22" s="18" t="n">
+        <f aca="false">IF(A22&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A22,"")</f>
         <v>142</v>
       </c>
-      <c r="E22" s="19" t="n">
-        <f aca="false">IF(A22&lt;상수!$B$34,ROUND(상수!$B$30*A22^상수!$B$31,0),"")</f>
+      <c r="F22" s="19" t="n">
+        <f aca="false">IF(A22&lt;상수!$B$35,ROUND(상수!$B$31*A22^상수!$B$32,0),"")</f>
         <v>9623</v>
       </c>
-      <c r="F22" s="19" t="n">
-        <f aca="false">IF(A22&lt;=상수!$B$34,F21+E21,"")</f>
+      <c r="G22" s="19" t="n">
+        <f aca="false">IF(A22&lt;=상수!$B$35,G21+F21,"")</f>
         <v>76079</v>
       </c>
-      <c r="G22" s="18" t="n">
-        <f aca="false">상수!$B$3*A22+상수!$B$4</f>
+      <c r="H22" s="18" t="n">
+        <f aca="false">상수!$B$4*A22+상수!$B$5</f>
         <v>365</v>
       </c>
     </row>
@@ -10203,24 +10420,28 @@
         <f aca="false">상수!$B$2^(A23-1)</f>
         <v>10.8038482644679</v>
       </c>
-      <c r="C23" s="18" t="n">
-        <f aca="false">IF(A23&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A23,"")</f>
+      <c r="C23" s="17" t="n">
+        <f aca="false">상수!$B$3^(A23-1)</f>
+        <v>6.10880773687835</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <f aca="false">IF(A23&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A23,"")</f>
         <v>320</v>
       </c>
-      <c r="D23" s="18" t="n">
-        <f aca="false">IF(A23&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A23,"")</f>
+      <c r="E23" s="18" t="n">
+        <f aca="false">IF(A23&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A23,"")</f>
         <v>144</v>
       </c>
-      <c r="E23" s="19" t="n">
-        <f aca="false">IF(A23&lt;상수!$B$34,ROUND(상수!$B$30*A23^상수!$B$31,0),"")</f>
+      <c r="F23" s="19" t="n">
+        <f aca="false">IF(A23&lt;상수!$B$35,ROUND(상수!$B$31*A23^상수!$B$32,0),"")</f>
         <v>10319</v>
       </c>
-      <c r="F23" s="19" t="n">
-        <f aca="false">IF(A23&lt;=상수!$B$34,F22+E22,"")</f>
+      <c r="G23" s="19" t="n">
+        <f aca="false">IF(A23&lt;=상수!$B$35,G22+F22,"")</f>
         <v>85702</v>
       </c>
-      <c r="G23" s="18" t="n">
-        <f aca="false">상수!$B$3*A23+상수!$B$4</f>
+      <c r="H23" s="18" t="n">
+        <f aca="false">상수!$B$4*A23+상수!$B$5</f>
         <v>380</v>
       </c>
     </row>
@@ -10232,24 +10453,28 @@
         <f aca="false">상수!$B$2^(A24-1)</f>
         <v>12.1003100562041</v>
       </c>
-      <c r="C24" s="18" t="n">
-        <f aca="false">IF(A24&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A24,"")</f>
+      <c r="C24" s="17" t="n">
+        <f aca="false">상수!$B$3^(A24-1)</f>
+        <v>6.6586004331974</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <f aca="false">IF(A24&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A24,"")</f>
         <v>330</v>
       </c>
-      <c r="D24" s="18" t="n">
-        <f aca="false">IF(A24&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A24,"")</f>
+      <c r="E24" s="18" t="n">
+        <f aca="false">IF(A24&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A24,"")</f>
         <v>146</v>
       </c>
-      <c r="E24" s="19" t="n">
-        <f aca="false">IF(A24&lt;상수!$B$34,ROUND(상수!$B$30*A24^상수!$B$31,0),"")</f>
+      <c r="F24" s="19" t="n">
+        <f aca="false">IF(A24&lt;상수!$B$35,ROUND(상수!$B$31*A24^상수!$B$32,0),"")</f>
         <v>11030</v>
       </c>
-      <c r="F24" s="19" t="n">
-        <f aca="false">IF(A24&lt;=상수!$B$34,F23+E23,"")</f>
+      <c r="G24" s="19" t="n">
+        <f aca="false">IF(A24&lt;=상수!$B$35,G23+F23,"")</f>
         <v>96021</v>
       </c>
-      <c r="G24" s="18" t="n">
-        <f aca="false">상수!$B$3*A24+상수!$B$4</f>
+      <c r="H24" s="18" t="n">
+        <f aca="false">상수!$B$4*A24+상수!$B$5</f>
         <v>395</v>
       </c>
     </row>
@@ -10261,24 +10486,28 @@
         <f aca="false">상수!$B$2^(A25-1)</f>
         <v>13.5523472629486</v>
       </c>
-      <c r="C25" s="18" t="n">
-        <f aca="false">IF(A25&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A25,"")</f>
+      <c r="C25" s="17" t="n">
+        <f aca="false">상수!$B$3^(A25-1)</f>
+        <v>7.25787447218517</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <f aca="false">IF(A25&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A25,"")</f>
         <v>340</v>
       </c>
-      <c r="D25" s="18" t="n">
-        <f aca="false">IF(A25&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A25,"")</f>
+      <c r="E25" s="18" t="n">
+        <f aca="false">IF(A25&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A25,"")</f>
         <v>148</v>
       </c>
-      <c r="E25" s="19" t="n">
-        <f aca="false">IF(A25&lt;상수!$B$34,ROUND(상수!$B$30*A25^상수!$B$31,0),"")</f>
+      <c r="F25" s="19" t="n">
+        <f aca="false">IF(A25&lt;상수!$B$35,ROUND(상수!$B$31*A25^상수!$B$32,0),"")</f>
         <v>11758</v>
       </c>
-      <c r="F25" s="19" t="n">
-        <f aca="false">IF(A25&lt;=상수!$B$34,F24+E24,"")</f>
+      <c r="G25" s="19" t="n">
+        <f aca="false">IF(A25&lt;=상수!$B$35,G24+F24,"")</f>
         <v>107051</v>
       </c>
-      <c r="G25" s="18" t="n">
-        <f aca="false">상수!$B$3*A25+상수!$B$4</f>
+      <c r="H25" s="18" t="n">
+        <f aca="false">상수!$B$4*A25+상수!$B$5</f>
         <v>410</v>
       </c>
     </row>
@@ -10290,24 +10519,28 @@
         <f aca="false">상수!$B$2^(A26-1)</f>
         <v>15.1786289345024</v>
       </c>
-      <c r="C26" s="18" t="n">
-        <f aca="false">IF(A26&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A26,"")</f>
+      <c r="C26" s="17" t="n">
+        <f aca="false">상수!$B$3^(A26-1)</f>
+        <v>7.91108317468183</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <f aca="false">IF(A26&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A26,"")</f>
         <v>350</v>
       </c>
-      <c r="D26" s="18" t="n">
-        <f aca="false">IF(A26&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A26,"")</f>
+      <c r="E26" s="18" t="n">
+        <f aca="false">IF(A26&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A26,"")</f>
         <v>150</v>
       </c>
-      <c r="E26" s="19" t="n">
-        <f aca="false">IF(A26&lt;상수!$B$34,ROUND(상수!$B$30*A26^상수!$B$31,0),"")</f>
+      <c r="F26" s="19" t="n">
+        <f aca="false">IF(A26&lt;상수!$B$35,ROUND(상수!$B$31*A26^상수!$B$32,0),"")</f>
         <v>12500</v>
       </c>
-      <c r="F26" s="19" t="n">
-        <f aca="false">IF(A26&lt;=상수!$B$34,F25+E25,"")</f>
+      <c r="G26" s="19" t="n">
+        <f aca="false">IF(A26&lt;=상수!$B$35,G25+F25,"")</f>
         <v>118809</v>
       </c>
-      <c r="G26" s="18" t="n">
-        <f aca="false">상수!$B$3*A26+상수!$B$4</f>
+      <c r="H26" s="18" t="n">
+        <f aca="false">상수!$B$4*A26+상수!$B$5</f>
         <v>425</v>
       </c>
     </row>
@@ -10319,24 +10552,28 @@
         <f aca="false">상수!$B$2^(A27-1)</f>
         <v>17.0000644066427</v>
       </c>
-      <c r="C27" s="18" t="n">
-        <f aca="false">IF(A27&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A27,"")</f>
+      <c r="C27" s="17" t="n">
+        <f aca="false">상수!$B$3^(A27-1)</f>
+        <v>8.6230806604032</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <f aca="false">IF(A27&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A27,"")</f>
         <v>360</v>
       </c>
-      <c r="D27" s="18" t="n">
-        <f aca="false">IF(A27&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A27,"")</f>
+      <c r="E27" s="18" t="n">
+        <f aca="false">IF(A27&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A27,"")</f>
         <v>152</v>
       </c>
-      <c r="E27" s="19" t="n">
-        <f aca="false">IF(A27&lt;상수!$B$34,ROUND(상수!$B$30*A27^상수!$B$31,0),"")</f>
+      <c r="F27" s="19" t="n">
+        <f aca="false">IF(A27&lt;상수!$B$35,ROUND(상수!$B$31*A27^상수!$B$32,0),"")</f>
         <v>13257</v>
       </c>
-      <c r="F27" s="19" t="n">
-        <f aca="false">IF(A27&lt;=상수!$B$34,F26+E26,"")</f>
+      <c r="G27" s="19" t="n">
+        <f aca="false">IF(A27&lt;=상수!$B$35,G26+F26,"")</f>
         <v>131309</v>
       </c>
-      <c r="G27" s="18" t="n">
-        <f aca="false">상수!$B$3*A27+상수!$B$4</f>
+      <c r="H27" s="18" t="n">
+        <f aca="false">상수!$B$4*A27+상수!$B$5</f>
         <v>440</v>
       </c>
     </row>
@@ -10348,24 +10585,28 @@
         <f aca="false">상수!$B$2^(A28-1)</f>
         <v>19.0400721354399</v>
       </c>
-      <c r="C28" s="18" t="n">
-        <f aca="false">IF(A28&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A28,"")</f>
+      <c r="C28" s="17" t="n">
+        <f aca="false">상수!$B$3^(A28-1)</f>
+        <v>9.39915791983949</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <f aca="false">IF(A28&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A28,"")</f>
         <v>370</v>
       </c>
-      <c r="D28" s="18" t="n">
-        <f aca="false">IF(A28&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A28,"")</f>
+      <c r="E28" s="18" t="n">
+        <f aca="false">IF(A28&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A28,"")</f>
         <v>154</v>
       </c>
-      <c r="E28" s="19" t="n">
-        <f aca="false">IF(A28&lt;상수!$B$34,ROUND(상수!$B$30*A28^상수!$B$31,0),"")</f>
+      <c r="F28" s="19" t="n">
+        <f aca="false">IF(A28&lt;상수!$B$35,ROUND(상수!$B$31*A28^상수!$B$32,0),"")</f>
         <v>14030</v>
       </c>
-      <c r="F28" s="19" t="n">
-        <f aca="false">IF(A28&lt;=상수!$B$34,F27+E27,"")</f>
+      <c r="G28" s="19" t="n">
+        <f aca="false">IF(A28&lt;=상수!$B$35,G27+F27,"")</f>
         <v>144566</v>
       </c>
-      <c r="G28" s="18" t="n">
-        <f aca="false">상수!$B$3*A28+상수!$B$4</f>
+      <c r="H28" s="18" t="n">
+        <f aca="false">상수!$B$4*A28+상수!$B$5</f>
         <v>455</v>
       </c>
     </row>
@@ -10377,24 +10618,28 @@
         <f aca="false">상수!$B$2^(A29-1)</f>
         <v>21.3248807916926</v>
       </c>
-      <c r="C29" s="18" t="n">
-        <f aca="false">IF(A29&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A29,"")</f>
+      <c r="C29" s="17" t="n">
+        <f aca="false">상수!$B$3^(A29-1)</f>
+        <v>10.245082132625</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <f aca="false">IF(A29&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A29,"")</f>
         <v>380</v>
       </c>
-      <c r="D29" s="18" t="n">
-        <f aca="false">IF(A29&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A29,"")</f>
+      <c r="E29" s="18" t="n">
+        <f aca="false">IF(A29&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A29,"")</f>
         <v>156</v>
       </c>
-      <c r="E29" s="19" t="n">
-        <f aca="false">IF(A29&lt;상수!$B$34,ROUND(상수!$B$30*A29^상수!$B$31,0),"")</f>
+      <c r="F29" s="19" t="n">
+        <f aca="false">IF(A29&lt;상수!$B$35,ROUND(상수!$B$31*A29^상수!$B$32,0),"")</f>
         <v>14816</v>
       </c>
-      <c r="F29" s="19" t="n">
-        <f aca="false">IF(A29&lt;=상수!$B$34,F28+E28,"")</f>
+      <c r="G29" s="19" t="n">
+        <f aca="false">IF(A29&lt;=상수!$B$35,G28+F28,"")</f>
         <v>158596</v>
       </c>
-      <c r="G29" s="18" t="n">
-        <f aca="false">상수!$B$3*A29+상수!$B$4</f>
+      <c r="H29" s="18" t="n">
+        <f aca="false">상수!$B$4*A29+상수!$B$5</f>
         <v>470</v>
       </c>
     </row>
@@ -10406,24 +10651,28 @@
         <f aca="false">상수!$B$2^(A30-1)</f>
         <v>23.8838664866958</v>
       </c>
-      <c r="C30" s="18" t="n">
-        <f aca="false">IF(A30&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A30,"")</f>
+      <c r="C30" s="17" t="n">
+        <f aca="false">상수!$B$3^(A30-1)</f>
+        <v>11.1671395245613</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <f aca="false">IF(A30&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A30,"")</f>
         <v>390</v>
       </c>
-      <c r="D30" s="18" t="n">
-        <f aca="false">IF(A30&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A30,"")</f>
+      <c r="E30" s="18" t="n">
+        <f aca="false">IF(A30&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A30,"")</f>
         <v>158</v>
       </c>
-      <c r="E30" s="19" t="n">
-        <f aca="false">IF(A30&lt;상수!$B$34,ROUND(상수!$B$30*A30^상수!$B$31,0),"")</f>
+      <c r="F30" s="19" t="n">
+        <f aca="false">IF(A30&lt;상수!$B$35,ROUND(상수!$B$31*A30^상수!$B$32,0),"")</f>
         <v>15617</v>
       </c>
-      <c r="F30" s="19" t="n">
-        <f aca="false">IF(A30&lt;=상수!$B$34,F29+E29,"")</f>
+      <c r="G30" s="19" t="n">
+        <f aca="false">IF(A30&lt;=상수!$B$35,G29+F29,"")</f>
         <v>173412</v>
       </c>
-      <c r="G30" s="18" t="n">
-        <f aca="false">상수!$B$3*A30+상수!$B$4</f>
+      <c r="H30" s="18" t="n">
+        <f aca="false">상수!$B$4*A30+상수!$B$5</f>
         <v>485</v>
       </c>
     </row>
@@ -10435,24 +10684,28 @@
         <f aca="false">상수!$B$2^(A31-1)</f>
         <v>26.7499304650992</v>
       </c>
-      <c r="C31" s="18" t="n">
-        <f aca="false">IF(A31&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A31,"")</f>
+      <c r="C31" s="17" t="n">
+        <f aca="false">상수!$B$3^(A31-1)</f>
+        <v>12.1721820817718</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <f aca="false">IF(A31&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A31,"")</f>
         <v>400</v>
       </c>
-      <c r="D31" s="18" t="n">
-        <f aca="false">IF(A31&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A31,"")</f>
+      <c r="E31" s="18" t="n">
+        <f aca="false">IF(A31&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A31,"")</f>
         <v>160</v>
       </c>
-      <c r="E31" s="19" t="n">
-        <f aca="false">IF(A31&lt;상수!$B$34,ROUND(상수!$B$30*A31^상수!$B$31,0),"")</f>
+      <c r="F31" s="19" t="n">
+        <f aca="false">IF(A31&lt;상수!$B$35,ROUND(상수!$B$31*A31^상수!$B$32,0),"")</f>
         <v>16432</v>
       </c>
-      <c r="F31" s="19" t="n">
-        <f aca="false">IF(A31&lt;=상수!$B$34,F30+E30,"")</f>
+      <c r="G31" s="19" t="n">
+        <f aca="false">IF(A31&lt;=상수!$B$35,G30+F30,"")</f>
         <v>189029</v>
       </c>
-      <c r="G31" s="18" t="n">
-        <f aca="false">상수!$B$3*A31+상수!$B$4</f>
+      <c r="H31" s="18" t="n">
+        <f aca="false">상수!$B$4*A31+상수!$B$5</f>
         <v>500</v>
       </c>
     </row>
@@ -10464,24 +10717,28 @@
         <f aca="false">상수!$B$2^(A32-1)</f>
         <v>29.9599221209112</v>
       </c>
-      <c r="C32" s="18" t="n">
-        <f aca="false">IF(A32&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A32,"")</f>
+      <c r="C32" s="17" t="n">
+        <f aca="false">상수!$B$3^(A32-1)</f>
+        <v>13.2676784691313</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <f aca="false">IF(A32&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A32,"")</f>
         <v>410</v>
       </c>
-      <c r="D32" s="18" t="n">
-        <f aca="false">IF(A32&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A32,"")</f>
+      <c r="E32" s="18" t="n">
+        <f aca="false">IF(A32&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A32,"")</f>
         <v>162</v>
       </c>
-      <c r="E32" s="19" t="n">
-        <f aca="false">IF(A32&lt;상수!$B$34,ROUND(상수!$B$30*A32^상수!$B$31,0),"")</f>
+      <c r="F32" s="19" t="n">
+        <f aca="false">IF(A32&lt;상수!$B$35,ROUND(상수!$B$31*A32^상수!$B$32,0),"")</f>
         <v>17260</v>
       </c>
-      <c r="F32" s="19" t="n">
-        <f aca="false">IF(A32&lt;=상수!$B$34,F31+E31,"")</f>
+      <c r="G32" s="19" t="n">
+        <f aca="false">IF(A32&lt;=상수!$B$35,G31+F31,"")</f>
         <v>205461</v>
       </c>
-      <c r="G32" s="18" t="n">
-        <f aca="false">상수!$B$3*A32+상수!$B$4</f>
+      <c r="H32" s="18" t="n">
+        <f aca="false">상수!$B$4*A32+상수!$B$5</f>
         <v>515</v>
       </c>
     </row>
@@ -10493,24 +10750,28 @@
         <f aca="false">상수!$B$2^(A33-1)</f>
         <v>33.5551127754205</v>
       </c>
-      <c r="C33" s="18" t="n">
-        <f aca="false">IF(A33&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A33,"")</f>
+      <c r="C33" s="17" t="n">
+        <f aca="false">상수!$B$3^(A33-1)</f>
+        <v>14.4617695313531</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <f aca="false">IF(A33&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A33,"")</f>
         <v>420</v>
       </c>
-      <c r="D33" s="18" t="n">
-        <f aca="false">IF(A33&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A33,"")</f>
+      <c r="E33" s="18" t="n">
+        <f aca="false">IF(A33&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A33,"")</f>
         <v>164</v>
       </c>
-      <c r="E33" s="19" t="n">
-        <f aca="false">IF(A33&lt;상수!$B$34,ROUND(상수!$B$30*A33^상수!$B$31,0),"")</f>
+      <c r="F33" s="19" t="n">
+        <f aca="false">IF(A33&lt;상수!$B$35,ROUND(상수!$B$31*A33^상수!$B$32,0),"")</f>
         <v>18102</v>
       </c>
-      <c r="F33" s="19" t="n">
-        <f aca="false">IF(A33&lt;=상수!$B$34,F32+E32,"")</f>
+      <c r="G33" s="19" t="n">
+        <f aca="false">IF(A33&lt;=상수!$B$35,G32+F32,"")</f>
         <v>222721</v>
       </c>
-      <c r="G33" s="18" t="n">
-        <f aca="false">상수!$B$3*A33+상수!$B$4</f>
+      <c r="H33" s="18" t="n">
+        <f aca="false">상수!$B$4*A33+상수!$B$5</f>
         <v>530</v>
       </c>
     </row>
@@ -10522,24 +10783,28 @@
         <f aca="false">상수!$B$2^(A34-1)</f>
         <v>37.581726308471</v>
       </c>
-      <c r="C34" s="18" t="n">
-        <f aca="false">IF(A34&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A34,"")</f>
+      <c r="C34" s="17" t="n">
+        <f aca="false">상수!$B$3^(A34-1)</f>
+        <v>15.7633287891749</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <f aca="false">IF(A34&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A34,"")</f>
         <v>430</v>
       </c>
-      <c r="D34" s="18" t="n">
-        <f aca="false">IF(A34&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A34,"")</f>
+      <c r="E34" s="18" t="n">
+        <f aca="false">IF(A34&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A34,"")</f>
         <v>166</v>
       </c>
-      <c r="E34" s="19" t="n">
-        <f aca="false">IF(A34&lt;상수!$B$34,ROUND(상수!$B$30*A34^상수!$B$31,0),"")</f>
+      <c r="F34" s="19" t="n">
+        <f aca="false">IF(A34&lt;상수!$B$35,ROUND(상수!$B$31*A34^상수!$B$32,0),"")</f>
         <v>18957</v>
       </c>
-      <c r="F34" s="19" t="n">
-        <f aca="false">IF(A34&lt;=상수!$B$34,F33+E33,"")</f>
+      <c r="G34" s="19" t="n">
+        <f aca="false">IF(A34&lt;=상수!$B$35,G33+F33,"")</f>
         <v>240823</v>
       </c>
-      <c r="G34" s="18" t="n">
-        <f aca="false">상수!$B$3*A34+상수!$B$4</f>
+      <c r="H34" s="18" t="n">
+        <f aca="false">상수!$B$4*A34+상수!$B$5</f>
         <v>545</v>
       </c>
     </row>
@@ -10551,24 +10816,28 @@
         <f aca="false">상수!$B$2^(A35-1)</f>
         <v>42.0915334654875</v>
       </c>
-      <c r="C35" s="18" t="n">
-        <f aca="false">IF(A35&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A35,"")</f>
+      <c r="C35" s="17" t="n">
+        <f aca="false">상수!$B$3^(A35-1)</f>
+        <v>17.1820283802006</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <f aca="false">IF(A35&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A35,"")</f>
         <v>440</v>
       </c>
-      <c r="D35" s="18" t="n">
-        <f aca="false">IF(A35&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A35,"")</f>
+      <c r="E35" s="18" t="n">
+        <f aca="false">IF(A35&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A35,"")</f>
         <v>168</v>
       </c>
-      <c r="E35" s="19" t="n">
-        <f aca="false">IF(A35&lt;상수!$B$34,ROUND(상수!$B$30*A35^상수!$B$31,0),"")</f>
+      <c r="F35" s="19" t="n">
+        <f aca="false">IF(A35&lt;상수!$B$35,ROUND(상수!$B$31*A35^상수!$B$32,0),"")</f>
         <v>19825</v>
       </c>
-      <c r="F35" s="19" t="n">
-        <f aca="false">IF(A35&lt;=상수!$B$34,F34+E34,"")</f>
+      <c r="G35" s="19" t="n">
+        <f aca="false">IF(A35&lt;=상수!$B$35,G34+F34,"")</f>
         <v>259780</v>
       </c>
-      <c r="G35" s="18" t="n">
-        <f aca="false">상수!$B$3*A35+상수!$B$4</f>
+      <c r="H35" s="18" t="n">
+        <f aca="false">상수!$B$4*A35+상수!$B$5</f>
         <v>560</v>
       </c>
     </row>
@@ -10580,24 +10849,28 @@
         <f aca="false">상수!$B$2^(A36-1)</f>
         <v>47.142517481346</v>
       </c>
-      <c r="C36" s="18" t="n">
-        <f aca="false">IF(A36&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A36,"")</f>
+      <c r="C36" s="17" t="n">
+        <f aca="false">상수!$B$3^(A36-1)</f>
+        <v>18.7284109344187</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <f aca="false">IF(A36&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A36,"")</f>
         <v>450</v>
       </c>
-      <c r="D36" s="18" t="n">
-        <f aca="false">IF(A36&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A36,"")</f>
+      <c r="E36" s="18" t="n">
+        <f aca="false">IF(A36&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A36,"")</f>
         <v>170</v>
       </c>
-      <c r="E36" s="19" t="n">
-        <f aca="false">IF(A36&lt;상수!$B$34,ROUND(상수!$B$30*A36^상수!$B$31,0),"")</f>
+      <c r="F36" s="19" t="n">
+        <f aca="false">IF(A36&lt;상수!$B$35,ROUND(상수!$B$31*A36^상수!$B$32,0),"")</f>
         <v>20706</v>
       </c>
-      <c r="F36" s="19" t="n">
-        <f aca="false">IF(A36&lt;=상수!$B$34,F35+E35,"")</f>
+      <c r="G36" s="19" t="n">
+        <f aca="false">IF(A36&lt;=상수!$B$35,G35+F35,"")</f>
         <v>279605</v>
       </c>
-      <c r="G36" s="18" t="n">
-        <f aca="false">상수!$B$3*A36+상수!$B$4</f>
+      <c r="H36" s="18" t="n">
+        <f aca="false">상수!$B$4*A36+상수!$B$5</f>
         <v>575</v>
       </c>
     </row>
@@ -10609,24 +10882,28 @@
         <f aca="false">상수!$B$2^(A37-1)</f>
         <v>52.7996195791075</v>
       </c>
-      <c r="C37" s="18" t="n">
-        <f aca="false">IF(A37&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A37,"")</f>
+      <c r="C37" s="17" t="n">
+        <f aca="false">상수!$B$3^(A37-1)</f>
+        <v>20.4139679185164</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <f aca="false">IF(A37&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A37,"")</f>
         <v>460</v>
       </c>
-      <c r="D37" s="18" t="n">
-        <f aca="false">IF(A37&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A37,"")</f>
+      <c r="E37" s="18" t="n">
+        <f aca="false">IF(A37&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A37,"")</f>
         <v>172</v>
       </c>
-      <c r="E37" s="19" t="n">
-        <f aca="false">IF(A37&lt;상수!$B$34,ROUND(상수!$B$30*A37^상수!$B$31,0),"")</f>
+      <c r="F37" s="19" t="n">
+        <f aca="false">IF(A37&lt;상수!$B$35,ROUND(상수!$B$31*A37^상수!$B$32,0),"")</f>
         <v>21600</v>
       </c>
-      <c r="F37" s="19" t="n">
-        <f aca="false">IF(A37&lt;=상수!$B$34,F36+E36,"")</f>
+      <c r="G37" s="19" t="n">
+        <f aca="false">IF(A37&lt;=상수!$B$35,G36+F36,"")</f>
         <v>300311</v>
       </c>
-      <c r="G37" s="18" t="n">
-        <f aca="false">상수!$B$3*A37+상수!$B$4</f>
+      <c r="H37" s="18" t="n">
+        <f aca="false">상수!$B$4*A37+상수!$B$5</f>
         <v>590</v>
       </c>
     </row>
@@ -10638,24 +10915,28 @@
         <f aca="false">상수!$B$2^(A38-1)</f>
         <v>59.1355739286004</v>
       </c>
-      <c r="C38" s="18" t="n">
-        <f aca="false">IF(A38&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A38,"")</f>
+      <c r="C38" s="17" t="n">
+        <f aca="false">상수!$B$3^(A38-1)</f>
+        <v>22.2512250311828</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <f aca="false">IF(A38&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A38,"")</f>
         <v>470</v>
       </c>
-      <c r="D38" s="18" t="n">
-        <f aca="false">IF(A38&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A38,"")</f>
+      <c r="E38" s="18" t="n">
+        <f aca="false">IF(A38&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A38,"")</f>
         <v>174</v>
       </c>
-      <c r="E38" s="19" t="n">
-        <f aca="false">IF(A38&lt;상수!$B$34,ROUND(상수!$B$30*A38^상수!$B$31,0),"")</f>
+      <c r="F38" s="19" t="n">
+        <f aca="false">IF(A38&lt;상수!$B$35,ROUND(상수!$B$31*A38^상수!$B$32,0),"")</f>
         <v>22506</v>
       </c>
-      <c r="F38" s="19" t="n">
-        <f aca="false">IF(A38&lt;=상수!$B$34,F37+E37,"")</f>
+      <c r="G38" s="19" t="n">
+        <f aca="false">IF(A38&lt;=상수!$B$35,G37+F37,"")</f>
         <v>321911</v>
       </c>
-      <c r="G38" s="18" t="n">
-        <f aca="false">상수!$B$3*A38+상수!$B$4</f>
+      <c r="H38" s="18" t="n">
+        <f aca="false">상수!$B$4*A38+상수!$B$5</f>
         <v>605</v>
       </c>
     </row>
@@ -10667,24 +10948,28 @@
         <f aca="false">상수!$B$2^(A39-1)</f>
         <v>66.2318428000325</v>
       </c>
-      <c r="C39" s="18" t="n">
-        <f aca="false">IF(A39&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A39,"")</f>
+      <c r="C39" s="17" t="n">
+        <f aca="false">상수!$B$3^(A39-1)</f>
+        <v>24.2538352839893</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <f aca="false">IF(A39&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A39,"")</f>
         <v>480</v>
       </c>
-      <c r="D39" s="18" t="n">
-        <f aca="false">IF(A39&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A39,"")</f>
+      <c r="E39" s="18" t="n">
+        <f aca="false">IF(A39&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A39,"")</f>
         <v>176</v>
       </c>
-      <c r="E39" s="19" t="n">
-        <f aca="false">IF(A39&lt;상수!$B$34,ROUND(상수!$B$30*A39^상수!$B$31,0),"")</f>
+      <c r="F39" s="19" t="n">
+        <f aca="false">IF(A39&lt;상수!$B$35,ROUND(상수!$B$31*A39^상수!$B$32,0),"")</f>
         <v>23425</v>
       </c>
-      <c r="F39" s="19" t="n">
-        <f aca="false">IF(A39&lt;=상수!$B$34,F38+E38,"")</f>
+      <c r="G39" s="19" t="n">
+        <f aca="false">IF(A39&lt;=상수!$B$35,G38+F38,"")</f>
         <v>344417</v>
       </c>
-      <c r="G39" s="18" t="n">
-        <f aca="false">상수!$B$3*A39+상수!$B$4</f>
+      <c r="H39" s="18" t="n">
+        <f aca="false">상수!$B$4*A39+상수!$B$5</f>
         <v>620</v>
       </c>
     </row>
@@ -10696,24 +10981,28 @@
         <f aca="false">상수!$B$2^(A40-1)</f>
         <v>74.1796639360364</v>
       </c>
-      <c r="C40" s="18" t="n">
-        <f aca="false">IF(A40&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A40,"")</f>
+      <c r="C40" s="17" t="n">
+        <f aca="false">상수!$B$3^(A40-1)</f>
+        <v>26.4366804595483</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <f aca="false">IF(A40&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A40,"")</f>
         <v>490</v>
       </c>
-      <c r="D40" s="18" t="n">
-        <f aca="false">IF(A40&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A40,"")</f>
+      <c r="E40" s="18" t="n">
+        <f aca="false">IF(A40&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A40,"")</f>
         <v>178</v>
       </c>
-      <c r="E40" s="19" t="n">
-        <f aca="false">IF(A40&lt;상수!$B$34,ROUND(상수!$B$30*A40^상수!$B$31,0),"")</f>
+      <c r="F40" s="19" t="n">
+        <f aca="false">IF(A40&lt;상수!$B$35,ROUND(상수!$B$31*A40^상수!$B$32,0),"")</f>
         <v>24355</v>
       </c>
-      <c r="F40" s="19" t="n">
-        <f aca="false">IF(A40&lt;=상수!$B$34,F39+E39,"")</f>
+      <c r="G40" s="19" t="n">
+        <f aca="false">IF(A40&lt;=상수!$B$35,G39+F39,"")</f>
         <v>367842</v>
       </c>
-      <c r="G40" s="18" t="n">
-        <f aca="false">상수!$B$3*A40+상수!$B$4</f>
+      <c r="H40" s="18" t="n">
+        <f aca="false">상수!$B$4*A40+상수!$B$5</f>
         <v>635</v>
       </c>
     </row>
@@ -10725,24 +11014,28 @@
         <f aca="false">상수!$B$2^(A41-1)</f>
         <v>83.0812236083607</v>
       </c>
-      <c r="C41" s="18" t="n">
-        <f aca="false">IF(A41&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A41,"")</f>
+      <c r="C41" s="17" t="n">
+        <f aca="false">상수!$B$3^(A41-1)</f>
+        <v>28.8159817009077</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <f aca="false">IF(A41&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A41,"")</f>
         <v>500</v>
       </c>
-      <c r="D41" s="18" t="n">
-        <f aca="false">IF(A41&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A41,"")</f>
+      <c r="E41" s="18" t="n">
+        <f aca="false">IF(A41&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A41,"")</f>
         <v>180</v>
       </c>
-      <c r="E41" s="19" t="n">
-        <f aca="false">IF(A41&lt;상수!$B$34,ROUND(상수!$B$30*A41^상수!$B$31,0),"")</f>
+      <c r="F41" s="19" t="n">
+        <f aca="false">IF(A41&lt;상수!$B$35,ROUND(상수!$B$31*A41^상수!$B$32,0),"")</f>
         <v>25298</v>
       </c>
-      <c r="F41" s="19" t="n">
-        <f aca="false">IF(A41&lt;=상수!$B$34,F40+E40,"")</f>
+      <c r="G41" s="19" t="n">
+        <f aca="false">IF(A41&lt;=상수!$B$35,G40+F40,"")</f>
         <v>392197</v>
       </c>
-      <c r="G41" s="18" t="n">
-        <f aca="false">상수!$B$3*A41+상수!$B$4</f>
+      <c r="H41" s="18" t="n">
+        <f aca="false">상수!$B$4*A41+상수!$B$5</f>
         <v>650</v>
       </c>
     </row>
@@ -10754,24 +11047,28 @@
         <f aca="false">상수!$B$2^(A42-1)</f>
         <v>93.050970441364</v>
       </c>
-      <c r="C42" s="18" t="n">
-        <f aca="false">IF(A42&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A42,"")</f>
+      <c r="C42" s="17" t="n">
+        <f aca="false">상수!$B$3^(A42-1)</f>
+        <v>31.4094200539894</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <f aca="false">IF(A42&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A42,"")</f>
         <v>510</v>
       </c>
-      <c r="D42" s="18" t="n">
-        <f aca="false">IF(A42&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A42,"")</f>
+      <c r="E42" s="18" t="n">
+        <f aca="false">IF(A42&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A42,"")</f>
         <v>182</v>
       </c>
-      <c r="E42" s="19" t="n">
-        <f aca="false">IF(A42&lt;상수!$B$34,ROUND(상수!$B$30*A42^상수!$B$31,0),"")</f>
+      <c r="F42" s="19" t="n">
+        <f aca="false">IF(A42&lt;상수!$B$35,ROUND(상수!$B$31*A42^상수!$B$32,0),"")</f>
         <v>26253</v>
       </c>
-      <c r="F42" s="19" t="n">
-        <f aca="false">IF(A42&lt;=상수!$B$34,F41+E41,"")</f>
+      <c r="G42" s="19" t="n">
+        <f aca="false">IF(A42&lt;=상수!$B$35,G41+F41,"")</f>
         <v>417495</v>
       </c>
-      <c r="G42" s="18" t="n">
-        <f aca="false">상수!$B$3*A42+상수!$B$4</f>
+      <c r="H42" s="18" t="n">
+        <f aca="false">상수!$B$4*A42+상수!$B$5</f>
         <v>665</v>
       </c>
     </row>
@@ -10783,24 +11080,28 @@
         <f aca="false">상수!$B$2^(A43-1)</f>
         <v>104.217086894328</v>
       </c>
-      <c r="C43" s="18" t="n">
-        <f aca="false">IF(A43&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A43,"")</f>
+      <c r="C43" s="17" t="n">
+        <f aca="false">상수!$B$3^(A43-1)</f>
+        <v>34.2362678588484</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <f aca="false">IF(A43&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A43,"")</f>
         <v>520</v>
       </c>
-      <c r="D43" s="18" t="n">
-        <f aca="false">IF(A43&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A43,"")</f>
+      <c r="E43" s="18" t="n">
+        <f aca="false">IF(A43&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A43,"")</f>
         <v>184</v>
       </c>
-      <c r="E43" s="19" t="n">
-        <f aca="false">IF(A43&lt;상수!$B$34,ROUND(상수!$B$30*A43^상수!$B$31,0),"")</f>
+      <c r="F43" s="19" t="n">
+        <f aca="false">IF(A43&lt;상수!$B$35,ROUND(상수!$B$31*A43^상수!$B$32,0),"")</f>
         <v>27219</v>
       </c>
-      <c r="F43" s="19" t="n">
-        <f aca="false">IF(A43&lt;=상수!$B$34,F42+E42,"")</f>
+      <c r="G43" s="19" t="n">
+        <f aca="false">IF(A43&lt;=상수!$B$35,G42+F42,"")</f>
         <v>443748</v>
       </c>
-      <c r="G43" s="18" t="n">
-        <f aca="false">상수!$B$3*A43+상수!$B$4</f>
+      <c r="H43" s="18" t="n">
+        <f aca="false">상수!$B$4*A43+상수!$B$5</f>
         <v>680</v>
       </c>
     </row>
@@ -10812,24 +11113,28 @@
         <f aca="false">상수!$B$2^(A44-1)</f>
         <v>116.723137321647</v>
       </c>
-      <c r="C44" s="18" t="n">
-        <f aca="false">IF(A44&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A44,"")</f>
+      <c r="C44" s="17" t="n">
+        <f aca="false">상수!$B$3^(A44-1)</f>
+        <v>37.3175319661448</v>
+      </c>
+      <c r="D44" s="18" t="n">
+        <f aca="false">IF(A44&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A44,"")</f>
         <v>530</v>
       </c>
-      <c r="D44" s="18" t="n">
-        <f aca="false">IF(A44&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A44,"")</f>
+      <c r="E44" s="18" t="n">
+        <f aca="false">IF(A44&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A44,"")</f>
         <v>186</v>
       </c>
-      <c r="E44" s="19" t="n">
-        <f aca="false">IF(A44&lt;상수!$B$34,ROUND(상수!$B$30*A44^상수!$B$31,0),"")</f>
+      <c r="F44" s="19" t="n">
+        <f aca="false">IF(A44&lt;상수!$B$35,ROUND(상수!$B$31*A44^상수!$B$32,0),"")</f>
         <v>28197</v>
       </c>
-      <c r="F44" s="19" t="n">
-        <f aca="false">IF(A44&lt;=상수!$B$34,F43+E43,"")</f>
+      <c r="G44" s="19" t="n">
+        <f aca="false">IF(A44&lt;=상수!$B$35,G43+F43,"")</f>
         <v>470967</v>
       </c>
-      <c r="G44" s="18" t="n">
-        <f aca="false">상수!$B$3*A44+상수!$B$4</f>
+      <c r="H44" s="18" t="n">
+        <f aca="false">상수!$B$4*A44+상수!$B$5</f>
         <v>695</v>
       </c>
     </row>
@@ -10841,24 +11146,28 @@
         <f aca="false">상수!$B$2^(A45-1)</f>
         <v>130.729913800245</v>
       </c>
-      <c r="C45" s="18" t="n">
-        <f aca="false">IF(A45&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A45,"")</f>
+      <c r="C45" s="17" t="n">
+        <f aca="false">상수!$B$3^(A45-1)</f>
+        <v>40.6761098430978</v>
+      </c>
+      <c r="D45" s="18" t="n">
+        <f aca="false">IF(A45&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A45,"")</f>
         <v>540</v>
       </c>
-      <c r="D45" s="18" t="n">
-        <f aca="false">IF(A45&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A45,"")</f>
+      <c r="E45" s="18" t="n">
+        <f aca="false">IF(A45&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A45,"")</f>
         <v>188</v>
       </c>
-      <c r="E45" s="19" t="n">
-        <f aca="false">IF(A45&lt;상수!$B$34,ROUND(상수!$B$30*A45^상수!$B$31,0),"")</f>
+      <c r="F45" s="19" t="n">
+        <f aca="false">IF(A45&lt;상수!$B$35,ROUND(상수!$B$31*A45^상수!$B$32,0),"")</f>
         <v>29186</v>
       </c>
-      <c r="F45" s="19" t="n">
-        <f aca="false">IF(A45&lt;=상수!$B$34,F44+E44,"")</f>
+      <c r="G45" s="19" t="n">
+        <f aca="false">IF(A45&lt;=상수!$B$35,G44+F44,"")</f>
         <v>499164</v>
       </c>
-      <c r="G45" s="18" t="n">
-        <f aca="false">상수!$B$3*A45+상수!$B$4</f>
+      <c r="H45" s="18" t="n">
+        <f aca="false">상수!$B$4*A45+상수!$B$5</f>
         <v>710</v>
       </c>
     </row>
@@ -10870,24 +11179,28 @@
         <f aca="false">상수!$B$2^(A46-1)</f>
         <v>146.417503456274</v>
       </c>
-      <c r="C46" s="18" t="n">
-        <f aca="false">IF(A46&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A46,"")</f>
+      <c r="C46" s="17" t="n">
+        <f aca="false">상수!$B$3^(A46-1)</f>
+        <v>44.3369597289766</v>
+      </c>
+      <c r="D46" s="18" t="n">
+        <f aca="false">IF(A46&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A46,"")</f>
         <v>550</v>
       </c>
-      <c r="D46" s="18" t="n">
-        <f aca="false">IF(A46&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A46,"")</f>
+      <c r="E46" s="18" t="n">
+        <f aca="false">IF(A46&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A46,"")</f>
         <v>190</v>
       </c>
-      <c r="E46" s="19" t="n">
-        <f aca="false">IF(A46&lt;상수!$B$34,ROUND(상수!$B$30*A46^상수!$B$31,0),"")</f>
+      <c r="F46" s="19" t="n">
+        <f aca="false">IF(A46&lt;상수!$B$35,ROUND(상수!$B$31*A46^상수!$B$32,0),"")</f>
         <v>30187</v>
       </c>
-      <c r="F46" s="19" t="n">
-        <f aca="false">IF(A46&lt;=상수!$B$34,F45+E45,"")</f>
+      <c r="G46" s="19" t="n">
+        <f aca="false">IF(A46&lt;=상수!$B$35,G45+F45,"")</f>
         <v>528350</v>
       </c>
-      <c r="G46" s="18" t="n">
-        <f aca="false">상수!$B$3*A46+상수!$B$4</f>
+      <c r="H46" s="18" t="n">
+        <f aca="false">상수!$B$4*A46+상수!$B$5</f>
         <v>725</v>
       </c>
     </row>
@@ -10899,24 +11212,28 @@
         <f aca="false">상수!$B$2^(A47-1)</f>
         <v>163.987603871027</v>
       </c>
-      <c r="C47" s="18" t="n">
-        <f aca="false">IF(A47&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A47,"")</f>
+      <c r="C47" s="17" t="n">
+        <f aca="false">상수!$B$3^(A47-1)</f>
+        <v>48.3272861045845</v>
+      </c>
+      <c r="D47" s="18" t="n">
+        <f aca="false">IF(A47&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A47,"")</f>
         <v>560</v>
       </c>
-      <c r="D47" s="18" t="n">
-        <f aca="false">IF(A47&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A47,"")</f>
+      <c r="E47" s="18" t="n">
+        <f aca="false">IF(A47&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A47,"")</f>
         <v>192</v>
       </c>
-      <c r="E47" s="19" t="n">
-        <f aca="false">IF(A47&lt;상수!$B$34,ROUND(상수!$B$30*A47^상수!$B$31,0),"")</f>
+      <c r="F47" s="19" t="n">
+        <f aca="false">IF(A47&lt;상수!$B$35,ROUND(상수!$B$31*A47^상수!$B$32,0),"")</f>
         <v>31199</v>
       </c>
-      <c r="F47" s="19" t="n">
-        <f aca="false">IF(A47&lt;=상수!$B$34,F46+E46,"")</f>
+      <c r="G47" s="19" t="n">
+        <f aca="false">IF(A47&lt;=상수!$B$35,G46+F46,"")</f>
         <v>558537</v>
       </c>
-      <c r="G47" s="18" t="n">
-        <f aca="false">상수!$B$3*A47+상수!$B$4</f>
+      <c r="H47" s="18" t="n">
+        <f aca="false">상수!$B$4*A47+상수!$B$5</f>
         <v>740</v>
       </c>
     </row>
@@ -10928,24 +11245,28 @@
         <f aca="false">상수!$B$2^(A48-1)</f>
         <v>183.66611633555</v>
       </c>
-      <c r="C48" s="18" t="n">
-        <f aca="false">IF(A48&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A48,"")</f>
+      <c r="C48" s="17" t="n">
+        <f aca="false">상수!$B$3^(A48-1)</f>
+        <v>52.6767418539971</v>
+      </c>
+      <c r="D48" s="18" t="n">
+        <f aca="false">IF(A48&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A48,"")</f>
         <v>570</v>
       </c>
-      <c r="D48" s="18" t="n">
-        <f aca="false">IF(A48&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A48,"")</f>
+      <c r="E48" s="18" t="n">
+        <f aca="false">IF(A48&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A48,"")</f>
         <v>194</v>
       </c>
-      <c r="E48" s="19" t="n">
-        <f aca="false">IF(A48&lt;상수!$B$34,ROUND(상수!$B$30*A48^상수!$B$31,0),"")</f>
+      <c r="F48" s="19" t="n">
+        <f aca="false">IF(A48&lt;상수!$B$35,ROUND(상수!$B$31*A48^상수!$B$32,0),"")</f>
         <v>32222</v>
       </c>
-      <c r="F48" s="19" t="n">
-        <f aca="false">IF(A48&lt;=상수!$B$34,F47+E47,"")</f>
+      <c r="G48" s="19" t="n">
+        <f aca="false">IF(A48&lt;=상수!$B$35,G47+F47,"")</f>
         <v>589736</v>
       </c>
-      <c r="G48" s="18" t="n">
-        <f aca="false">상수!$B$3*A48+상수!$B$4</f>
+      <c r="H48" s="18" t="n">
+        <f aca="false">상수!$B$4*A48+상수!$B$5</f>
         <v>755</v>
       </c>
     </row>
@@ -10957,24 +11278,28 @@
         <f aca="false">상수!$B$2^(A49-1)</f>
         <v>205.706050295816</v>
       </c>
-      <c r="C49" s="18" t="n">
-        <f aca="false">IF(A49&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A49,"")</f>
+      <c r="C49" s="17" t="n">
+        <f aca="false">상수!$B$3^(A49-1)</f>
+        <v>57.4176486208568</v>
+      </c>
+      <c r="D49" s="18" t="n">
+        <f aca="false">IF(A49&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A49,"")</f>
         <v>580</v>
       </c>
-      <c r="D49" s="18" t="n">
-        <f aca="false">IF(A49&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A49,"")</f>
+      <c r="E49" s="18" t="n">
+        <f aca="false">IF(A49&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A49,"")</f>
         <v>196</v>
       </c>
-      <c r="E49" s="19" t="n">
-        <f aca="false">IF(A49&lt;상수!$B$34,ROUND(상수!$B$30*A49^상수!$B$31,0),"")</f>
+      <c r="F49" s="19" t="n">
+        <f aca="false">IF(A49&lt;상수!$B$35,ROUND(상수!$B$31*A49^상수!$B$32,0),"")</f>
         <v>33255</v>
       </c>
-      <c r="F49" s="19" t="n">
-        <f aca="false">IF(A49&lt;=상수!$B$34,F48+E48,"")</f>
+      <c r="G49" s="19" t="n">
+        <f aca="false">IF(A49&lt;=상수!$B$35,G48+F48,"")</f>
         <v>621958</v>
       </c>
-      <c r="G49" s="18" t="n">
-        <f aca="false">상수!$B$3*A49+상수!$B$4</f>
+      <c r="H49" s="18" t="n">
+        <f aca="false">상수!$B$4*A49+상수!$B$5</f>
         <v>770</v>
       </c>
     </row>
@@ -10986,24 +11311,28 @@
         <f aca="false">상수!$B$2^(A50-1)</f>
         <v>230.390776331314</v>
       </c>
-      <c r="C50" s="18" t="n">
-        <f aca="false">IF(A50&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A50,"")</f>
+      <c r="C50" s="17" t="n">
+        <f aca="false">상수!$B$3^(A50-1)</f>
+        <v>62.585236996734</v>
+      </c>
+      <c r="D50" s="18" t="n">
+        <f aca="false">IF(A50&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A50,"")</f>
         <v>590</v>
       </c>
-      <c r="D50" s="18" t="n">
-        <f aca="false">IF(A50&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A50,"")</f>
+      <c r="E50" s="18" t="n">
+        <f aca="false">IF(A50&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A50,"")</f>
         <v>198</v>
       </c>
-      <c r="E50" s="19" t="n">
-        <f aca="false">IF(A50&lt;상수!$B$34,ROUND(상수!$B$30*A50^상수!$B$31,0),"")</f>
+      <c r="F50" s="19" t="n">
+        <f aca="false">IF(A50&lt;상수!$B$35,ROUND(상수!$B$31*A50^상수!$B$32,0),"")</f>
         <v>34300</v>
       </c>
-      <c r="F50" s="19" t="n">
-        <f aca="false">IF(A50&lt;=상수!$B$34,F49+E49,"")</f>
+      <c r="G50" s="19" t="n">
+        <f aca="false">IF(A50&lt;=상수!$B$35,G49+F49,"")</f>
         <v>655213</v>
       </c>
-      <c r="G50" s="18" t="n">
-        <f aca="false">상수!$B$3*A50+상수!$B$4</f>
+      <c r="H50" s="18" t="n">
+        <f aca="false">상수!$B$4*A50+상수!$B$5</f>
         <v>785</v>
       </c>
     </row>
@@ -11015,24 +11344,28 @@
         <f aca="false">상수!$B$2^(A51-1)</f>
         <v>258.037669491072</v>
       </c>
-      <c r="C51" s="18" t="n">
-        <f aca="false">IF(A51&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A51,"")</f>
+      <c r="C51" s="17" t="n">
+        <f aca="false">상수!$B$3^(A51-1)</f>
+        <v>68.21790832644</v>
+      </c>
+      <c r="D51" s="18" t="n">
+        <f aca="false">IF(A51&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A51,"")</f>
         <v>600</v>
       </c>
-      <c r="D51" s="18" t="n">
-        <f aca="false">IF(A51&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A51,"")</f>
+      <c r="E51" s="18" t="n">
+        <f aca="false">IF(A51&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A51,"")</f>
         <v>200</v>
       </c>
-      <c r="E51" s="19" t="str">
-        <f aca="false">IF(A51&lt;상수!$B$34,ROUND(상수!$B$30*A51^상수!$B$31,0),"")</f>
+      <c r="F51" s="19" t="str">
+        <f aca="false">IF(A51&lt;상수!$B$35,ROUND(상수!$B$31*A51^상수!$B$32,0),"")</f>
         <v/>
       </c>
-      <c r="F51" s="19" t="n">
-        <f aca="false">IF(A51&lt;=상수!$B$34,F50+E50,"")</f>
+      <c r="G51" s="19" t="n">
+        <f aca="false">IF(A51&lt;=상수!$B$35,G50+F50,"")</f>
         <v>689513</v>
       </c>
-      <c r="G51" s="18" t="n">
-        <f aca="false">상수!$B$3*A51+상수!$B$4</f>
+      <c r="H51" s="18" t="n">
+        <f aca="false">상수!$B$4*A51+상수!$B$5</f>
         <v>800</v>
       </c>
     </row>
@@ -11044,24 +11377,28 @@
         <f aca="false">상수!$B$2^(A52-1)</f>
         <v>289.002189830001</v>
       </c>
-      <c r="C52" s="18" t="str">
-        <f aca="false">IF(A52&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A52,"")</f>
+      <c r="C52" s="17" t="n">
+        <f aca="false">상수!$B$3^(A52-1)</f>
+        <v>74.3575200758196</v>
+      </c>
+      <c r="D52" s="18" t="str">
+        <f aca="false">IF(A52&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A52,"")</f>
         <v/>
       </c>
-      <c r="D52" s="18" t="str">
-        <f aca="false">IF(A52&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A52,"")</f>
+      <c r="E52" s="18" t="str">
+        <f aca="false">IF(A52&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A52,"")</f>
         <v/>
       </c>
-      <c r="E52" s="19" t="str">
-        <f aca="false">IF(A52&lt;상수!$B$34,ROUND(상수!$B$30*A52^상수!$B$31,0),"")</f>
+      <c r="F52" s="19" t="str">
+        <f aca="false">IF(A52&lt;상수!$B$35,ROUND(상수!$B$31*A52^상수!$B$32,0),"")</f>
         <v/>
       </c>
-      <c r="F52" s="19" t="str">
-        <f aca="false">IF(A52&lt;=상수!$B$34,F51+E51,"")</f>
+      <c r="G52" s="19" t="str">
+        <f aca="false">IF(A52&lt;=상수!$B$35,G51+F51,"")</f>
         <v/>
       </c>
-      <c r="G52" s="18" t="n">
-        <f aca="false">상수!$B$3*A52+상수!$B$4</f>
+      <c r="H52" s="18" t="n">
+        <f aca="false">상수!$B$4*A52+상수!$B$5</f>
         <v>815</v>
       </c>
     </row>
@@ -11073,24 +11410,28 @@
         <f aca="false">상수!$B$2^(A53-1)</f>
         <v>323.682452609601</v>
       </c>
-      <c r="C53" s="18" t="str">
-        <f aca="false">IF(A53&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A53,"")</f>
+      <c r="C53" s="17" t="n">
+        <f aca="false">상수!$B$3^(A53-1)</f>
+        <v>81.0496968826434</v>
+      </c>
+      <c r="D53" s="18" t="str">
+        <f aca="false">IF(A53&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A53,"")</f>
         <v/>
       </c>
-      <c r="D53" s="18" t="str">
-        <f aca="false">IF(A53&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A53,"")</f>
+      <c r="E53" s="18" t="str">
+        <f aca="false">IF(A53&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A53,"")</f>
         <v/>
       </c>
-      <c r="E53" s="19" t="str">
-        <f aca="false">IF(A53&lt;상수!$B$34,ROUND(상수!$B$30*A53^상수!$B$31,0),"")</f>
+      <c r="F53" s="19" t="str">
+        <f aca="false">IF(A53&lt;상수!$B$35,ROUND(상수!$B$31*A53^상수!$B$32,0),"")</f>
         <v/>
       </c>
-      <c r="F53" s="19" t="str">
-        <f aca="false">IF(A53&lt;=상수!$B$34,F52+E52,"")</f>
+      <c r="G53" s="19" t="str">
+        <f aca="false">IF(A53&lt;=상수!$B$35,G52+F52,"")</f>
         <v/>
       </c>
-      <c r="G53" s="18" t="n">
-        <f aca="false">상수!$B$3*A53+상수!$B$4</f>
+      <c r="H53" s="18" t="n">
+        <f aca="false">상수!$B$4*A53+상수!$B$5</f>
         <v>830</v>
       </c>
     </row>
@@ -11102,24 +11443,28 @@
         <f aca="false">상수!$B$2^(A54-1)</f>
         <v>362.524346922753</v>
       </c>
-      <c r="C54" s="18" t="str">
-        <f aca="false">IF(A54&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A54,"")</f>
+      <c r="C54" s="17" t="n">
+        <f aca="false">상수!$B$3^(A54-1)</f>
+        <v>88.3441696020813</v>
+      </c>
+      <c r="D54" s="18" t="str">
+        <f aca="false">IF(A54&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A54,"")</f>
         <v/>
       </c>
-      <c r="D54" s="18" t="str">
-        <f aca="false">IF(A54&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A54,"")</f>
+      <c r="E54" s="18" t="str">
+        <f aca="false">IF(A54&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A54,"")</f>
         <v/>
       </c>
-      <c r="E54" s="19" t="str">
-        <f aca="false">IF(A54&lt;상수!$B$34,ROUND(상수!$B$30*A54^상수!$B$31,0),"")</f>
+      <c r="F54" s="19" t="str">
+        <f aca="false">IF(A54&lt;상수!$B$35,ROUND(상수!$B$31*A54^상수!$B$32,0),"")</f>
         <v/>
       </c>
-      <c r="F54" s="19" t="str">
-        <f aca="false">IF(A54&lt;=상수!$B$34,F53+E53,"")</f>
+      <c r="G54" s="19" t="str">
+        <f aca="false">IF(A54&lt;=상수!$B$35,G53+F53,"")</f>
         <v/>
       </c>
-      <c r="G54" s="18" t="n">
-        <f aca="false">상수!$B$3*A54+상수!$B$4</f>
+      <c r="H54" s="18" t="n">
+        <f aca="false">상수!$B$4*A54+상수!$B$5</f>
         <v>845</v>
       </c>
     </row>
@@ -11131,24 +11476,28 @@
         <f aca="false">상수!$B$2^(A55-1)</f>
         <v>406.027268553483</v>
       </c>
-      <c r="C55" s="18" t="str">
-        <f aca="false">IF(A55&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A55,"")</f>
+      <c r="C55" s="17" t="n">
+        <f aca="false">상수!$B$3^(A55-1)</f>
+        <v>96.2951448662686</v>
+      </c>
+      <c r="D55" s="18" t="str">
+        <f aca="false">IF(A55&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A55,"")</f>
         <v/>
       </c>
-      <c r="D55" s="18" t="str">
-        <f aca="false">IF(A55&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A55,"")</f>
+      <c r="E55" s="18" t="str">
+        <f aca="false">IF(A55&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A55,"")</f>
         <v/>
       </c>
-      <c r="E55" s="19" t="str">
-        <f aca="false">IF(A55&lt;상수!$B$34,ROUND(상수!$B$30*A55^상수!$B$31,0),"")</f>
+      <c r="F55" s="19" t="str">
+        <f aca="false">IF(A55&lt;상수!$B$35,ROUND(상수!$B$31*A55^상수!$B$32,0),"")</f>
         <v/>
       </c>
-      <c r="F55" s="19" t="str">
-        <f aca="false">IF(A55&lt;=상수!$B$34,F54+E54,"")</f>
+      <c r="G55" s="19" t="str">
+        <f aca="false">IF(A55&lt;=상수!$B$35,G54+F54,"")</f>
         <v/>
       </c>
-      <c r="G55" s="18" t="n">
-        <f aca="false">상수!$B$3*A55+상수!$B$4</f>
+      <c r="H55" s="18" t="n">
+        <f aca="false">상수!$B$4*A55+상수!$B$5</f>
         <v>860</v>
       </c>
     </row>
@@ -11160,24 +11509,28 @@
         <f aca="false">상수!$B$2^(A56-1)</f>
         <v>454.750540779902</v>
       </c>
-      <c r="C56" s="18" t="str">
-        <f aca="false">IF(A56&lt;=상수!$B$34,상수!$B$18+상수!$B$19*A56,"")</f>
+      <c r="C56" s="17" t="n">
+        <f aca="false">상수!$B$3^(A56-1)</f>
+        <v>104.961707904233</v>
+      </c>
+      <c r="D56" s="18" t="str">
+        <f aca="false">IF(A56&lt;=상수!$B$35,상수!$B$19+상수!$B$20*A56,"")</f>
         <v/>
       </c>
-      <c r="D56" s="18" t="str">
-        <f aca="false">IF(A56&lt;=상수!$B$34,상수!$B$20+상수!$B$21*A56,"")</f>
+      <c r="E56" s="18" t="str">
+        <f aca="false">IF(A56&lt;=상수!$B$35,상수!$B$21+상수!$B$22*A56,"")</f>
         <v/>
       </c>
-      <c r="E56" s="19" t="str">
-        <f aca="false">IF(A56&lt;상수!$B$34,ROUND(상수!$B$30*A56^상수!$B$31,0),"")</f>
+      <c r="F56" s="19" t="str">
+        <f aca="false">IF(A56&lt;상수!$B$35,ROUND(상수!$B$31*A56^상수!$B$32,0),"")</f>
         <v/>
       </c>
-      <c r="F56" s="19" t="str">
-        <f aca="false">IF(A56&lt;=상수!$B$34,F55+E55,"")</f>
+      <c r="G56" s="19" t="str">
+        <f aca="false">IF(A56&lt;=상수!$B$35,G55+F55,"")</f>
         <v/>
       </c>
-      <c r="G56" s="18" t="n">
-        <f aca="false">상수!$B$3*A56+상수!$B$4</f>
+      <c r="H56" s="18" t="n">
+        <f aca="false">상수!$B$4*A56+상수!$B$5</f>
         <v>875</v>
       </c>
     </row>
@@ -11218,72 +11571,72 @@
   <sheetData>
     <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="N1" s="16" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="O1" s="16" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="P1" s="16" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D2" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F2" s="20" t="n">
         <v>30</v>
@@ -11295,7 +11648,7 @@
         <v>1.5</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J2" s="20" t="n">
         <v>5</v>
@@ -11319,24 +11672,24 @@
         <v>50</v>
       </c>
       <c r="Q2" s="13" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F3" s="20" t="n">
         <v>24</v>
@@ -11348,7 +11701,7 @@
         <v>1.2</v>
       </c>
       <c r="I3" s="20" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J3" s="20" t="n">
         <v>3</v>
@@ -11375,19 +11728,19 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F4" s="20" t="n">
         <v>36</v>
@@ -11399,7 +11752,7 @@
         <v>1.5</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J4" s="20" t="n">
         <v>5</v>
@@ -11423,24 +11776,24 @@
         <v>65</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F5" s="20" t="n">
         <v>18</v>
@@ -11452,7 +11805,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J5" s="20" t="n">
         <v>2</v>
@@ -11476,24 +11829,24 @@
         <v>35</v>
       </c>
       <c r="Q5" s="13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F6" s="20" t="n">
         <v>20</v>
@@ -11505,7 +11858,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J6" s="20" t="n">
         <v>0</v>
@@ -11529,24 +11882,24 @@
         <v>45</v>
       </c>
       <c r="Q6" s="13" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F7" s="20" t="n">
         <v>90</v>
@@ -11558,7 +11911,7 @@
         <v>2.5</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J7" s="20" t="n">
         <v>25</v>
@@ -11582,24 +11935,24 @@
         <v>120</v>
       </c>
       <c r="Q7" s="13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F8" s="20" t="n">
         <v>120</v>
@@ -11611,7 +11964,7 @@
         <v>2.5</v>
       </c>
       <c r="I8" s="20" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J8" s="20" t="n">
         <v>40</v>
@@ -11638,19 +11991,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F9" s="20" t="n">
         <v>80</v>
@@ -11662,7 +12015,7 @@
         <v>1.5</v>
       </c>
       <c r="I9" s="20" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J9" s="20" t="n">
         <v>10</v>
@@ -11686,24 +12039,24 @@
         <v>200</v>
       </c>
       <c r="Q9" s="13" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F10" s="20" t="n">
         <v>1500</v>
@@ -11715,7 +12068,7 @@
         <v>1.8</v>
       </c>
       <c r="I10" s="20" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J10" s="20" t="n">
         <v>30</v>
@@ -11739,7 +12092,7 @@
         <v>2000</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -11773,78 +12126,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N1" s="16" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="O1" s="16" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="P1" s="16" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="R1" s="16" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="S1" s="16" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="T1" s="16" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E2" s="14" t="n">
         <v>1</v>
@@ -11870,35 +12223,35 @@
       <c r="L2" s="22"/>
       <c r="M2" s="22"/>
       <c r="N2" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="O2" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="P2" s="22"/>
       <c r="Q2" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="R2" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="S2" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="T2" s="22"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>1</v>
@@ -11922,35 +12275,35 @@
         <v>0.2</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="22"/>
       <c r="O3" s="22"/>
       <c r="P3" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q3" s="22"/>
       <c r="R3" s="22"/>
       <c r="S3" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="T3" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>203</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>200</v>
       </c>
       <c r="E4" s="14" t="n">
         <v>1</v>
@@ -11974,7 +12327,7 @@
         <v>0.8</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
@@ -11987,16 +12340,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E5" s="14" t="n">
         <v>5</v>
@@ -12021,7 +12374,7 @@
       </c>
       <c r="L5" s="22"/>
       <c r="M5" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="N5" s="22"/>
       <c r="O5" s="22"/>
@@ -12029,22 +12382,22 @@
       <c r="Q5" s="22"/>
       <c r="R5" s="22"/>
       <c r="S5" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="T5" s="22"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E6" s="14" t="n">
         <v>5</v>
@@ -12069,7 +12422,7 @@
       </c>
       <c r="L6" s="22"/>
       <c r="M6" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="N6" s="22"/>
       <c r="O6" s="22"/>
@@ -12077,22 +12430,22 @@
       <c r="Q6" s="22"/>
       <c r="R6" s="22"/>
       <c r="S6" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="T6" s="22"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E7" s="14" t="n">
         <v>5</v>
@@ -12116,7 +12469,7 @@
         <v>35</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="M7" s="22"/>
       <c r="N7" s="22"/>
@@ -12129,16 +12482,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>5</v>
@@ -12162,13 +12515,13 @@
         <v>0.15</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="M8" s="22"/>
       <c r="N8" s="22"/>
       <c r="O8" s="22"/>
       <c r="P8" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q8" s="22"/>
       <c r="R8" s="22"/>
@@ -12177,16 +12530,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>5</v>
@@ -12214,29 +12567,29 @@
       <c r="N9" s="22"/>
       <c r="O9" s="22"/>
       <c r="P9" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q9" s="22"/>
       <c r="R9" s="22"/>
       <c r="S9" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="T9" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>5</v>
@@ -12260,7 +12613,7 @@
         <v>0.35</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -12269,24 +12622,24 @@
       <c r="Q10" s="22"/>
       <c r="R10" s="22"/>
       <c r="S10" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="T10" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>1</v>
@@ -12312,33 +12665,33 @@
       <c r="L11" s="22"/>
       <c r="M11" s="22"/>
       <c r="N11" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="O11" s="22"/>
       <c r="P11" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q11" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="R11" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="S11" s="22"/>
       <c r="T11" s="22"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>1</v>
@@ -12365,7 +12718,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
       <c r="O12" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="P12" s="22"/>
       <c r="Q12" s="22"/>
@@ -12375,16 +12728,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>1</v>
@@ -12410,37 +12763,37 @@
       <c r="L13" s="22"/>
       <c r="M13" s="22"/>
       <c r="N13" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="O13" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="P13" s="22"/>
       <c r="Q13" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="R13" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="S13" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="T13" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>1</v>
@@ -12466,37 +12819,37 @@
       <c r="L14" s="22"/>
       <c r="M14" s="22"/>
       <c r="N14" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="O14" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="P14" s="22"/>
       <c r="Q14" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="R14" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="S14" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="T14" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E15" s="14" t="n">
         <v>1</v>
@@ -12522,37 +12875,37 @@
       <c r="L15" s="22"/>
       <c r="M15" s="22"/>
       <c r="N15" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="O15" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="P15" s="22"/>
       <c r="Q15" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="R15" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="S15" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="T15" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>1</v>
@@ -12578,37 +12931,37 @@
       <c r="L16" s="22"/>
       <c r="M16" s="22"/>
       <c r="N16" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="O16" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="P16" s="22"/>
       <c r="Q16" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="R16" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="S16" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="T16" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>15</v>
@@ -12639,22 +12992,22 @@
       <c r="Q17" s="22"/>
       <c r="R17" s="22"/>
       <c r="S17" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="T17" s="22"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E18" s="14" t="n">
         <v>10</v>
@@ -12681,7 +13034,7 @@
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
       <c r="O18" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="P18" s="22"/>
       <c r="Q18" s="22"/>
@@ -12691,16 +13044,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>1</v>
@@ -12727,7 +13080,7 @@
       <c r="M19" s="22"/>
       <c r="N19" s="22"/>
       <c r="O19" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="P19" s="22"/>
       <c r="Q19" s="22"/>
@@ -12737,16 +13090,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E20" s="14" t="n">
         <v>1</v>
@@ -12770,7 +13123,7 @@
         <v>25</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
@@ -12783,16 +13136,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E21" s="14" t="n">
         <v>1</v>
@@ -12818,29 +13171,29 @@
       <c r="L21" s="22"/>
       <c r="M21" s="22"/>
       <c r="N21" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="O21" s="22"/>
       <c r="P21" s="22"/>
       <c r="Q21" s="22"/>
       <c r="R21" s="22"/>
       <c r="S21" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="T21" s="22"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E22" s="14" t="n">
         <v>5</v>
@@ -12871,24 +13224,24 @@
       <c r="Q22" s="22"/>
       <c r="R22" s="22"/>
       <c r="S22" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="T22" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E23" s="14" t="n">
         <v>10</v>
@@ -12913,7 +13266,7 @@
       </c>
       <c r="L23" s="22"/>
       <c r="M23" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="N23" s="22"/>
       <c r="O23" s="22"/>
@@ -12925,16 +13278,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E24" s="14" t="n">
         <v>10</v>
@@ -12959,10 +13312,10 @@
       </c>
       <c r="L24" s="22"/>
       <c r="M24" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="N24" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="O24" s="22"/>
       <c r="P24" s="22"/>
@@ -12973,16 +13326,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E25" s="14" t="n">
         <v>1</v>
@@ -13012,23 +13365,23 @@
       <c r="P25" s="22"/>
       <c r="Q25" s="22"/>
       <c r="R25" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="S25" s="22"/>
       <c r="T25" s="22"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E26" s="14" t="n">
         <v>5</v>
@@ -13057,7 +13410,7 @@
       <c r="O26" s="22"/>
       <c r="P26" s="22"/>
       <c r="Q26" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="R26" s="22"/>
       <c r="S26" s="22"/>
@@ -13065,16 +13418,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E27" s="14" t="n">
         <v>5</v>
@@ -13106,21 +13459,21 @@
       <c r="R27" s="22"/>
       <c r="S27" s="22"/>
       <c r="T27" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E28" s="14" t="n">
         <v>1</v>
@@ -13152,21 +13505,21 @@
       <c r="R28" s="22"/>
       <c r="S28" s="22"/>
       <c r="T28" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E29" s="14" t="n">
         <v>20</v>
@@ -13197,22 +13550,22 @@
       <c r="Q29" s="22"/>
       <c r="R29" s="22"/>
       <c r="S29" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="T29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E30" s="14" t="n">
         <v>30</v>
@@ -13239,7 +13592,7 @@
       <c r="M30" s="22"/>
       <c r="N30" s="22"/>
       <c r="O30" s="22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="P30" s="22"/>
       <c r="Q30" s="22"/>
@@ -13279,36 +13632,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B2" s="11" t="n">
         <v>1</v>
@@ -13317,13 +13670,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G2" s="14" t="n">
         <v>1</v>
@@ -13332,12 +13685,12 @@
         <v>6</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B3" s="11" t="n">
         <v>1</v>
@@ -13346,13 +13699,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>287</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>284</v>
       </c>
       <c r="G3" s="14" t="n">
         <v>2</v>
@@ -13364,7 +13717,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>1</v>
@@ -13373,13 +13726,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G4" s="14" t="n">
         <v>3</v>
@@ -13391,7 +13744,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>1</v>
@@ -13400,10 +13753,10 @@
         <v>4</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F5" s="11"/>
       <c r="G5" s="14" t="n">
@@ -13413,12 +13766,12 @@
         <v>6</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>1</v>
@@ -13427,13 +13780,13 @@
         <v>5</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>5</v>
@@ -13445,7 +13798,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>1</v>
@@ -13454,13 +13807,13 @@
         <v>6</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>6</v>
@@ -13469,12 +13822,12 @@
         <v>20</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>1</v>
@@ -13483,13 +13836,13 @@
         <v>7</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>7</v>
@@ -13501,7 +13854,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>1</v>
@@ -13510,13 +13863,13 @@
         <v>8</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>8</v>
@@ -13525,12 +13878,12 @@
         <v>20</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>1</v>
@@ -13539,13 +13892,13 @@
         <v>9</v>
       </c>
       <c r="D10" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>307</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>304</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>9</v>
@@ -13554,12 +13907,12 @@
         <v>20</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B11" s="11" t="n">
         <v>1</v>
@@ -13568,13 +13921,13 @@
         <v>10</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>9</v>
@@ -13586,7 +13939,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B12" s="11" t="n">
         <v>1</v>
@@ -13595,13 +13948,13 @@
         <v>11</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>10</v>
@@ -13613,7 +13966,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B13" s="11" t="n">
         <v>1</v>
@@ -13622,13 +13975,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>11</v>
@@ -13637,12 +13990,12 @@
         <v>20</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B14" s="11" t="n">
         <v>1</v>
@@ -13651,13 +14004,13 @@
         <v>13</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>12</v>
@@ -13666,12 +14019,12 @@
         <v>20</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B15" s="11" t="n">
         <v>1</v>
@@ -13680,13 +14033,13 @@
         <v>14</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>12</v>
@@ -13698,7 +14051,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>1</v>
@@ -13707,13 +14060,13 @@
         <v>15</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>13</v>
@@ -13722,12 +14075,12 @@
         <v>6</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B17" s="11" t="n">
         <v>2</v>
@@ -13736,13 +14089,13 @@
         <v>1</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>14</v>
@@ -13754,7 +14107,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B18" s="11" t="n">
         <v>2</v>
@@ -13763,10 +14116,10 @@
         <v>2</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="14" t="n">
@@ -13776,12 +14129,12 @@
         <v>0</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B19" s="11" t="n">
         <v>2</v>
@@ -13790,13 +14143,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>15</v>
@@ -13808,7 +14161,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B20" s="11" t="n">
         <v>2</v>
@@ -13817,13 +14170,13 @@
         <v>4</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G20" s="14" t="n">
         <v>16</v>
@@ -13832,12 +14185,12 @@
         <v>20</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B21" s="11" t="n">
         <v>2</v>
@@ -13846,13 +14199,13 @@
         <v>5</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>17</v>
@@ -13864,7 +14217,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B22" s="11" t="n">
         <v>2</v>
@@ -13873,13 +14226,13 @@
         <v>6</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>18</v>
@@ -13891,7 +14244,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B23" s="11" t="n">
         <v>2</v>
@@ -13900,13 +14253,13 @@
         <v>7</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>19</v>
@@ -13915,12 +14268,12 @@
         <v>20</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B24" s="11" t="n">
         <v>2</v>
@@ -13929,13 +14282,13 @@
         <v>8</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>20</v>
@@ -13944,12 +14297,12 @@
         <v>20</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B25" s="11" t="n">
         <v>2</v>
@@ -13958,13 +14311,13 @@
         <v>9</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>19</v>
@@ -13973,12 +14326,12 @@
         <v>20</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B26" s="11" t="n">
         <v>2</v>
@@ -13987,13 +14340,13 @@
         <v>10</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G26" s="14" t="n">
         <v>20</v>
@@ -14005,7 +14358,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B27" s="11" t="n">
         <v>2</v>
@@ -14014,13 +14367,13 @@
         <v>11</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>21</v>
@@ -14029,12 +14382,12 @@
         <v>20</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B28" s="11" t="n">
         <v>2</v>
@@ -14043,13 +14396,13 @@
         <v>12</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>22</v>
@@ -14058,12 +14411,12 @@
         <v>20</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B29" s="11" t="n">
         <v>2</v>
@@ -14072,13 +14425,13 @@
         <v>13</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>22</v>
@@ -14090,7 +14443,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B30" s="11" t="n">
         <v>2</v>
@@ -14099,13 +14452,13 @@
         <v>14</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>23</v>
@@ -14117,7 +14470,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B31" s="11" t="n">
         <v>2</v>
@@ -14126,13 +14479,13 @@
         <v>15</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>24</v>
@@ -14144,7 +14497,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B32" s="11" t="n">
         <v>2</v>
@@ -14153,13 +14506,13 @@
         <v>16</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>24</v>
@@ -14168,12 +14521,12 @@
         <v>6</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B33" s="11" t="n">
         <v>3</v>
@@ -14182,13 +14535,13 @@
         <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>25</v>
@@ -14200,7 +14553,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B34" s="11" t="n">
         <v>3</v>
@@ -14209,10 +14562,10 @@
         <v>2</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F34" s="11"/>
       <c r="G34" s="14" t="n">
@@ -14222,12 +14575,12 @@
         <v>0</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B35" s="11" t="n">
         <v>3</v>
@@ -14236,13 +14589,13 @@
         <v>3</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>26</v>
@@ -14254,7 +14607,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B36" s="11" t="n">
         <v>3</v>
@@ -14263,13 +14616,13 @@
         <v>4</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G36" s="14" t="n">
         <v>27</v>
@@ -14278,12 +14631,12 @@
         <v>20</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B37" s="11" t="n">
         <v>3</v>
@@ -14292,13 +14645,13 @@
         <v>5</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>28</v>
@@ -14307,12 +14660,12 @@
         <v>20</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B38" s="11" t="n">
         <v>3</v>
@@ -14321,13 +14674,13 @@
         <v>6</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G38" s="14" t="n">
         <v>29</v>
@@ -14336,12 +14689,12 @@
         <v>20</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B39" s="11" t="n">
         <v>3</v>
@@ -14350,13 +14703,13 @@
         <v>7</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>28</v>
@@ -14368,7 +14721,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B40" s="11" t="n">
         <v>3</v>
@@ -14377,13 +14730,13 @@
         <v>8</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>29</v>
@@ -14395,7 +14748,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B41" s="11" t="n">
         <v>3</v>
@@ -14404,13 +14757,13 @@
         <v>9</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>30</v>
@@ -14419,12 +14772,12 @@
         <v>20</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B42" s="11" t="n">
         <v>3</v>
@@ -14433,13 +14786,13 @@
         <v>10</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G42" s="14" t="n">
         <v>30</v>
@@ -14448,12 +14801,12 @@
         <v>6</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B43" s="11" t="n">
         <v>3</v>
@@ -14462,13 +14815,13 @@
         <v>11</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>31</v>
@@ -14480,7 +14833,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B44" s="11" t="n">
         <v>3</v>
@@ -14489,13 +14842,13 @@
         <v>12</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G44" s="14" t="n">
         <v>32</v>
@@ -14504,12 +14857,12 @@
         <v>20</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B45" s="11" t="n">
         <v>3</v>
@@ -14518,13 +14871,13 @@
         <v>13</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G45" s="14" t="n">
         <v>33</v>
@@ -14536,7 +14889,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B46" s="11" t="n">
         <v>3</v>
@@ -14545,13 +14898,13 @@
         <v>14</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G46" s="14" t="n">
         <v>34</v>
@@ -14560,12 +14913,12 @@
         <v>20</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B47" s="11" t="n">
         <v>3</v>
@@ -14574,13 +14927,13 @@
         <v>15</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>35</v>
@@ -14589,12 +14942,12 @@
         <v>20</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B48" s="11" t="n">
         <v>3</v>
@@ -14603,13 +14956,13 @@
         <v>16</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G48" s="14" t="n">
         <v>35</v>
@@ -14621,7 +14974,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B49" s="11" t="n">
         <v>3</v>
@@ -14630,13 +14983,13 @@
         <v>17</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>36</v>
@@ -14645,7 +14998,7 @@
         <v>6</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14661,7 +15014,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="23" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -14674,13 +15027,13 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="24" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -14694,11 +15047,11 @@
         <v>1</v>
       </c>
       <c r="B53" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A53</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A53</f>
         <v>14</v>
       </c>
       <c r="C53" s="18" t="n">
-        <f aca="false">B53+상수!$B$28</f>
+        <f aca="false">B53+상수!$B$29</f>
         <v>17</v>
       </c>
       <c r="D53" s="2"/>
@@ -14713,11 +15066,11 @@
         <v>2</v>
       </c>
       <c r="B54" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A54</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A54</f>
         <v>16</v>
       </c>
       <c r="C54" s="18" t="n">
-        <f aca="false">B54+상수!$B$28</f>
+        <f aca="false">B54+상수!$B$29</f>
         <v>19</v>
       </c>
       <c r="D54" s="2"/>
@@ -14732,11 +15085,11 @@
         <v>3</v>
       </c>
       <c r="B55" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A55</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A55</f>
         <v>18</v>
       </c>
       <c r="C55" s="18" t="n">
-        <f aca="false">B55+상수!$B$28</f>
+        <f aca="false">B55+상수!$B$29</f>
         <v>21</v>
       </c>
       <c r="D55" s="2"/>
@@ -14751,11 +15104,11 @@
         <v>4</v>
       </c>
       <c r="B56" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A56</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A56</f>
         <v>20</v>
       </c>
       <c r="C56" s="18" t="n">
-        <f aca="false">B56+상수!$B$28</f>
+        <f aca="false">B56+상수!$B$29</f>
         <v>23</v>
       </c>
       <c r="D56" s="2"/>
@@ -14770,11 +15123,11 @@
         <v>5</v>
       </c>
       <c r="B57" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A57</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A57</f>
         <v>22</v>
       </c>
       <c r="C57" s="18" t="n">
-        <f aca="false">B57+상수!$B$28</f>
+        <f aca="false">B57+상수!$B$29</f>
         <v>25</v>
       </c>
       <c r="D57" s="2"/>
@@ -14789,11 +15142,11 @@
         <v>6</v>
       </c>
       <c r="B58" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A58</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A58</f>
         <v>24</v>
       </c>
       <c r="C58" s="18" t="n">
-        <f aca="false">B58+상수!$B$28</f>
+        <f aca="false">B58+상수!$B$29</f>
         <v>27</v>
       </c>
       <c r="D58" s="2"/>
@@ -14808,11 +15161,11 @@
         <v>7</v>
       </c>
       <c r="B59" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A59</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A59</f>
         <v>26</v>
       </c>
       <c r="C59" s="18" t="n">
-        <f aca="false">B59+상수!$B$28</f>
+        <f aca="false">B59+상수!$B$29</f>
         <v>29</v>
       </c>
       <c r="D59" s="2"/>
@@ -14827,11 +15180,11 @@
         <v>8</v>
       </c>
       <c r="B60" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A60</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A60</f>
         <v>28</v>
       </c>
       <c r="C60" s="18" t="n">
-        <f aca="false">B60+상수!$B$28</f>
+        <f aca="false">B60+상수!$B$29</f>
         <v>31</v>
       </c>
       <c r="D60" s="2"/>
@@ -14846,11 +15199,11 @@
         <v>9</v>
       </c>
       <c r="B61" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A61</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A61</f>
         <v>30</v>
       </c>
       <c r="C61" s="18" t="n">
-        <f aca="false">B61+상수!$B$28</f>
+        <f aca="false">B61+상수!$B$29</f>
         <v>33</v>
       </c>
       <c r="D61" s="2"/>
@@ -14865,11 +15218,11 @@
         <v>10</v>
       </c>
       <c r="B62" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A62</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A62</f>
         <v>32</v>
       </c>
       <c r="C62" s="18" t="n">
-        <f aca="false">B62+상수!$B$28</f>
+        <f aca="false">B62+상수!$B$29</f>
         <v>35</v>
       </c>
       <c r="D62" s="2"/>
@@ -14884,11 +15237,11 @@
         <v>11</v>
       </c>
       <c r="B63" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A63</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A63</f>
         <v>34</v>
       </c>
       <c r="C63" s="18" t="n">
-        <f aca="false">B63+상수!$B$28</f>
+        <f aca="false">B63+상수!$B$29</f>
         <v>37</v>
       </c>
       <c r="D63" s="2"/>
@@ -14903,11 +15256,11 @@
         <v>12</v>
       </c>
       <c r="B64" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A64</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A64</f>
         <v>36</v>
       </c>
       <c r="C64" s="18" t="n">
-        <f aca="false">B64+상수!$B$28</f>
+        <f aca="false">B64+상수!$B$29</f>
         <v>39</v>
       </c>
       <c r="D64" s="2"/>
@@ -14922,11 +15275,11 @@
         <v>13</v>
       </c>
       <c r="B65" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A65</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A65</f>
         <v>38</v>
       </c>
       <c r="C65" s="18" t="n">
-        <f aca="false">B65+상수!$B$28</f>
+        <f aca="false">B65+상수!$B$29</f>
         <v>41</v>
       </c>
       <c r="D65" s="2"/>
@@ -14941,11 +15294,11 @@
         <v>14</v>
       </c>
       <c r="B66" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A66</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A66</f>
         <v>40</v>
       </c>
       <c r="C66" s="18" t="n">
-        <f aca="false">B66+상수!$B$28</f>
+        <f aca="false">B66+상수!$B$29</f>
         <v>43</v>
       </c>
       <c r="D66" s="2"/>
@@ -14960,11 +15313,11 @@
         <v>15</v>
       </c>
       <c r="B67" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A67</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A67</f>
         <v>42</v>
       </c>
       <c r="C67" s="18" t="n">
-        <f aca="false">B67+상수!$B$28</f>
+        <f aca="false">B67+상수!$B$29</f>
         <v>45</v>
       </c>
       <c r="D67" s="2"/>
@@ -14979,11 +15332,11 @@
         <v>16</v>
       </c>
       <c r="B68" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A68</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A68</f>
         <v>44</v>
       </c>
       <c r="C68" s="18" t="n">
-        <f aca="false">B68+상수!$B$28</f>
+        <f aca="false">B68+상수!$B$29</f>
         <v>47</v>
       </c>
       <c r="D68" s="2"/>
@@ -14998,11 +15351,11 @@
         <v>17</v>
       </c>
       <c r="B69" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A69</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A69</f>
         <v>46</v>
       </c>
       <c r="C69" s="18" t="n">
-        <f aca="false">B69+상수!$B$28</f>
+        <f aca="false">B69+상수!$B$29</f>
         <v>49</v>
       </c>
       <c r="D69" s="2"/>
@@ -15017,11 +15370,11 @@
         <v>18</v>
       </c>
       <c r="B70" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A70</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A70</f>
         <v>48</v>
       </c>
       <c r="C70" s="18" t="n">
-        <f aca="false">B70+상수!$B$28</f>
+        <f aca="false">B70+상수!$B$29</f>
         <v>51</v>
       </c>
       <c r="D70" s="2"/>
@@ -15036,11 +15389,11 @@
         <v>19</v>
       </c>
       <c r="B71" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A71</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A71</f>
         <v>50</v>
       </c>
       <c r="C71" s="18" t="n">
-        <f aca="false">B71+상수!$B$28</f>
+        <f aca="false">B71+상수!$B$29</f>
         <v>53</v>
       </c>
       <c r="D71" s="2"/>
@@ -15055,11 +15408,11 @@
         <v>20</v>
       </c>
       <c r="B72" s="18" t="n">
-        <f aca="false">상수!$B$35+상수!$B$36*A72</f>
+        <f aca="false">상수!$B$36+상수!$B$37*A72</f>
         <v>52</v>
       </c>
       <c r="C72" s="18" t="n">
-        <f aca="false">B72+상수!$B$28</f>
+        <f aca="false">B72+상수!$B$29</f>
         <v>55</v>
       </c>
       <c r="D72" s="2"/>
@@ -15097,7 +15450,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15137,13 +15490,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -15162,13 +15515,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B4" s="21" t="n">
         <v>6</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -15187,13 +15540,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B5" s="26" t="n">
         <v>1.115</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -15212,13 +15565,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>1.2</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -15237,13 +15590,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B7" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -15262,13 +15615,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B8" s="27" t="n">
         <v>0.02</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -15287,13 +15640,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B9" s="27" t="n">
         <v>0.003</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -15312,13 +15665,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B10" s="14" t="n">
         <v>4</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -15337,13 +15690,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B11" s="14" t="n">
         <v>12</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -15362,7 +15715,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B12" s="14" t="n">
         <v>20</v>
@@ -15385,13 +15738,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B13" s="21" t="n">
         <v>2.5</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -15410,13 +15763,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B14" s="14" t="n">
         <v>15</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -15435,7 +15788,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B15" s="28" t="n">
         <f aca="false">INDEX(귀신!$F:$F,MATCH($B$3,귀신!$A:$A,0))</f>
@@ -15459,7 +15812,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B16" s="28" t="n">
         <f aca="false">INDEX(귀신!$G:$G,MATCH($B$3,귀신!$A:$A,0))</f>
@@ -15483,7 +15836,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B17" s="29" t="n">
         <f aca="false">INDEX(귀신!$H:$H,MATCH($B$3,귀신!$A:$A,0))</f>
@@ -15507,7 +15860,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B18" s="28" t="n">
         <f aca="false">INDEX(귀신!$J:$J,MATCH($B$3,귀신!$A:$A,0))</f>
@@ -15550,55 +15903,55 @@
     </row>
     <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="G20" s="30" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="H20" s="30" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="I20" s="30" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="J20" s="30" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K20" s="30" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="L20" s="30" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="M20" s="30" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="N20" s="30" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="O20" s="30" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="P20" s="30" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="Q20" s="31" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15618,11 +15971,11 @@
         <v>0.02</v>
       </c>
       <c r="E21" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A21,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A21,상수!$B$12)</f>
         <v>0.053</v>
       </c>
       <c r="F21" s="17" t="n">
-        <f aca="false">1+E21*상수!$B$10</f>
+        <f aca="false">1+E21*상수!$B$11</f>
         <v>1.0265</v>
       </c>
       <c r="G21" s="33" t="n">
@@ -15638,7 +15991,7 @@
         <v>3.97951029738085</v>
       </c>
       <c r="J21" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A21,레벨표!$A:$A,0))+$B$10*A21</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A21,레벨표!$A:$A,0))+$B$10*A21</f>
         <v>114</v>
       </c>
       <c r="K21" s="18" t="n">
@@ -15646,11 +15999,11 @@
         <v>32</v>
       </c>
       <c r="L21" s="34" t="n">
-        <f aca="false">MIN(K21/(K21+상수!$B$3*A21+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K21/(K21+상수!$B$4*A21+상수!$B$5),상수!$B$6)</f>
         <v>0.329896907216495</v>
       </c>
       <c r="M21" s="33" t="n">
-        <f aca="false">$B$16*B21*(1-L21)</f>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A21,레벨표!$A:$A,0))*(1-L21)</f>
         <v>3.35051546391753</v>
       </c>
       <c r="N21" s="33" t="n">
@@ -15687,11 +16040,11 @@
         <v>0.04</v>
       </c>
       <c r="E22" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A22,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A22,상수!$B$12)</f>
         <v>0.056</v>
       </c>
       <c r="F22" s="17" t="n">
-        <f aca="false">1+E22*상수!$B$10</f>
+        <f aca="false">1+E22*상수!$B$11</f>
         <v>1.028</v>
       </c>
       <c r="G22" s="33" t="n">
@@ -15707,7 +16060,7 @@
         <v>3.91476286156191</v>
       </c>
       <c r="J22" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A22,레벨표!$A:$A,0))+$B$10*A22</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A22,레벨표!$A:$A,0))+$B$10*A22</f>
         <v>128</v>
       </c>
       <c r="K22" s="18" t="n">
@@ -15715,20 +16068,20 @@
         <v>44</v>
       </c>
       <c r="L22" s="34" t="n">
-        <f aca="false">MIN(K22/(K22+상수!$B$3*A22+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K22/(K22+상수!$B$4*A22+상수!$B$5),상수!$B$6)</f>
         <v>0.354838709677419</v>
       </c>
       <c r="M22" s="33" t="n">
-        <f aca="false">$B$16*B22*(1-L22)</f>
-        <v>3.61290322580645</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A22,레벨표!$A:$A,0))*(1-L22)</f>
+        <v>3.51612903225806</v>
       </c>
       <c r="N22" s="33" t="n">
         <f aca="false">J22/M22</f>
-        <v>35.4285714285714</v>
+        <v>36.4036697247706</v>
       </c>
       <c r="O22" s="33" t="n">
         <f aca="false">N22*$B$17</f>
-        <v>53.1428571428571</v>
+        <v>54.605504587156</v>
       </c>
       <c r="P22" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -15756,11 +16109,11 @@
         <v>0.06</v>
       </c>
       <c r="E23" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A23,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A23,상수!$B$12)</f>
         <v>0.059</v>
       </c>
       <c r="F23" s="17" t="n">
-        <f aca="false">1+E23*상수!$B$10</f>
+        <f aca="false">1+E23*상수!$B$11</f>
         <v>1.0295</v>
       </c>
       <c r="G23" s="33" t="n">
@@ -15776,7 +16129,7 @@
         <v>3.85250182072341</v>
       </c>
       <c r="J23" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A23,레벨표!$A:$A,0))+$B$10*A23</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A23,레벨표!$A:$A,0))+$B$10*A23</f>
         <v>142</v>
       </c>
       <c r="K23" s="18" t="n">
@@ -15784,20 +16137,20 @@
         <v>56</v>
       </c>
       <c r="L23" s="34" t="n">
-        <f aca="false">MIN(K23/(K23+상수!$B$3*A23+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K23/(K23+상수!$B$4*A23+상수!$B$5),상수!$B$6)</f>
         <v>0.370860927152318</v>
       </c>
       <c r="M23" s="33" t="n">
-        <f aca="false">$B$16*B23*(1-L23)</f>
-        <v>3.94596026490066</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A23,레벨표!$A:$A,0))*(1-L23)</f>
+        <v>3.73740066225166</v>
       </c>
       <c r="N23" s="33" t="n">
         <f aca="false">J23/M23</f>
-        <v>35.9861707841031</v>
+        <v>37.9943208749928</v>
       </c>
       <c r="O23" s="33" t="n">
         <f aca="false">N23*$B$17</f>
-        <v>53.9792561761547</v>
+        <v>56.9914813124892</v>
       </c>
       <c r="P23" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -15825,11 +16178,11 @@
         <v>0.08</v>
       </c>
       <c r="E24" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A24,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A24,상수!$B$12)</f>
         <v>0.062</v>
       </c>
       <c r="F24" s="17" t="n">
-        <f aca="false">1+E24*상수!$B$10</f>
+        <f aca="false">1+E24*상수!$B$11</f>
         <v>1.031</v>
       </c>
       <c r="G24" s="33" t="n">
@@ -15845,7 +16198,7 @@
         <v>3.7925891946317</v>
       </c>
       <c r="J24" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A24,레벨표!$A:$A,0))+$B$10*A24</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A24,레벨표!$A:$A,0))+$B$10*A24</f>
         <v>156</v>
       </c>
       <c r="K24" s="18" t="n">
@@ -15853,20 +16206,20 @@
         <v>68</v>
       </c>
       <c r="L24" s="34" t="n">
-        <f aca="false">MIN(K24/(K24+상수!$B$3*A24+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K24/(K24+상수!$B$4*A24+상수!$B$5),상수!$B$6)</f>
         <v>0.382022471910112</v>
       </c>
       <c r="M24" s="33" t="n">
-        <f aca="false">$B$16*B24*(1-L24)</f>
-        <v>4.34106966292135</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A24,레벨표!$A:$A,0))*(1-L24)</f>
+        <v>4.0014941011236</v>
       </c>
       <c r="N24" s="33" t="n">
         <f aca="false">J24/M24</f>
-        <v>35.9358434932415</v>
+        <v>38.9854379533375</v>
       </c>
       <c r="O24" s="33" t="n">
         <f aca="false">N24*$B$17</f>
-        <v>53.9037652398622</v>
+        <v>58.4781569300063</v>
       </c>
       <c r="P24" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -15894,11 +16247,11 @@
         <v>0.1</v>
       </c>
       <c r="E25" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A25,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A25,상수!$B$12)</f>
         <v>0.065</v>
       </c>
       <c r="F25" s="17" t="n">
-        <f aca="false">1+E25*상수!$B$10</f>
+        <f aca="false">1+E25*상수!$B$11</f>
         <v>1.0325</v>
       </c>
       <c r="G25" s="33" t="n">
@@ -15914,7 +16267,7 @@
         <v>3.73489703859079</v>
       </c>
       <c r="J25" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A25,레벨표!$A:$A,0))+$B$10*A25</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A25,레벨표!$A:$A,0))+$B$10*A25</f>
         <v>170</v>
       </c>
       <c r="K25" s="18" t="n">
@@ -15922,20 +16275,20 @@
         <v>80</v>
       </c>
       <c r="L25" s="34" t="n">
-        <f aca="false">MIN(K25/(K25+상수!$B$3*A25+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K25/(K25+상수!$B$4*A25+상수!$B$5),상수!$B$6)</f>
         <v>0.390243902439024</v>
       </c>
       <c r="M25" s="33" t="n">
-        <f aca="false">$B$16*B25*(1-L25)</f>
-        <v>4.79731512195122</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A25,레벨표!$A:$A,0))*(1-L25)</f>
+        <v>4.3036024695122</v>
       </c>
       <c r="N25" s="33" t="n">
         <f aca="false">J25/M25</f>
-        <v>35.4364880518534</v>
+        <v>39.5017897689953</v>
       </c>
       <c r="O25" s="33" t="n">
         <f aca="false">N25*$B$17</f>
-        <v>53.1547320777801</v>
+        <v>59.252684653493</v>
       </c>
       <c r="P25" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -15963,11 +16316,11 @@
         <v>0.12</v>
       </c>
       <c r="E26" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A26,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A26,상수!$B$12)</f>
         <v>0.068</v>
       </c>
       <c r="F26" s="17" t="n">
-        <f aca="false">1+E26*상수!$B$10</f>
+        <f aca="false">1+E26*상수!$B$11</f>
         <v>1.034</v>
       </c>
       <c r="G26" s="33" t="n">
@@ -15983,7 +16336,7 @@
         <v>3.67930654741436</v>
       </c>
       <c r="J26" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A26,레벨표!$A:$A,0))+$B$10*A26</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A26,레벨표!$A:$A,0))+$B$10*A26</f>
         <v>184</v>
       </c>
       <c r="K26" s="18" t="n">
@@ -15991,20 +16344,20 @@
         <v>92</v>
       </c>
       <c r="L26" s="34" t="n">
-        <f aca="false">MIN(K26/(K26+상수!$B$3*A26+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K26/(K26+상수!$B$4*A26+상수!$B$5),상수!$B$6)</f>
         <v>0.396551724137931</v>
       </c>
       <c r="M26" s="33" t="n">
-        <f aca="false">$B$16*B26*(1-L26)</f>
-        <v>5.31741025103448</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A26,레벨표!$A:$A,0))*(1-L26)</f>
+        <v>4.64239986392242</v>
       </c>
       <c r="N26" s="33" t="n">
         <f aca="false">J26/M26</f>
-        <v>34.603310881308</v>
+        <v>39.6346728832911</v>
       </c>
       <c r="O26" s="33" t="n">
         <f aca="false">N26*$B$17</f>
-        <v>51.9049663219619</v>
+        <v>59.4520093249366</v>
       </c>
       <c r="P26" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -16032,11 +16385,11 @@
         <v>0.14</v>
       </c>
       <c r="E27" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A27,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A27,상수!$B$12)</f>
         <v>0.071</v>
       </c>
       <c r="F27" s="17" t="n">
-        <f aca="false">1+E27*상수!$B$10</f>
+        <f aca="false">1+E27*상수!$B$11</f>
         <v>1.0355</v>
       </c>
       <c r="G27" s="33" t="n">
@@ -16052,7 +16405,7 @@
         <v>3.62570725371655</v>
       </c>
       <c r="J27" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A27,레벨표!$A:$A,0))+$B$10*A27</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A27,레벨표!$A:$A,0))+$B$10*A27</f>
         <v>198</v>
       </c>
       <c r="K27" s="18" t="n">
@@ -16060,20 +16413,20 @@
         <v>104</v>
       </c>
       <c r="L27" s="34" t="n">
-        <f aca="false">MIN(K27/(K27+상수!$B$3*A27+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K27/(K27+상수!$B$4*A27+상수!$B$5),상수!$B$6)</f>
         <v>0.401544401544402</v>
       </c>
       <c r="M27" s="33" t="n">
-        <f aca="false">$B$16*B27*(1-L27)</f>
-        <v>5.90622618153514</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A27,레벨표!$A:$A,0))*(1-L27)</f>
+        <v>5.01834975251651</v>
       </c>
       <c r="N27" s="33" t="n">
         <f aca="false">J27/M27</f>
-        <v>33.5239447176972</v>
+        <v>39.4552013638967</v>
       </c>
       <c r="O27" s="33" t="n">
         <f aca="false">N27*$B$17</f>
-        <v>50.2859170765458</v>
+        <v>59.1828020458451</v>
       </c>
       <c r="P27" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -16101,11 +16454,11 @@
         <v>0.16</v>
       </c>
       <c r="E28" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A28,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A28,상수!$B$12)</f>
         <v>0.074</v>
       </c>
       <c r="F28" s="17" t="n">
-        <f aca="false">1+E28*상수!$B$10</f>
+        <f aca="false">1+E28*상수!$B$11</f>
         <v>1.037</v>
       </c>
       <c r="G28" s="33" t="n">
@@ -16121,7 +16474,7 @@
         <v>3.57399630913816</v>
       </c>
       <c r="J28" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A28,레벨표!$A:$A,0))+$B$10*A28</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A28,레벨표!$A:$A,0))+$B$10*A28</f>
         <v>212</v>
       </c>
       <c r="K28" s="18" t="n">
@@ -16129,20 +16482,20 @@
         <v>116</v>
       </c>
       <c r="L28" s="34" t="n">
-        <f aca="false">MIN(K28/(K28+상수!$B$3*A28+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K28/(K28+상수!$B$4*A28+상수!$B$5),상수!$B$6)</f>
         <v>0.405594405594406</v>
       </c>
       <c r="M28" s="33" t="n">
-        <f aca="false">$B$16*B28*(1-L28)</f>
-        <v>6.57020698005304</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A28,레벨표!$A:$A,0))*(1-L28)</f>
+        <v>5.43298340102863</v>
       </c>
       <c r="N28" s="33" t="n">
         <f aca="false">J28/M28</f>
-        <v>32.2668677933018</v>
+        <v>39.0209180392235</v>
       </c>
       <c r="O28" s="33" t="n">
         <f aca="false">N28*$B$17</f>
-        <v>48.4003016899527</v>
+        <v>58.5313770588353</v>
       </c>
       <c r="P28" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -16170,11 +16523,11 @@
         <v>0.18</v>
       </c>
       <c r="E29" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A29,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A29,상수!$B$12)</f>
         <v>0.077</v>
       </c>
       <c r="F29" s="17" t="n">
-        <f aca="false">1+E29*상수!$B$10</f>
+        <f aca="false">1+E29*상수!$B$11</f>
         <v>1.0385</v>
       </c>
       <c r="G29" s="33" t="n">
@@ -16190,7 +16543,7 @@
         <v>3.52407783866851</v>
       </c>
       <c r="J29" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A29,레벨표!$A:$A,0))+$B$10*A29</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A29,레벨표!$A:$A,0))+$B$10*A29</f>
         <v>226</v>
       </c>
       <c r="K29" s="18" t="n">
@@ -16198,20 +16551,20 @@
         <v>128</v>
       </c>
       <c r="L29" s="34" t="n">
-        <f aca="false">MIN(K29/(K29+상수!$B$3*A29+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K29/(K29+상수!$B$4*A29+상수!$B$5),상수!$B$6)</f>
         <v>0.408945686900958</v>
       </c>
       <c r="M29" s="33" t="n">
-        <f aca="false">$B$16*B29*(1-L29)</f>
-        <v>7.31714357211726</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A29,레벨표!$A:$A,0))*(1-L29)</f>
+        <v>5.88856371745505</v>
       </c>
       <c r="N29" s="33" t="n">
         <f aca="false">J29/M29</f>
-        <v>30.8863694927617</v>
+        <v>38.3794777205322</v>
       </c>
       <c r="O29" s="33" t="n">
         <f aca="false">N29*$B$17</f>
-        <v>46.3295542391426</v>
+        <v>57.5692165807983</v>
       </c>
       <c r="P29" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -16239,11 +16592,11 @@
         <v>0.2</v>
       </c>
       <c r="E30" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A30,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A30,상수!$B$12)</f>
         <v>0.08</v>
       </c>
       <c r="F30" s="17" t="n">
-        <f aca="false">1+E30*상수!$B$10</f>
+        <f aca="false">1+E30*상수!$B$11</f>
         <v>1.04</v>
       </c>
       <c r="G30" s="33" t="n">
@@ -16259,7 +16612,7 @@
         <v>3.47586235953511</v>
       </c>
       <c r="J30" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A30,레벨표!$A:$A,0))+$B$10*A30</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A30,레벨표!$A:$A,0))+$B$10*A30</f>
         <v>240</v>
       </c>
       <c r="K30" s="18" t="n">
@@ -16267,20 +16620,20 @@
         <v>140</v>
       </c>
       <c r="L30" s="34" t="n">
-        <f aca="false">MIN(K30/(K30+상수!$B$3*A30+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K30/(K30+상수!$B$4*A30+상수!$B$5),상수!$B$6)</f>
         <v>0.411764705882353</v>
       </c>
       <c r="M30" s="33" t="n">
-        <f aca="false">$B$16*B30*(1-L30)</f>
-        <v>8.15611399250056</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A30,레벨표!$A:$A,0))*(1-L30)</f>
+        <v>6.38792141012445</v>
       </c>
       <c r="N30" s="33" t="n">
         <f aca="false">J30/M30</f>
-        <v>29.4257780384969</v>
+        <v>37.5709068085302</v>
       </c>
       <c r="O30" s="33" t="n">
         <f aca="false">N30*$B$17</f>
-        <v>44.1386670577453</v>
+        <v>56.3563602127952</v>
       </c>
       <c r="P30" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -16308,11 +16661,11 @@
         <v>0.22</v>
       </c>
       <c r="E31" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A31,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A31,상수!$B$12)</f>
         <v>0.083</v>
       </c>
       <c r="F31" s="17" t="n">
-        <f aca="false">1+E31*상수!$B$10</f>
+        <f aca="false">1+E31*상수!$B$11</f>
         <v>1.0415</v>
       </c>
       <c r="G31" s="33" t="n">
@@ -16328,7 +16681,7 @@
         <v>3.42926625725178</v>
       </c>
       <c r="J31" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A31,레벨표!$A:$A,0))+$B$10*A31</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A31,레벨표!$A:$A,0))+$B$10*A31</f>
         <v>254</v>
       </c>
       <c r="K31" s="18" t="n">
@@ -16336,20 +16689,20 @@
         <v>152</v>
       </c>
       <c r="L31" s="34" t="n">
-        <f aca="false">MIN(K31/(K31+상수!$B$3*A31+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K31/(K31+상수!$B$4*A31+상수!$B$5),상수!$B$6)</f>
         <v>0.4141689373297</v>
       </c>
       <c r="M31" s="33" t="n">
-        <f aca="false">$B$16*B31*(1-L31)</f>
-        <v>9.09751178193468</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A31,레벨표!$A:$A,0))*(1-L31)</f>
+        <v>6.93437588606683</v>
       </c>
       <c r="N31" s="33" t="n">
         <f aca="false">J31/M31</f>
-        <v>27.91972201722</v>
+        <v>36.6291075322812</v>
       </c>
       <c r="O31" s="33" t="n">
         <f aca="false">N31*$B$17</f>
-        <v>41.87958302583</v>
+        <v>54.9436612984218</v>
       </c>
       <c r="P31" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -16377,11 +16730,11 @@
         <v>0.24</v>
       </c>
       <c r="E32" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A32,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A32,상수!$B$12)</f>
         <v>0.086</v>
       </c>
       <c r="F32" s="17" t="n">
-        <f aca="false">1+E32*상수!$B$10</f>
+        <f aca="false">1+E32*상수!$B$11</f>
         <v>1.043</v>
       </c>
       <c r="G32" s="33" t="n">
@@ -16397,7 +16750,7 @@
         <v>3.38421131237176</v>
       </c>
       <c r="J32" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A32,레벨표!$A:$A,0))+$B$10*A32</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A32,레벨표!$A:$A,0))+$B$10*A32</f>
         <v>268</v>
       </c>
       <c r="K32" s="18" t="n">
@@ -16405,20 +16758,20 @@
         <v>164</v>
       </c>
       <c r="L32" s="34" t="n">
-        <f aca="false">MIN(K32/(K32+상수!$B$3*A32+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K32/(K32+상수!$B$4*A32+상수!$B$5),상수!$B$6)</f>
         <v>0.416243654822335</v>
       </c>
       <c r="M32" s="33" t="n">
-        <f aca="false">$B$16*B32*(1-L32)</f>
-        <v>10.1531281531659</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A32,레벨표!$A:$A,0))*(1-L32)</f>
+        <v>7.53170143680513</v>
       </c>
       <c r="N32" s="33" t="n">
         <f aca="false">J32/M32</f>
-        <v>26.3958058991341</v>
+        <v>35.582929335245</v>
       </c>
       <c r="O32" s="33" t="n">
         <f aca="false">N32*$B$17</f>
-        <v>39.5937088487012</v>
+        <v>53.3743940028675</v>
       </c>
       <c r="P32" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -16446,11 +16799,11 @@
         <v>0.26</v>
       </c>
       <c r="E33" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A33,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A33,상수!$B$12)</f>
         <v>0.089</v>
       </c>
       <c r="F33" s="17" t="n">
-        <f aca="false">1+E33*상수!$B$10</f>
+        <f aca="false">1+E33*상수!$B$11</f>
         <v>1.0445</v>
       </c>
       <c r="G33" s="33" t="n">
@@ -16466,7 +16819,7 @@
         <v>3.34062427231193</v>
       </c>
       <c r="J33" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A33,레벨표!$A:$A,0))+$B$10*A33</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A33,레벨표!$A:$A,0))+$B$10*A33</f>
         <v>282</v>
       </c>
       <c r="K33" s="18" t="n">
@@ -16474,20 +16827,20 @@
         <v>176</v>
       </c>
       <c r="L33" s="34" t="n">
-        <f aca="false">MIN(K33/(K33+상수!$B$3*A33+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K33/(K33+상수!$B$4*A33+상수!$B$5),상수!$B$6)</f>
         <v>0.418052256532067</v>
       </c>
       <c r="M33" s="33" t="n">
-        <f aca="false">$B$16*B33*(1-L33)</f>
-        <v>11.3362721873398</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A33,레벨표!$A:$A,0))*(1-L33)</f>
+        <v>8.18411961445142</v>
       </c>
       <c r="N33" s="33" t="n">
         <f aca="false">J33/M33</f>
-        <v>24.8759023548265</v>
+        <v>34.4569743949059</v>
       </c>
       <c r="O33" s="33" t="n">
         <f aca="false">N33*$B$17</f>
-        <v>37.3138535322398</v>
+        <v>51.6854615923589</v>
       </c>
       <c r="P33" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -16515,11 +16868,11 @@
         <v>0.28</v>
       </c>
       <c r="E34" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A34,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A34,상수!$B$12)</f>
         <v>0.092</v>
       </c>
       <c r="F34" s="17" t="n">
-        <f aca="false">1+E34*상수!$B$10</f>
+        <f aca="false">1+E34*상수!$B$11</f>
         <v>1.046</v>
       </c>
       <c r="G34" s="33" t="n">
@@ -16535,7 +16888,7 @@
         <v>3.29843646331861</v>
       </c>
       <c r="J34" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A34,레벨표!$A:$A,0))+$B$10*A34</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A34,레벨표!$A:$A,0))+$B$10*A34</f>
         <v>296</v>
       </c>
       <c r="K34" s="18" t="n">
@@ -16543,20 +16896,20 @@
         <v>188</v>
       </c>
       <c r="L34" s="34" t="n">
-        <f aca="false">MIN(K34/(K34+상수!$B$3*A34+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K34/(K34+상수!$B$4*A34+상수!$B$5),상수!$B$6)</f>
         <v>0.419642857142857</v>
       </c>
       <c r="M34" s="33" t="n">
-        <f aca="false">$B$16*B34*(1-L34)</f>
-        <v>12.6619219757777</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A34,레벨표!$A:$A,0))*(1-L34)</f>
+        <v>8.89630802630885</v>
       </c>
       <c r="N34" s="33" t="n">
         <f aca="false">J34/M34</f>
-        <v>23.3771776959493</v>
+        <v>33.2722292353914</v>
       </c>
       <c r="O34" s="33" t="n">
         <f aca="false">N34*$B$17</f>
-        <v>35.0657665439239</v>
+        <v>49.908343853087</v>
       </c>
       <c r="P34" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -16584,11 +16937,11 @@
         <v>0.3</v>
       </c>
       <c r="E35" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A35,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A35,상수!$B$12)</f>
         <v>0.095</v>
       </c>
       <c r="F35" s="17" t="n">
-        <f aca="false">1+E35*상수!$B$10</f>
+        <f aca="false">1+E35*상수!$B$11</f>
         <v>1.0475</v>
       </c>
       <c r="G35" s="33" t="n">
@@ -16604,7 +16957,7 @@
         <v>3.25758343825184</v>
       </c>
       <c r="J35" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A35,레벨표!$A:$A,0))+$B$10*A35</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A35,레벨표!$A:$A,0))+$B$10*A35</f>
         <v>310</v>
       </c>
       <c r="K35" s="18" t="n">
@@ -16612,20 +16965,20 @@
         <v>200</v>
       </c>
       <c r="L35" s="34" t="n">
-        <f aca="false">MIN(K35/(K35+상수!$B$3*A35+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K35/(K35+상수!$B$4*A35+상수!$B$5),상수!$B$6)</f>
         <v>0.421052631578947</v>
       </c>
       <c r="M35" s="33" t="n">
-        <f aca="false">$B$16*B35*(1-L35)</f>
-        <v>14.1469039830422</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A35,레벨표!$A:$A,0))*(1-L35)</f>
+        <v>9.6734203419997</v>
       </c>
       <c r="N35" s="33" t="n">
         <f aca="false">J35/M35</f>
-        <v>21.9129217510485</v>
+        <v>32.0465759824427</v>
       </c>
       <c r="O35" s="33" t="n">
         <f aca="false">N35*$B$17</f>
-        <v>32.8693826265728</v>
+        <v>48.069863973664</v>
       </c>
       <c r="P35" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -16653,11 +17006,11 @@
         <v>0.32</v>
       </c>
       <c r="E36" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A36,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A36,상수!$B$12)</f>
         <v>0.098</v>
       </c>
       <c r="F36" s="17" t="n">
-        <f aca="false">1+E36*상수!$B$10</f>
+        <f aca="false">1+E36*상수!$B$11</f>
         <v>1.049</v>
       </c>
       <c r="G36" s="33" t="n">
@@ -16673,7 +17026,7 @@
         <v>3.2180046563893</v>
       </c>
       <c r="J36" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A36,레벨표!$A:$A,0))+$B$10*A36</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A36,레벨표!$A:$A,0))+$B$10*A36</f>
         <v>324</v>
       </c>
       <c r="K36" s="18" t="n">
@@ -16681,20 +17034,20 @@
         <v>212</v>
       </c>
       <c r="L36" s="34" t="n">
-        <f aca="false">MIN(K36/(K36+상수!$B$3*A36+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K36/(K36+상수!$B$4*A36+상수!$B$5),상수!$B$6)</f>
         <v>0.422310756972112</v>
       </c>
       <c r="M36" s="33" t="n">
-        <f aca="false">$B$16*B36*(1-L36)</f>
-        <v>15.8101003006429</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A36,레벨표!$A:$A,0))*(1-L36)</f>
+        <v>10.5211146743962</v>
       </c>
       <c r="N36" s="33" t="n">
         <f aca="false">J36/M36</f>
-        <v>20.4932286221376</v>
+        <v>30.7952160989627</v>
       </c>
       <c r="O36" s="33" t="n">
         <f aca="false">N36*$B$17</f>
-        <v>30.7398429332064</v>
+        <v>46.1928241484441</v>
       </c>
       <c r="P36" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -16722,11 +17075,11 @@
         <v>0.34</v>
       </c>
       <c r="E37" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A37,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A37,상수!$B$12)</f>
         <v>0.101</v>
       </c>
       <c r="F37" s="17" t="n">
-        <f aca="false">1+E37*상수!$B$10</f>
+        <f aca="false">1+E37*상수!$B$11</f>
         <v>1.0505</v>
       </c>
       <c r="G37" s="33" t="n">
@@ -16742,7 +17095,7 @@
         <v>3.17964319190448</v>
       </c>
       <c r="J37" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A37,레벨표!$A:$A,0))+$B$10*A37</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A37,레벨표!$A:$A,0))+$B$10*A37</f>
         <v>338</v>
       </c>
       <c r="K37" s="18" t="n">
@@ -16750,20 +17103,20 @@
         <v>224</v>
       </c>
       <c r="L37" s="34" t="n">
-        <f aca="false">MIN(K37/(K37+상수!$B$3*A37+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K37/(K37+상수!$B$4*A37+상수!$B$5),상수!$B$6)</f>
         <v>0.4234404536862</v>
       </c>
       <c r="M37" s="33" t="n">
-        <f aca="false">$B$16*B37*(1-L37)</f>
-        <v>17.6726849089056</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A37,레벨표!$A:$A,0))*(1-L37)</f>
+        <v>11.4455887875531</v>
       </c>
       <c r="N37" s="33" t="n">
         <f aca="false">J37/M37</f>
-        <v>19.1255602497432</v>
+        <v>29.5310277412351</v>
       </c>
       <c r="O37" s="33" t="n">
         <f aca="false">N37*$B$17</f>
-        <v>28.6883403746148</v>
+        <v>44.2965416118527</v>
       </c>
       <c r="P37" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -16791,11 +17144,11 @@
         <v>0.36</v>
       </c>
       <c r="E38" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A38,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A38,상수!$B$12)</f>
         <v>0.104</v>
       </c>
       <c r="F38" s="17" t="n">
-        <f aca="false">1+E38*상수!$B$10</f>
+        <f aca="false">1+E38*상수!$B$11</f>
         <v>1.052</v>
       </c>
       <c r="G38" s="33" t="n">
@@ -16811,7 +17164,7 @@
         <v>3.14244546806749</v>
       </c>
       <c r="J38" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A38,레벨표!$A:$A,0))+$B$10*A38</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A38,레벨표!$A:$A,0))+$B$10*A38</f>
         <v>352</v>
       </c>
       <c r="K38" s="18" t="n">
@@ -16819,20 +17172,20 @@
         <v>236</v>
       </c>
       <c r="L38" s="34" t="n">
-        <f aca="false">MIN(K38/(K38+상수!$B$3*A38+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K38/(K38+상수!$B$4*A38+상수!$B$5),상수!$B$6)</f>
         <v>0.424460431654676</v>
       </c>
       <c r="M38" s="33" t="n">
-        <f aca="false">$B$16*B38*(1-L38)</f>
-        <v>19.75839104579</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A38,레벨표!$A:$A,0))*(1-L38)</f>
+        <v>12.4536213247619</v>
       </c>
       <c r="N38" s="33" t="n">
         <f aca="false">J38/M38</f>
-        <v>17.8152157827143</v>
+        <v>28.2648709817528</v>
       </c>
       <c r="O38" s="33" t="n">
         <f aca="false">N38*$B$17</f>
-        <v>26.7228236740715</v>
+        <v>42.3973064726293</v>
       </c>
       <c r="P38" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -16860,11 +17213,11 @@
         <v>0.38</v>
       </c>
       <c r="E39" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A39,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A39,상수!$B$12)</f>
         <v>0.107</v>
       </c>
       <c r="F39" s="17" t="n">
-        <f aca="false">1+E39*상수!$B$10</f>
+        <f aca="false">1+E39*상수!$B$11</f>
         <v>1.0535</v>
       </c>
       <c r="G39" s="33" t="n">
@@ -16880,7 +17233,7 @@
         <v>3.10636101455866</v>
       </c>
       <c r="J39" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A39,레벨표!$A:$A,0))+$B$10*A39</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A39,레벨표!$A:$A,0))+$B$10*A39</f>
         <v>366</v>
       </c>
       <c r="K39" s="18" t="n">
@@ -16888,20 +17241,20 @@
         <v>248</v>
       </c>
       <c r="L39" s="34" t="n">
-        <f aca="false">MIN(K39/(K39+상수!$B$3*A39+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K39/(K39+상수!$B$4*A39+상수!$B$5),상수!$B$6)</f>
         <v>0.425385934819897</v>
       </c>
       <c r="M39" s="33" t="n">
-        <f aca="false">$B$16*B39*(1-L39)</f>
-        <v>22.0938125328662</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A39,레벨표!$A:$A,0))*(1-L39)</f>
+        <v>13.5526186946058</v>
       </c>
       <c r="N39" s="33" t="n">
         <f aca="false">J39/M39</f>
-        <v>16.565723976138</v>
+        <v>27.0058509168914</v>
       </c>
       <c r="O39" s="33" t="n">
         <f aca="false">N39*$B$17</f>
-        <v>24.848585964207</v>
+        <v>40.5087763753371</v>
       </c>
       <c r="P39" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -16929,11 +17282,11 @@
         <v>0.4</v>
       </c>
       <c r="E40" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A40,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A40,상수!$B$12)</f>
         <v>0.11</v>
       </c>
       <c r="F40" s="17" t="n">
-        <f aca="false">1+E40*상수!$B$10</f>
+        <f aca="false">1+E40*상수!$B$11</f>
         <v>1.055</v>
       </c>
       <c r="G40" s="33" t="n">
@@ -16949,7 +17302,7 @@
         <v>3.07134224558405</v>
       </c>
       <c r="J40" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A40,레벨표!$A:$A,0))+$B$10*A40</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A40,레벨표!$A:$A,0))+$B$10*A40</f>
         <v>380</v>
       </c>
       <c r="K40" s="18" t="n">
@@ -16957,20 +17310,20 @@
         <v>260</v>
       </c>
       <c r="L40" s="34" t="n">
-        <f aca="false">MIN(K40/(K40+상수!$B$3*A40+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K40/(K40+상수!$B$4*A40+상수!$B$5),상수!$B$6)</f>
         <v>0.426229508196721</v>
       </c>
       <c r="M40" s="33" t="n">
-        <f aca="false">$B$16*B40*(1-L40)</f>
-        <v>24.7087425544953</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A40,레벨표!$A:$A,0))*(1-L40)</f>
+        <v>14.7506675343842</v>
       </c>
       <c r="N40" s="33" t="n">
         <f aca="false">J40/M40</f>
-        <v>15.3791719332503</v>
+        <v>25.7615459852384</v>
       </c>
       <c r="O40" s="33" t="n">
         <f aca="false">N40*$B$17</f>
-        <v>23.0687578998754</v>
+        <v>38.6423189778576</v>
       </c>
       <c r="P40" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -16998,11 +17351,11 @@
         <v>0.42</v>
       </c>
       <c r="E41" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A41,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A41,상수!$B$12)</f>
         <v>0.113</v>
       </c>
       <c r="F41" s="17" t="n">
-        <f aca="false">1+E41*상수!$B$10</f>
+        <f aca="false">1+E41*상수!$B$11</f>
         <v>1.0565</v>
       </c>
       <c r="G41" s="33" t="n">
@@ -17018,7 +17371,7 @@
         <v>3.03734425674159</v>
       </c>
       <c r="J41" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A41,레벨표!$A:$A,0))+$B$10*A41</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A41,레벨표!$A:$A,0))+$B$10*A41</f>
         <v>394</v>
       </c>
       <c r="K41" s="18" t="n">
@@ -17026,20 +17379,20 @@
         <v>272</v>
       </c>
       <c r="L41" s="34" t="n">
-        <f aca="false">MIN(K41/(K41+상수!$B$3*A41+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K41/(K41+상수!$B$4*A41+상수!$B$5),상수!$B$6)</f>
         <v>0.427001569858713</v>
       </c>
       <c r="M41" s="33" t="n">
-        <f aca="false">$B$16*B41*(1-L41)</f>
-        <v>27.6365539956464</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A41,레벨표!$A:$A,0))*(1-L41)</f>
+        <v>16.0565928590195</v>
       </c>
       <c r="N41" s="33" t="n">
         <f aca="false">J41/M41</f>
-        <v>14.2564807487238</v>
+        <v>24.5382070442596</v>
       </c>
       <c r="O41" s="33" t="n">
         <f aca="false">N41*$B$17</f>
-        <v>21.3847211230857</v>
+        <v>36.8073105663894</v>
       </c>
       <c r="P41" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -17067,11 +17420,11 @@
         <v>0.44</v>
       </c>
       <c r="E42" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A42,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A42,상수!$B$12)</f>
         <v>0.116</v>
       </c>
       <c r="F42" s="17" t="n">
-        <f aca="false">1+E42*상수!$B$10</f>
+        <f aca="false">1+E42*상수!$B$11</f>
         <v>1.058</v>
       </c>
       <c r="G42" s="33" t="n">
@@ -17087,7 +17440,7 @@
         <v>3.0043246388152</v>
       </c>
       <c r="J42" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A42,레벨표!$A:$A,0))+$B$10*A42</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A42,레벨표!$A:$A,0))+$B$10*A42</f>
         <v>408</v>
       </c>
       <c r="K42" s="18" t="n">
@@ -17095,20 +17448,20 @@
         <v>284</v>
       </c>
       <c r="L42" s="34" t="n">
-        <f aca="false">MIN(K42/(K42+상수!$B$3*A42+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K42/(K42+상수!$B$4*A42+상수!$B$5),상수!$B$6)</f>
         <v>0.427710843373494</v>
       </c>
       <c r="M42" s="33" t="n">
-        <f aca="false">$B$16*B42*(1-L42)</f>
-        <v>30.9146260579655</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A42,레벨표!$A:$A,0))*(1-L42)</f>
+        <v>17.4800221386579</v>
       </c>
       <c r="N42" s="33" t="n">
         <f aca="false">J42/M42</f>
-        <v>13.1976365890693</v>
+        <v>23.3409315367907</v>
       </c>
       <c r="O42" s="33" t="n">
         <f aca="false">N42*$B$17</f>
-        <v>19.7964548836039</v>
+        <v>35.011397305186</v>
       </c>
       <c r="P42" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -17136,11 +17489,11 @@
         <v>0.46</v>
       </c>
       <c r="E43" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A43,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A43,상수!$B$12)</f>
         <v>0.119</v>
       </c>
       <c r="F43" s="17" t="n">
-        <f aca="false">1+E43*상수!$B$10</f>
+        <f aca="false">1+E43*상수!$B$11</f>
         <v>1.0595</v>
       </c>
       <c r="G43" s="33" t="n">
@@ -17156,7 +17509,7 @@
         <v>2.97224330687336</v>
       </c>
       <c r="J43" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A43,레벨표!$A:$A,0))+$B$10*A43</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A43,레벨표!$A:$A,0))+$B$10*A43</f>
         <v>422</v>
       </c>
       <c r="K43" s="18" t="n">
@@ -17164,20 +17517,20 @@
         <v>296</v>
       </c>
       <c r="L43" s="34" t="n">
-        <f aca="false">MIN(K43/(K43+상수!$B$3*A43+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K43/(K43+상수!$B$4*A43+상수!$B$5),상수!$B$6)</f>
         <v>0.428364688856729</v>
       </c>
       <c r="M43" s="33" t="n">
-        <f aca="false">$B$16*B43*(1-L43)</f>
-        <v>34.5848225195414</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A43,레벨표!$A:$A,0))*(1-L43)</f>
+        <v>19.0314556520476</v>
       </c>
       <c r="N43" s="33" t="n">
         <f aca="false">J43/M43</f>
-        <v>12.201884215585</v>
+        <v>22.1738162185507</v>
       </c>
       <c r="O43" s="33" t="n">
         <f aca="false">N43*$B$17</f>
-        <v>18.3028263233775</v>
+        <v>33.260724327826</v>
       </c>
       <c r="P43" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -17205,11 +17558,11 @@
         <v>0.48</v>
       </c>
       <c r="E44" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A44,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A44,상수!$B$12)</f>
         <v>0.122</v>
       </c>
       <c r="F44" s="17" t="n">
-        <f aca="false">1+E44*상수!$B$10</f>
+        <f aca="false">1+E44*상수!$B$11</f>
         <v>1.061</v>
       </c>
       <c r="G44" s="33" t="n">
@@ -17225,7 +17578,7 @@
         <v>2.94106234322471</v>
       </c>
       <c r="J44" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A44,레벨표!$A:$A,0))+$B$10*A44</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A44,레벨표!$A:$A,0))+$B$10*A44</f>
         <v>436</v>
       </c>
       <c r="K44" s="18" t="n">
@@ -17233,20 +17586,20 @@
         <v>308</v>
       </c>
       <c r="L44" s="34" t="n">
-        <f aca="false">MIN(K44/(K44+상수!$B$3*A44+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K44/(K44+상수!$B$4*A44+상수!$B$5),상수!$B$6)</f>
         <v>0.428969359331476</v>
       </c>
       <c r="M44" s="33" t="n">
-        <f aca="false">$B$16*B44*(1-L44)</f>
-        <v>38.6940277006193</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A44,레벨표!$A:$A,0))*(1-L44)</f>
+        <v>20.7223435487181</v>
       </c>
       <c r="N44" s="33" t="n">
         <f aca="false">J44/M44</f>
-        <v>11.2678887649895</v>
+        <v>21.040091289625</v>
       </c>
       <c r="O44" s="33" t="n">
         <f aca="false">N44*$B$17</f>
-        <v>16.9018331474842</v>
+        <v>31.5601369344375</v>
       </c>
       <c r="P44" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -17274,11 +17627,11 @@
         <v>0.5</v>
       </c>
       <c r="E45" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A45,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A45,상수!$B$12)</f>
         <v>0.125</v>
       </c>
       <c r="F45" s="17" t="n">
-        <f aca="false">1+E45*상수!$B$10</f>
+        <f aca="false">1+E45*상수!$B$11</f>
         <v>1.0625</v>
       </c>
       <c r="G45" s="33" t="n">
@@ -17294,7 +17647,7 @@
         <v>2.91074585293712</v>
       </c>
       <c r="J45" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A45,레벨표!$A:$A,0))+$B$10*A45</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A45,레벨표!$A:$A,0))+$B$10*A45</f>
         <v>450</v>
       </c>
       <c r="K45" s="18" t="n">
@@ -17302,20 +17655,20 @@
         <v>320</v>
       </c>
       <c r="L45" s="34" t="n">
-        <f aca="false">MIN(K45/(K45+상수!$B$3*A45+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K45/(K45+상수!$B$4*A45+상수!$B$5),상수!$B$6)</f>
         <v>0.429530201342282</v>
       </c>
       <c r="M45" s="33" t="n">
-        <f aca="false">$B$16*B45*(1-L45)</f>
-        <v>43.2947469608291</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A45,레벨표!$A:$A,0))*(1-L45)</f>
+        <v>22.565170129126</v>
       </c>
       <c r="N45" s="33" t="n">
         <f aca="false">J45/M45</f>
-        <v>10.393870656113</v>
+        <v>19.9422383002183</v>
       </c>
       <c r="O45" s="33" t="n">
         <f aca="false">N45*$B$17</f>
-        <v>15.5908059841695</v>
+        <v>29.9133574503275</v>
       </c>
       <c r="P45" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -17343,11 +17696,11 @@
         <v>0.52</v>
       </c>
       <c r="E46" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A46,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A46,상수!$B$12)</f>
         <v>0.128</v>
       </c>
       <c r="F46" s="17" t="n">
-        <f aca="false">1+E46*상수!$B$10</f>
+        <f aca="false">1+E46*상수!$B$11</f>
         <v>1.064</v>
       </c>
       <c r="G46" s="33" t="n">
@@ -17363,7 +17716,7 @@
         <v>2.88125983076316</v>
       </c>
       <c r="J46" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A46,레벨표!$A:$A,0))+$B$10*A46</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A46,레벨표!$A:$A,0))+$B$10*A46</f>
         <v>464</v>
       </c>
       <c r="K46" s="18" t="n">
@@ -17371,20 +17724,20 @@
         <v>332</v>
       </c>
       <c r="L46" s="34" t="n">
-        <f aca="false">MIN(K46/(K46+상수!$B$3*A46+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K46/(K46+상수!$B$4*A46+상수!$B$5),상수!$B$6)</f>
         <v>0.430051813471503</v>
       </c>
       <c r="M46" s="33" t="n">
-        <f aca="false">$B$16*B46*(1-L46)</f>
-        <v>48.4457793971684</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A46,레벨표!$A:$A,0))*(1-L46)</f>
+        <v>24.5735459234288</v>
       </c>
       <c r="N46" s="33" t="n">
         <f aca="false">J46/M46</f>
-        <v>9.57771772430439</v>
+        <v>18.8820938356159</v>
       </c>
       <c r="O46" s="33" t="n">
         <f aca="false">N46*$B$17</f>
-        <v>14.3665765864566</v>
+        <v>28.3231407534239</v>
       </c>
       <c r="P46" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -17412,11 +17765,11 @@
         <v>0.54</v>
       </c>
       <c r="E47" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A47,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A47,상수!$B$12)</f>
         <v>0.131</v>
       </c>
       <c r="F47" s="17" t="n">
-        <f aca="false">1+E47*상수!$B$10</f>
+        <f aca="false">1+E47*상수!$B$11</f>
         <v>1.0655</v>
       </c>
       <c r="G47" s="33" t="n">
@@ -17432,7 +17785,7 @@
         <v>2.85257203843506</v>
       </c>
       <c r="J47" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A47,레벨표!$A:$A,0))+$B$10*A47</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A47,레벨표!$A:$A,0))+$B$10*A47</f>
         <v>478</v>
       </c>
       <c r="K47" s="18" t="n">
@@ -17440,20 +17793,20 @@
         <v>344</v>
       </c>
       <c r="L47" s="34" t="n">
-        <f aca="false">MIN(K47/(K47+상수!$B$3*A47+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K47/(K47+상수!$B$4*A47+상수!$B$5),상수!$B$6)</f>
         <v>0.430538172715895</v>
       </c>
       <c r="M47" s="33" t="n">
-        <f aca="false">$B$16*B47*(1-L47)</f>
-        <v>54.2129713493438</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A47,레벨표!$A:$A,0))*(1-L47)</f>
+        <v>26.7623082198183</v>
       </c>
       <c r="N47" s="33" t="n">
         <f aca="false">J47/M47</f>
-        <v>8.81707805535706</v>
+        <v>17.860940695916</v>
       </c>
       <c r="O47" s="33" t="n">
         <f aca="false">N47*$B$17</f>
-        <v>13.2256170830356</v>
+        <v>26.791411043874</v>
       </c>
       <c r="P47" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -17481,11 +17834,11 @@
         <v>0.56</v>
       </c>
       <c r="E48" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A48,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A48,상수!$B$12)</f>
         <v>0.134</v>
       </c>
       <c r="F48" s="17" t="n">
-        <f aca="false">1+E48*상수!$B$10</f>
+        <f aca="false">1+E48*상수!$B$11</f>
         <v>1.067</v>
       </c>
       <c r="G48" s="33" t="n">
@@ -17501,7 +17854,7 @@
         <v>2.82465189139851</v>
       </c>
       <c r="J48" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A48,레벨표!$A:$A,0))+$B$10*A48</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A48,레벨표!$A:$A,0))+$B$10*A48</f>
         <v>492</v>
       </c>
       <c r="K48" s="18" t="n">
@@ -17509,20 +17862,20 @@
         <v>356</v>
       </c>
       <c r="L48" s="34" t="n">
-        <f aca="false">MIN(K48/(K48+상수!$B$3*A48+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K48/(K48+상수!$B$4*A48+상수!$B$5),상수!$B$6)</f>
         <v>0.430992736077482</v>
       </c>
       <c r="M48" s="33" t="n">
-        <f aca="false">$B$16*B48*(1-L48)</f>
-        <v>60.6700603637744</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A48,레벨표!$A:$A,0))*(1-L48)</f>
+        <v>29.1476307647323</v>
       </c>
       <c r="N48" s="33" t="n">
         <f aca="false">J48/M48</f>
-        <v>8.10943646750958</v>
+        <v>16.8795880519835</v>
       </c>
       <c r="O48" s="33" t="n">
         <f aca="false">N48*$B$17</f>
-        <v>12.1641547012644</v>
+        <v>25.3193820779752</v>
       </c>
       <c r="P48" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -17550,11 +17903,11 @@
         <v>0.58</v>
       </c>
       <c r="E49" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A49,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A49,상수!$B$12)</f>
         <v>0.137</v>
       </c>
       <c r="F49" s="17" t="n">
-        <f aca="false">1+E49*상수!$B$10</f>
+        <f aca="false">1+E49*상수!$B$11</f>
         <v>1.0685</v>
       </c>
       <c r="G49" s="33" t="n">
@@ -17570,7 +17923,7 @@
         <v>2.79747035414894</v>
       </c>
       <c r="J49" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A49,레벨표!$A:$A,0))+$B$10*A49</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A49,레벨표!$A:$A,0))+$B$10*A49</f>
         <v>506</v>
       </c>
       <c r="K49" s="18" t="n">
@@ -17578,20 +17931,20 @@
         <v>368</v>
       </c>
       <c r="L49" s="34" t="n">
-        <f aca="false">MIN(K49/(K49+상수!$B$3*A49+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K49/(K49+상수!$B$4*A49+상수!$B$5),상수!$B$6)</f>
         <v>0.431418522860492</v>
       </c>
       <c r="M49" s="33" t="n">
-        <f aca="false">$B$16*B49*(1-L49)</f>
-        <v>67.8996204340413</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A49,레벨표!$A:$A,0))*(1-L49)</f>
+        <v>31.7471434314902</v>
       </c>
       <c r="N49" s="33" t="n">
         <f aca="false">J49/M49</f>
-        <v>7.45217715158711</v>
+        <v>15.9384418661773</v>
       </c>
       <c r="O49" s="33" t="n">
         <f aca="false">N49*$B$17</f>
-        <v>11.1782657273807</v>
+        <v>23.907662799266</v>
       </c>
       <c r="P49" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -17619,11 +17972,11 @@
         <v>0.6</v>
       </c>
       <c r="E50" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A50,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A50,상수!$B$12)</f>
         <v>0.14</v>
       </c>
       <c r="F50" s="17" t="n">
-        <f aca="false">1+E50*상수!$B$10</f>
+        <f aca="false">1+E50*상수!$B$11</f>
         <v>1.07</v>
       </c>
       <c r="G50" s="33" t="n">
@@ -17639,7 +17992,7 @@
         <v>2.77099984341764</v>
       </c>
       <c r="J50" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A50,레벨표!$A:$A,0))+$B$10*A50</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A50,레벨표!$A:$A,0))+$B$10*A50</f>
         <v>520</v>
       </c>
       <c r="K50" s="18" t="n">
@@ -17647,20 +18000,20 @@
         <v>380</v>
       </c>
       <c r="L50" s="34" t="n">
-        <f aca="false">MIN(K50/(K50+상수!$B$3*A50+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K50/(K50+상수!$B$4*A50+상수!$B$5),상수!$B$6)</f>
         <v>0.431818181818182</v>
       </c>
       <c r="M50" s="33" t="n">
-        <f aca="false">$B$16*B50*(1-L50)</f>
-        <v>75.9941206394865</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A50,레벨표!$A:$A,0))*(1-L50)</f>
+        <v>34.5800627323063</v>
       </c>
       <c r="N50" s="33" t="n">
         <f aca="false">J50/M50</f>
-        <v>6.84263460941751</v>
+        <v>15.0375667049959</v>
       </c>
       <c r="O50" s="33" t="n">
         <f aca="false">N50*$B$17</f>
-        <v>10.2639519141263</v>
+        <v>22.5563500574939</v>
       </c>
       <c r="P50" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -17688,11 +18041,11 @@
         <v>0.62</v>
       </c>
       <c r="E51" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A51,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A51,상수!$B$12)</f>
         <v>0.143</v>
       </c>
       <c r="F51" s="17" t="n">
-        <f aca="false">1+E51*상수!$B$10</f>
+        <f aca="false">1+E51*상수!$B$11</f>
         <v>1.0715</v>
       </c>
       <c r="G51" s="33" t="n">
@@ -17708,7 +18061,7 @@
         <v>2.7452141385292</v>
       </c>
       <c r="J51" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A51,레벨표!$A:$A,0))+$B$10*A51</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A51,레벨표!$A:$A,0))+$B$10*A51</f>
         <v>534</v>
       </c>
       <c r="K51" s="18" t="n">
@@ -17716,20 +18069,20 @@
         <v>392</v>
       </c>
       <c r="L51" s="34" t="n">
-        <f aca="false">MIN(K51/(K51+상수!$B$3*A51+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K51/(K51+상수!$B$4*A51+상수!$B$5),상수!$B$6)</f>
         <v>0.432194046306505</v>
       </c>
       <c r="M51" s="33" t="n">
-        <f aca="false">$B$16*B51*(1-L51)</f>
-        <v>85.057110762234</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A51,레벨표!$A:$A,0))*(1-L51)</f>
+        <v>37.6673341323187</v>
       </c>
       <c r="N51" s="33" t="n">
         <f aca="false">J51/M51</f>
-        <v>6.27813471695185</v>
+        <v>14.1767399339744</v>
       </c>
       <c r="O51" s="33" t="n">
         <f aca="false">N51*$B$17</f>
-        <v>9.41720207542777</v>
+        <v>21.2651099009616</v>
       </c>
       <c r="P51" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -17757,11 +18110,11 @@
         <v>0.64</v>
       </c>
       <c r="E52" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A52,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A52,상수!$B$12)</f>
         <v>0.146</v>
       </c>
       <c r="F52" s="17" t="n">
-        <f aca="false">1+E52*상수!$B$10</f>
+        <f aca="false">1+E52*상수!$B$11</f>
         <v>1.073</v>
       </c>
       <c r="G52" s="33" t="n">
@@ -17777,7 +18130,7 @@
         <v>2.72008829831832</v>
       </c>
       <c r="J52" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A52,레벨표!$A:$A,0))+$B$10*A52</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A52,레벨표!$A:$A,0))+$B$10*A52</f>
         <v>548</v>
       </c>
       <c r="K52" s="18" t="n">
@@ -17785,20 +18138,20 @@
         <v>404</v>
       </c>
       <c r="L52" s="34" t="n">
-        <f aca="false">MIN(K52/(K52+상수!$B$3*A52+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K52/(K52+상수!$B$4*A52+상수!$B$5),상수!$B$6)</f>
         <v>0.43254817987152</v>
       </c>
       <c r="M52" s="33" t="n">
-        <f aca="false">$B$16*B52*(1-L52)</f>
-        <v>95.2045490951438</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A52,레벨표!$A:$A,0))*(1-L52)</f>
+        <v>41.0317872142245</v>
       </c>
       <c r="N52" s="33" t="n">
         <f aca="false">J52/M52</f>
-        <v>5.7560274714641</v>
+        <v>13.3554991679725</v>
       </c>
       <c r="O52" s="33" t="n">
         <f aca="false">N52*$B$17</f>
-        <v>8.63404120719614</v>
+        <v>20.0332487519587</v>
       </c>
       <c r="P52" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -17826,11 +18179,11 @@
         <v>0.66</v>
       </c>
       <c r="E53" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A53,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A53,상수!$B$12)</f>
         <v>0.149</v>
       </c>
       <c r="F53" s="17" t="n">
-        <f aca="false">1+E53*상수!$B$10</f>
+        <f aca="false">1+E53*상수!$B$11</f>
         <v>1.0745</v>
       </c>
       <c r="G53" s="33" t="n">
@@ -17846,7 +18199,7 @@
         <v>2.69559858405242</v>
       </c>
       <c r="J53" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A53,레벨표!$A:$A,0))+$B$10*A53</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A53,레벨표!$A:$A,0))+$B$10*A53</f>
         <v>562</v>
       </c>
       <c r="K53" s="18" t="n">
@@ -17854,20 +18207,20 @@
         <v>416</v>
       </c>
       <c r="L53" s="34" t="n">
-        <f aca="false">MIN(K53/(K53+상수!$B$3*A53+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K53/(K53+상수!$B$4*A53+상수!$B$5),상수!$B$6)</f>
         <v>0.432882414151925</v>
       </c>
       <c r="M53" s="33" t="n">
-        <f aca="false">$B$16*B53*(1-L53)</f>
-        <v>106.566289480316</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A53,레벨표!$A:$A,0))*(1-L53)</f>
+        <v>44.6983048392316</v>
       </c>
       <c r="N53" s="33" t="n">
         <f aca="false">J53/M53</f>
-        <v>5.27371275419897</v>
+        <v>12.5731837487209</v>
       </c>
       <c r="O53" s="33" t="n">
         <f aca="false">N53*$B$17</f>
-        <v>7.91056913129845</v>
+        <v>18.8597756230814</v>
       </c>
       <c r="P53" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -17895,11 +18248,11 @@
         <v>0.68</v>
       </c>
       <c r="E54" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A54,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A54,상수!$B$12)</f>
         <v>0.152</v>
       </c>
       <c r="F54" s="17" t="n">
-        <f aca="false">1+E54*상수!$B$10</f>
+        <f aca="false">1+E54*상수!$B$11</f>
         <v>1.076</v>
       </c>
       <c r="G54" s="33" t="n">
@@ -17915,7 +18268,7 @@
         <v>2.67172238786003</v>
       </c>
       <c r="J54" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A54,레벨표!$A:$A,0))+$B$10*A54</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A54,레벨표!$A:$A,0))+$B$10*A54</f>
         <v>576</v>
       </c>
       <c r="K54" s="18" t="n">
@@ -17923,20 +18276,20 @@
         <v>428</v>
       </c>
       <c r="L54" s="34" t="n">
-        <f aca="false">MIN(K54/(K54+상수!$B$3*A54+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K54/(K54+상수!$B$4*A54+상수!$B$5),상수!$B$6)</f>
         <v>0.433198380566802</v>
       </c>
       <c r="M54" s="33" t="n">
-        <f aca="false">$B$16*B54*(1-L54)</f>
-        <v>119.287746663325</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A54,레벨표!$A:$A,0))*(1-L54)</f>
+        <v>48.6940075552244</v>
       </c>
       <c r="N54" s="33" t="n">
         <f aca="false">J54/M54</f>
-        <v>4.82866024475833</v>
+        <v>11.828970933369</v>
       </c>
       <c r="O54" s="33" t="n">
         <f aca="false">N54*$B$17</f>
-        <v>7.2429903671375</v>
+        <v>17.7434564000535</v>
       </c>
       <c r="P54" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -17964,11 +18317,11 @@
         <v>0.7</v>
       </c>
       <c r="E55" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A55,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A55,상수!$B$12)</f>
         <v>0.155</v>
       </c>
       <c r="F55" s="17" t="n">
-        <f aca="false">1+E55*상수!$B$10</f>
+        <f aca="false">1+E55*상수!$B$11</f>
         <v>1.0775</v>
       </c>
       <c r="G55" s="33" t="n">
@@ -17984,7 +18337,7 @@
         <v>2.64843816621109</v>
       </c>
       <c r="J55" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A55,레벨표!$A:$A,0))+$B$10*A55</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A55,레벨표!$A:$A,0))+$B$10*A55</f>
         <v>590</v>
       </c>
       <c r="K55" s="18" t="n">
@@ -17992,20 +18345,20 @@
         <v>440</v>
       </c>
       <c r="L55" s="34" t="n">
-        <f aca="false">MIN(K55/(K55+상수!$B$3*A55+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K55/(K55+상수!$B$4*A55+상수!$B$5),상수!$B$6)</f>
         <v>0.433497536945813</v>
       </c>
       <c r="M55" s="33" t="n">
-        <f aca="false">$B$16*B55*(1-L55)</f>
-        <v>133.531761338788</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A55,레벨표!$A:$A,0))*(1-L55)</f>
+        <v>53.0484546171957</v>
       </c>
       <c r="N55" s="33" t="n">
         <f aca="false">J55/M55</f>
-        <v>4.41842445635905</v>
+        <v>11.1219074006493</v>
       </c>
       <c r="O55" s="33" t="n">
         <f aca="false">N55*$B$17</f>
-        <v>6.62763668453857</v>
+        <v>16.682861100974</v>
       </c>
       <c r="P55" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -18033,11 +18386,11 @@
         <v>0.72</v>
       </c>
       <c r="E56" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A56,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A56,상수!$B$12)</f>
         <v>0.158</v>
       </c>
       <c r="F56" s="17" t="n">
-        <f aca="false">1+E56*상수!$B$10</f>
+        <f aca="false">1+E56*상수!$B$11</f>
         <v>1.079</v>
       </c>
       <c r="G56" s="33" t="n">
@@ -18053,7 +18406,7 @@
         <v>2.62572537803831</v>
       </c>
       <c r="J56" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A56,레벨표!$A:$A,0))+$B$10*A56</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A56,레벨표!$A:$A,0))+$B$10*A56</f>
         <v>604</v>
       </c>
       <c r="K56" s="18" t="n">
@@ -18061,20 +18414,20 @@
         <v>452</v>
       </c>
       <c r="L56" s="34" t="n">
-        <f aca="false">MIN(K56/(K56+상수!$B$3*A56+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K56/(K56+상수!$B$4*A56+상수!$B$5),상수!$B$6)</f>
         <v>0.433781190019194</v>
       </c>
       <c r="M56" s="33" t="n">
-        <f aca="false">$B$16*B56*(1-L56)</f>
-        <v>149.480688827608</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A56,레벨표!$A:$A,0))*(1-L56)</f>
+        <v>57.7938631090434</v>
       </c>
       <c r="N56" s="33" t="n">
         <f aca="false">J56/M56</f>
-        <v>4.04065571772002</v>
+        <v>10.450936613467</v>
       </c>
       <c r="O56" s="33" t="n">
         <f aca="false">N56*$B$17</f>
-        <v>6.06098357658003</v>
+        <v>15.6764049202005</v>
       </c>
       <c r="P56" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -18102,11 +18455,11 @@
         <v>0.74</v>
       </c>
       <c r="E57" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A57,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A57,상수!$B$12)</f>
         <v>0.161</v>
       </c>
       <c r="F57" s="17" t="n">
-        <f aca="false">1+E57*상수!$B$10</f>
+        <f aca="false">1+E57*상수!$B$11</f>
         <v>1.0805</v>
       </c>
       <c r="G57" s="33" t="n">
@@ -18122,7 +18475,7 @@
         <v>2.60356442712597</v>
       </c>
       <c r="J57" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A57,레벨표!$A:$A,0))+$B$10*A57</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A57,레벨표!$A:$A,0))+$B$10*A57</f>
         <v>618</v>
       </c>
       <c r="K57" s="18" t="n">
@@ -18130,20 +18483,20 @@
         <v>464</v>
       </c>
       <c r="L57" s="34" t="n">
-        <f aca="false">MIN(K57/(K57+상수!$B$3*A57+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K57/(K57+상수!$B$4*A57+상수!$B$5),상수!$B$6)</f>
         <v>0.434050514499532</v>
       </c>
       <c r="M57" s="33" t="n">
-        <f aca="false">$B$16*B57*(1-L57)</f>
-        <v>167.338738198331</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A57,레벨표!$A:$A,0))*(1-L57)</f>
+        <v>62.9653467907652</v>
       </c>
       <c r="N57" s="33" t="n">
         <f aca="false">J57/M57</f>
-        <v>3.69310780428821</v>
+        <v>9.81492251688255</v>
       </c>
       <c r="O57" s="33" t="n">
         <f aca="false">N57*$B$17</f>
-        <v>5.53966170643232</v>
+        <v>14.7223837753238</v>
       </c>
       <c r="P57" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -18171,11 +18524,11 @@
         <v>0.76</v>
       </c>
       <c r="E58" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A58,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A58,상수!$B$12)</f>
         <v>0.164</v>
       </c>
       <c r="F58" s="17" t="n">
-        <f aca="false">1+E58*상수!$B$10</f>
+        <f aca="false">1+E58*상수!$B$11</f>
         <v>1.082</v>
       </c>
       <c r="G58" s="33" t="n">
@@ -18191,7 +18544,7 @@
         <v>2.58193660842674</v>
       </c>
       <c r="J58" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A58,레벨표!$A:$A,0))+$B$10*A58</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A58,레벨표!$A:$A,0))+$B$10*A58</f>
         <v>632</v>
       </c>
       <c r="K58" s="18" t="n">
@@ -18199,20 +18552,20 @@
         <v>476</v>
       </c>
       <c r="L58" s="34" t="n">
-        <f aca="false">MIN(K58/(K58+상수!$B$3*A58+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K58/(K58+상수!$B$4*A58+상수!$B$5),상수!$B$6)</f>
         <v>0.434306569343066</v>
       </c>
       <c r="M58" s="33" t="n">
-        <f aca="false">$B$16*B58*(1-L58)</f>
-        <v>187.334591861406</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A58,레벨표!$A:$A,0))*(1-L58)</f>
+        <v>68.6011764419405</v>
       </c>
       <c r="N58" s="33" t="n">
         <f aca="false">J58/M58</f>
-        <v>3.37364281588511</v>
+        <v>9.21266999750191</v>
       </c>
       <c r="O58" s="33" t="n">
         <f aca="false">N58*$B$17</f>
-        <v>5.06046422382766</v>
+        <v>13.8190049962529</v>
       </c>
       <c r="P58" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -18240,11 +18593,11 @@
         <v>0.78</v>
       </c>
       <c r="E59" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A59,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A59,상수!$B$12)</f>
         <v>0.167</v>
       </c>
       <c r="F59" s="17" t="n">
-        <f aca="false">1+E59*상수!$B$10</f>
+        <f aca="false">1+E59*상수!$B$11</f>
         <v>1.0835</v>
       </c>
       <c r="G59" s="33" t="n">
@@ -18260,7 +18613,7 @@
         <v>2.56082405799768</v>
       </c>
       <c r="J59" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A59,레벨표!$A:$A,0))+$B$10*A59</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A59,레벨표!$A:$A,0))+$B$10*A59</f>
         <v>646</v>
       </c>
       <c r="K59" s="18" t="n">
@@ -18268,20 +18621,20 @@
         <v>488</v>
       </c>
       <c r="L59" s="34" t="n">
-        <f aca="false">MIN(K59/(K59+상수!$B$3*A59+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K59/(K59+상수!$B$4*A59+상수!$B$5),상수!$B$6)</f>
         <v>0.434550311665183</v>
       </c>
       <c r="M59" s="33" t="n">
-        <f aca="false">$B$16*B59*(1-L59)</f>
-        <v>209.724339267066</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A59,레벨표!$A:$A,0))*(1-L59)</f>
+        <v>74.7430636322938</v>
       </c>
       <c r="N59" s="33" t="n">
         <f aca="false">J59/M59</f>
-        <v>3.08023380718522</v>
+        <v>8.64294248330606</v>
       </c>
       <c r="O59" s="33" t="n">
         <f aca="false">N59*$B$17</f>
-        <v>4.62035071077783</v>
+        <v>12.9644137249591</v>
       </c>
       <c r="P59" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -18309,11 +18662,11 @@
         <v>0.8</v>
       </c>
       <c r="E60" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A60,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A60,상수!$B$12)</f>
         <v>0.17</v>
       </c>
       <c r="F60" s="17" t="n">
-        <f aca="false">1+E60*상수!$B$10</f>
+        <f aca="false">1+E60*상수!$B$11</f>
         <v>1.085</v>
       </c>
       <c r="G60" s="33" t="n">
@@ -18329,7 +18682,7 @@
         <v>2.54020970627376</v>
       </c>
       <c r="J60" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A60,레벨표!$A:$A,0))+$B$10*A60</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A60,레벨표!$A:$A,0))+$B$10*A60</f>
         <v>660</v>
       </c>
       <c r="K60" s="18" t="n">
@@ -18337,20 +18690,20 @@
         <v>500</v>
       </c>
       <c r="L60" s="34" t="n">
-        <f aca="false">MIN(K60/(K60+상수!$B$3*A60+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K60/(K60+상수!$B$4*A60+상수!$B$5),상수!$B$6)</f>
         <v>0.434782608695652</v>
       </c>
       <c r="M60" s="33" t="n">
-        <f aca="false">$B$16*B60*(1-L60)</f>
-        <v>234.794762371454</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A60,레벨표!$A:$A,0))*(1-L60)</f>
+        <v>81.4364700243043</v>
       </c>
       <c r="N60" s="33" t="n">
         <f aca="false">J60/M60</f>
-        <v>2.81096559963231</v>
+        <v>8.10447702120471</v>
       </c>
       <c r="O60" s="33" t="n">
         <f aca="false">N60*$B$17</f>
-        <v>4.21644839944846</v>
+        <v>12.1567155318071</v>
       </c>
       <c r="P60" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -18378,11 +18731,11 @@
         <v>0.82</v>
       </c>
       <c r="E61" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A61,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A61,상수!$B$12)</f>
         <v>0.173</v>
       </c>
       <c r="F61" s="17" t="n">
-        <f aca="false">1+E61*상수!$B$10</f>
+        <f aca="false">1+E61*상수!$B$11</f>
         <v>1.0865</v>
       </c>
       <c r="G61" s="33" t="n">
@@ -18398,7 +18751,7 @@
         <v>2.52007723442228</v>
       </c>
       <c r="J61" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A61,레벨표!$A:$A,0))+$B$10*A61</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A61,레벨표!$A:$A,0))+$B$10*A61</f>
         <v>674</v>
       </c>
       <c r="K61" s="18" t="n">
@@ -18406,20 +18759,20 @@
         <v>512</v>
       </c>
       <c r="L61" s="34" t="n">
-        <f aca="false">MIN(K61/(K61+상수!$B$3*A61+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K61/(K61+상수!$B$4*A61+상수!$B$5),상수!$B$6)</f>
         <v>0.43500424808836</v>
       </c>
       <c r="M61" s="33" t="n">
-        <f aca="false">$B$16*B61*(1-L61)</f>
-        <v>262.867015053131</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A61,레벨표!$A:$A,0))*(1-L61)</f>
+        <v>88.7309445025613</v>
       </c>
       <c r="N61" s="33" t="n">
         <f aca="false">J61/M61</f>
-        <v>2.56403413666705</v>
+        <v>7.59599713243833</v>
       </c>
       <c r="O61" s="33" t="n">
         <f aca="false">N61*$B$17</f>
-        <v>3.84605120500058</v>
+        <v>11.3939956986575</v>
       </c>
       <c r="P61" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -18447,11 +18800,11 @@
         <v>0.84</v>
       </c>
       <c r="E62" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A62,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A62,상수!$B$12)</f>
         <v>0.176</v>
       </c>
       <c r="F62" s="17" t="n">
-        <f aca="false">1+E62*상수!$B$10</f>
+        <f aca="false">1+E62*상수!$B$11</f>
         <v>1.088</v>
       </c>
       <c r="G62" s="33" t="n">
@@ -18467,7 +18820,7 @@
         <v>2.5004110335438</v>
       </c>
       <c r="J62" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A62,레벨표!$A:$A,0))+$B$10*A62</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A62,레벨표!$A:$A,0))+$B$10*A62</f>
         <v>688</v>
       </c>
       <c r="K62" s="18" t="n">
@@ -18475,20 +18828,20 @@
         <v>524</v>
       </c>
       <c r="L62" s="34" t="n">
-        <f aca="false">MIN(K62/(K62+상수!$B$3*A62+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K62/(K62+상수!$B$4*A62+상수!$B$5),상수!$B$6)</f>
         <v>0.435215946843854</v>
       </c>
       <c r="M62" s="33" t="n">
-        <f aca="false">$B$16*B62*(1-L62)</f>
-        <v>294.300743721524</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A62,레벨표!$A:$A,0))*(1-L62)</f>
+        <v>96.6804906312995</v>
       </c>
       <c r="N62" s="33" t="n">
         <f aca="false">J62/M62</f>
-        <v>2.33774468694856</v>
+        <v>7.1162237128456</v>
       </c>
       <c r="O62" s="33" t="n">
         <f aca="false">N62*$B$17</f>
-        <v>3.50661703042283</v>
+        <v>10.6743355692684</v>
       </c>
       <c r="P62" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -18516,11 +18869,11 @@
         <v>0.86</v>
       </c>
       <c r="E63" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A63,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A63,상수!$B$12)</f>
         <v>0.179</v>
       </c>
       <c r="F63" s="17" t="n">
-        <f aca="false">1+E63*상수!$B$10</f>
+        <f aca="false">1+E63*상수!$B$11</f>
         <v>1.0895</v>
       </c>
       <c r="G63" s="33" t="n">
@@ -18536,7 +18889,7 @@
         <v>2.4811961665052</v>
       </c>
       <c r="J63" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A63,레벨표!$A:$A,0))+$B$10*A63</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A63,레벨표!$A:$A,0))+$B$10*A63</f>
         <v>702</v>
       </c>
       <c r="K63" s="18" t="n">
@@ -18544,20 +18897,20 @@
         <v>536</v>
       </c>
       <c r="L63" s="34" t="n">
-        <f aca="false">MIN(K63/(K63+상수!$B$3*A63+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K63/(K63+상수!$B$4*A63+상수!$B$5),상수!$B$6)</f>
         <v>0.435418359057677</v>
       </c>
       <c r="M63" s="33" t="n">
-        <f aca="false">$B$16*B63*(1-L63)</f>
-        <v>329.498702024958</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A63,레벨표!$A:$A,0))*(1-L63)</f>
+        <v>105.343967166818</v>
       </c>
       <c r="N63" s="33" t="n">
         <f aca="false">J63/M63</f>
-        <v>2.13050915128287</v>
+        <v>6.66388421548947</v>
       </c>
       <c r="O63" s="33" t="n">
         <f aca="false">N63*$B$17</f>
-        <v>3.1957637269243</v>
+        <v>9.99582632323421</v>
       </c>
       <c r="P63" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -18585,11 +18938,11 @@
         <v>0.88</v>
       </c>
       <c r="E64" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A64,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A64,상수!$B$12)</f>
         <v>0.182</v>
       </c>
       <c r="F64" s="17" t="n">
-        <f aca="false">1+E64*상수!$B$10</f>
+        <f aca="false">1+E64*상수!$B$11</f>
         <v>1.091</v>
       </c>
       <c r="G64" s="33" t="n">
@@ -18605,7 +18958,7 @@
         <v>2.46241833220898</v>
       </c>
       <c r="J64" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A64,레벨표!$A:$A,0))+$B$10*A64</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A64,레벨표!$A:$A,0))+$B$10*A64</f>
         <v>716</v>
       </c>
       <c r="K64" s="18" t="n">
@@ -18613,20 +18966,20 @@
         <v>548</v>
       </c>
       <c r="L64" s="34" t="n">
-        <f aca="false">MIN(K64/(K64+상수!$B$3*A64+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K64/(K64+상수!$B$4*A64+상수!$B$5),상수!$B$6)</f>
         <v>0.435612082670906</v>
       </c>
       <c r="M64" s="33" t="n">
-        <f aca="false">$B$16*B64*(1-L64)</f>
-        <v>368.91191891166</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A64,레벨표!$A:$A,0))*(1-L64)</f>
+        <v>114.785524596977</v>
       </c>
       <c r="N64" s="33" t="n">
         <f aca="false">J64/M64</f>
-        <v>1.9408426870899</v>
+        <v>6.23772032679159</v>
       </c>
       <c r="O64" s="33" t="n">
         <f aca="false">N64*$B$17</f>
-        <v>2.91126403063486</v>
+        <v>9.35658049018739</v>
       </c>
       <c r="P64" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -18654,11 +19007,11 @@
         <v>0.9</v>
       </c>
       <c r="E65" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A65,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A65,상수!$B$12)</f>
         <v>0.185</v>
       </c>
       <c r="F65" s="17" t="n">
-        <f aca="false">1+E65*상수!$B$10</f>
+        <f aca="false">1+E65*상수!$B$11</f>
         <v>1.0925</v>
       </c>
       <c r="G65" s="33" t="n">
@@ -18674,7 +19027,7 @@
         <v>2.44406383211923</v>
       </c>
       <c r="J65" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A65,레벨표!$A:$A,0))+$B$10*A65</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A65,레벨표!$A:$A,0))+$B$10*A65</f>
         <v>730</v>
       </c>
       <c r="K65" s="18" t="n">
@@ -18682,20 +19035,20 @@
         <v>560</v>
       </c>
       <c r="L65" s="34" t="n">
-        <f aca="false">MIN(K65/(K65+상수!$B$3*A65+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K65/(K65+상수!$B$4*A65+상수!$B$5),상수!$B$6)</f>
         <v>0.43579766536965</v>
       </c>
       <c r="M65" s="33" t="n">
-        <f aca="false">$B$16*B65*(1-L65)</f>
-        <v>413.045486403886</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A65,레벨표!$A:$A,0))*(1-L65)</f>
+        <v>125.075080947502</v>
       </c>
       <c r="N65" s="33" t="n">
         <f aca="false">J65/M65</f>
-        <v>1.76735982846739</v>
+        <v>5.83649432380862</v>
       </c>
       <c r="O65" s="33" t="n">
         <f aca="false">N65*$B$17</f>
-        <v>2.65103974270108</v>
+        <v>8.75474148571294</v>
       </c>
       <c r="P65" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -18723,11 +19076,11 @@
         <v>0.92</v>
       </c>
       <c r="E66" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A66,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A66,상수!$B$12)</f>
         <v>0.188</v>
       </c>
       <c r="F66" s="17" t="n">
-        <f aca="false">1+E66*상수!$B$10</f>
+        <f aca="false">1+E66*상수!$B$11</f>
         <v>1.094</v>
       </c>
       <c r="G66" s="33" t="n">
@@ -18743,7 +19096,7 @@
         <v>2.42611953887972</v>
       </c>
       <c r="J66" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A66,레벨표!$A:$A,0))+$B$10*A66</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A66,레벨표!$A:$A,0))+$B$10*A66</f>
         <v>744</v>
       </c>
       <c r="K66" s="18" t="n">
@@ -18751,20 +19104,20 @@
         <v>572</v>
       </c>
       <c r="L66" s="34" t="n">
-        <f aca="false">MIN(K66/(K66+상수!$B$3*A66+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K66/(K66+상수!$B$4*A66+상수!$B$5),상수!$B$6)</f>
         <v>0.435975609756098</v>
       </c>
       <c r="M66" s="33" t="n">
-        <f aca="false">$B$16*B66*(1-L66)</f>
-        <v>462.465041404573</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A66,레벨표!$A:$A,0))*(1-L66)</f>
+        <v>136.288840386404</v>
       </c>
       <c r="N66" s="33" t="n">
         <f aca="false">J66/M66</f>
-        <v>1.60877024940169</v>
+        <v>5.4589942792867</v>
       </c>
       <c r="O66" s="33" t="n">
         <f aca="false">N66*$B$17</f>
-        <v>2.41315537410254</v>
+        <v>8.18849141893005</v>
       </c>
       <c r="P66" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -18792,11 +19145,11 @@
         <v>0.94</v>
       </c>
       <c r="E67" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A67,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A67,상수!$B$12)</f>
         <v>0.191</v>
       </c>
       <c r="F67" s="17" t="n">
-        <f aca="false">1+E67*상수!$B$10</f>
+        <f aca="false">1+E67*상수!$B$11</f>
         <v>1.0955</v>
       </c>
       <c r="G67" s="33" t="n">
@@ -18812,7 +19165,7 @@
         <v>2.40857286687318</v>
       </c>
       <c r="J67" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A67,레벨표!$A:$A,0))+$B$10*A67</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A67,레벨표!$A:$A,0))+$B$10*A67</f>
         <v>758</v>
       </c>
       <c r="K67" s="18" t="n">
@@ -18820,20 +19173,20 @@
         <v>584</v>
       </c>
       <c r="L67" s="34" t="n">
-        <f aca="false">MIN(K67/(K67+상수!$B$3*A67+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K67/(K67+상수!$B$4*A67+상수!$B$5),상수!$B$6)</f>
         <v>0.436146377893951</v>
       </c>
       <c r="M67" s="33" t="n">
-        <f aca="false">$B$16*B67*(1-L67)</f>
-        <v>517.804024769755</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A67,레벨표!$A:$A,0))*(1-L67)</f>
+        <v>148.509858475608</v>
       </c>
       <c r="N67" s="33" t="n">
         <f aca="false">J67/M67</f>
-        <v>1.46387429170148</v>
+        <v>5.10403826237905</v>
       </c>
       <c r="O67" s="33" t="n">
         <f aca="false">N67*$B$17</f>
-        <v>2.19581143755222</v>
+        <v>7.65605739356857</v>
       </c>
       <c r="P67" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -18861,11 +19214,11 @@
         <v>0.96</v>
       </c>
       <c r="E68" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A68,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A68,상수!$B$12)</f>
         <v>0.194</v>
       </c>
       <c r="F68" s="17" t="n">
-        <f aca="false">1+E68*상수!$B$10</f>
+        <f aca="false">1+E68*상수!$B$11</f>
         <v>1.097</v>
       </c>
       <c r="G68" s="33" t="n">
@@ -18881,7 +19234,7 @@
         <v>2.39141174458303</v>
       </c>
       <c r="J68" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A68,레벨표!$A:$A,0))+$B$10*A68</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A68,레벨표!$A:$A,0))+$B$10*A68</f>
         <v>772</v>
       </c>
       <c r="K68" s="18" t="n">
@@ -18889,20 +19242,20 @@
         <v>596</v>
       </c>
       <c r="L68" s="34" t="n">
-        <f aca="false">MIN(K68/(K68+상수!$B$3*A68+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K68/(K68+상수!$B$4*A68+상수!$B$5),상수!$B$6)</f>
         <v>0.436310395314788</v>
       </c>
       <c r="M68" s="33" t="n">
-        <f aca="false">$B$16*B68*(1-L68)</f>
-        <v>579.771810863026</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A68,레벨표!$A:$A,0))*(1-L68)</f>
+        <v>161.828658265226</v>
       </c>
       <c r="N68" s="33" t="n">
         <f aca="false">J68/M68</f>
-        <v>1.33155835715923</v>
+        <v>4.7704776661668</v>
       </c>
       <c r="O68" s="33" t="n">
         <f aca="false">N68*$B$17</f>
-        <v>1.99733753573884</v>
+        <v>7.1557164992502</v>
       </c>
       <c r="P68" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -18930,11 +19283,11 @@
         <v>0.98</v>
       </c>
       <c r="E69" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A69,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A69,상수!$B$12)</f>
         <v>0.197</v>
       </c>
       <c r="F69" s="17" t="n">
-        <f aca="false">1+E69*상수!$B$10</f>
+        <f aca="false">1+E69*상수!$B$11</f>
         <v>1.0985</v>
       </c>
       <c r="G69" s="33" t="n">
@@ -18950,7 +19303,7 @@
         <v>2.37462458863025</v>
       </c>
       <c r="J69" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A69,레벨표!$A:$A,0))+$B$10*A69</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A69,레벨표!$A:$A,0))+$B$10*A69</f>
         <v>786</v>
       </c>
       <c r="K69" s="18" t="n">
@@ -18958,20 +19311,20 @@
         <v>608</v>
       </c>
       <c r="L69" s="34" t="n">
-        <f aca="false">MIN(K69/(K69+상수!$B$3*A69+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K69/(K69+상수!$B$4*A69+상수!$B$5),상수!$B$6)</f>
         <v>0.436468054558507</v>
       </c>
       <c r="M69" s="33" t="n">
-        <f aca="false">$B$16*B69*(1-L69)</f>
-        <v>649.162811988807</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A69,레벨표!$A:$A,0))*(1-L69)</f>
+        <v>176.343901803432</v>
       </c>
       <c r="N69" s="33" t="n">
         <f aca="false">J69/M69</f>
-        <v>1.21079024473378</v>
+        <v>4.45719977817063</v>
       </c>
       <c r="O69" s="33" t="n">
         <f aca="false">N69*$B$17</f>
-        <v>1.81618536710068</v>
+        <v>6.68579966725594</v>
       </c>
       <c r="P69" s="33" t="n">
         <f aca="false">$B$13</f>
@@ -18999,11 +19352,11 @@
         <v>1</v>
       </c>
       <c r="E70" s="35" t="n">
-        <f aca="false">MIN(상수!$B$9+$B$9*A70,상수!$B$11)</f>
+        <f aca="false">MIN(상수!$B$10+$B$9*A70,상수!$B$12)</f>
         <v>0.2</v>
       </c>
       <c r="F70" s="17" t="n">
-        <f aca="false">1+E70*상수!$B$10</f>
+        <f aca="false">1+E70*상수!$B$11</f>
         <v>1.1</v>
       </c>
       <c r="G70" s="33" t="n">
@@ -19019,7 +19372,7 @@
         <v>2.3582002793679</v>
       </c>
       <c r="J70" s="18" t="n">
-        <f aca="false">INDEX(레벨표!$C:$C,MATCH(A70,레벨표!$A:$A,0))+$B$10*A70</f>
+        <f aca="false">INDEX(레벨표!$D:$D,MATCH(A70,레벨표!$A:$A,0))+$B$10*A70</f>
         <v>800</v>
       </c>
       <c r="K70" s="18" t="n">
@@ -19027,20 +19380,20 @@
         <v>620</v>
       </c>
       <c r="L70" s="34" t="n">
-        <f aca="false">MIN(K70/(K70+상수!$B$3*A70+상수!$B$4),상수!$B$5)</f>
+        <f aca="false">MIN(K70/(K70+상수!$B$4*A70+상수!$B$5),상수!$B$6)</f>
         <v>0.436619718309859</v>
       </c>
       <c r="M70" s="33" t="n">
-        <f aca="false">$B$16*B70*(1-L70)</f>
-        <v>726.866674622738</v>
+        <f aca="false">$B$16*INDEX(레벨표!$C:$C,MATCH(A70,레벨표!$A:$A,0))*(1-L70)</f>
+        <v>192.16312204631</v>
       </c>
       <c r="N70" s="33" t="n">
         <f aca="false">J70/M70</f>
-        <v>1.10061449772095</v>
+        <v>4.16312969669178</v>
       </c>
       <c r="O70" s="33" t="n">
         <f aca="false">N70*$B$17</f>
-        <v>1.65092174658142</v>
+        <v>6.24469454503767</v>
       </c>
       <c r="P70" s="33" t="n">
         <f aca="false">$B$13</f>

--- a/Docs/Balance/귀살_밸런스.xlsx
+++ b/Docs/Balance/귀살_밸런스.xlsx
@@ -854,7 +854,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="448">
   <si>
     <r>
       <rPr>
@@ -4033,6 +4033,15 @@
   </si>
   <si>
     <t xml:space="preserve">LifeOnKill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resource_on_hit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">적중 시 기력</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ResourceOnHit</t>
   </si>
   <si>
     <t xml:space="preserve">max_resource</t>
@@ -7516,11 +7525,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="96354353"/>
-        <c:axId val="80361097"/>
+        <c:axId val="68993882"/>
+        <c:axId val="73737917"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="96354353"/>
+        <c:axId val="68993882"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7586,7 +7595,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80361097"/>
+        <c:crossAx val="73737917"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7594,7 +7603,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="80361097"/>
+        <c:axId val="73737917"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7670,7 +7679,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96354353"/>
+        <c:crossAx val="68993882"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8518,11 +8527,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="21459630"/>
-        <c:axId val="78736989"/>
+        <c:axId val="35607910"/>
+        <c:axId val="14767814"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="21459630"/>
+        <c:axId val="35607910"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8588,7 +8597,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78736989"/>
+        <c:crossAx val="14767814"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8596,7 +8605,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="78736989"/>
+        <c:axId val="14767814"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8672,7 +8681,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21459630"/>
+        <c:crossAx val="35607910"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12112,7 +12121,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:T31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -13148,38 +13157,38 @@
         <v>198</v>
       </c>
       <c r="E21" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="14" t="n">
+      <c r="G21" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="G21" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="H21" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I21" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="J21" s="14" t="n">
-        <v>21</v>
-      </c>
-      <c r="K21" s="14" t="n">
-        <v>30</v>
-      </c>
-      <c r="L21" s="22"/>
+      <c r="L21" s="22" t="s">
+        <v>199</v>
+      </c>
       <c r="M21" s="22"/>
-      <c r="N21" s="22" t="s">
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="O21" s="22"/>
-      <c r="P21" s="22"/>
       <c r="Q21" s="22"/>
       <c r="R21" s="22"/>
-      <c r="S21" s="22" t="s">
-        <v>199</v>
-      </c>
+      <c r="S21" s="22"/>
       <c r="T21" s="22"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13190,35 +13199,37 @@
         <v>254</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>83</v>
+        <v>255</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>198</v>
       </c>
       <c r="E22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F22" s="21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G22" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" s="21" t="n">
-        <v>3</v>
+      <c r="G22" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="K22" s="14" t="n">
+        <v>30</v>
       </c>
       <c r="L22" s="22"/>
       <c r="M22" s="22"/>
-      <c r="N22" s="22"/>
+      <c r="N22" s="22" t="s">
+        <v>199</v>
+      </c>
       <c r="O22" s="22"/>
       <c r="P22" s="22"/>
       <c r="Q22" s="22"/>
@@ -13226,55 +13237,55 @@
       <c r="S22" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="T22" s="22" t="s">
-        <v>199</v>
-      </c>
+      <c r="T22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>257</v>
+        <v>83</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>198</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="F23" s="15" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G23" s="15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I23" s="15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J23" s="15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K23" s="15" t="n">
-        <v>0.12</v>
+        <v>5</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G23" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="L23" s="22"/>
-      <c r="M23" s="22" t="s">
-        <v>199</v>
-      </c>
+      <c r="M23" s="22"/>
       <c r="N23" s="22"/>
       <c r="O23" s="22"/>
       <c r="P23" s="22"/>
       <c r="Q23" s="22"/>
       <c r="R23" s="22"/>
-      <c r="S23" s="22"/>
-      <c r="T23" s="22"/>
+      <c r="S23" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="T23" s="22" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
@@ -13314,9 +13325,7 @@
       <c r="M24" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="N24" s="22" t="s">
-        <v>199</v>
-      </c>
+      <c r="N24" s="22"/>
       <c r="O24" s="22"/>
       <c r="P24" s="22"/>
       <c r="Q24" s="22"/>
@@ -13335,10 +13344,10 @@
         <v>263</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F25" s="15" t="n">
         <v>0.03</v>
@@ -13347,26 +13356,28 @@
         <v>0.05</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="K25" s="15" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="L25" s="22"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="22"/>
+      <c r="M25" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="N25" s="22" t="s">
+        <v>199</v>
+      </c>
       <c r="O25" s="22"/>
       <c r="P25" s="22"/>
       <c r="Q25" s="22"/>
-      <c r="R25" s="22" t="s">
-        <v>199</v>
-      </c>
+      <c r="R25" s="22"/>
       <c r="S25" s="22"/>
       <c r="T25" s="22"/>
     </row>
@@ -13384,35 +13395,35 @@
         <v>203</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F26" s="15" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G26" s="15" t="n">
         <v>0.05</v>
       </c>
-      <c r="G26" s="15" t="n">
+      <c r="H26" s="15" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I26" s="15" t="n">
         <v>0.1</v>
       </c>
-      <c r="H26" s="15" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I26" s="15" t="n">
-        <v>0.2</v>
-      </c>
       <c r="J26" s="15" t="n">
-        <v>0.21</v>
+        <v>0.1</v>
       </c>
       <c r="K26" s="15" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="L26" s="22"/>
       <c r="M26" s="22"/>
       <c r="N26" s="22"/>
       <c r="O26" s="22"/>
       <c r="P26" s="22"/>
-      <c r="Q26" s="22" t="s">
+      <c r="Q26" s="22"/>
+      <c r="R26" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="R26" s="22"/>
       <c r="S26" s="22"/>
       <c r="T26" s="22"/>
     </row>
@@ -13427,7 +13438,7 @@
         <v>269</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E27" s="14" t="n">
         <v>5</v>
@@ -13448,19 +13459,19 @@
         <v>0.21</v>
       </c>
       <c r="K27" s="15" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="L27" s="22"/>
       <c r="M27" s="22"/>
       <c r="N27" s="22"/>
       <c r="O27" s="22"/>
       <c r="P27" s="22"/>
-      <c r="Q27" s="22"/>
+      <c r="Q27" s="22" t="s">
+        <v>199</v>
+      </c>
       <c r="R27" s="22"/>
       <c r="S27" s="22"/>
-      <c r="T27" s="22" t="s">
-        <v>199</v>
-      </c>
+      <c r="T27" s="22"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
@@ -13476,25 +13487,25 @@
         <v>198</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F28" s="15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G28" s="15" t="n">
         <v>0.1</v>
       </c>
-      <c r="G28" s="15" t="n">
+      <c r="H28" s="15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I28" s="15" t="n">
         <v>0.2</v>
       </c>
-      <c r="H28" s="15" t="n">
+      <c r="J28" s="15" t="n">
         <v>0.21</v>
       </c>
-      <c r="I28" s="15" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J28" s="15" t="n">
-        <v>0.41</v>
-      </c>
       <c r="K28" s="15" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="L28" s="22"/>
       <c r="M28" s="22"/>
@@ -13522,25 +13533,25 @@
         <v>198</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="F29" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" s="14" t="n">
-        <v>2</v>
+      <c r="F29" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J29" s="15" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K29" s="15" t="n">
+        <v>0.6</v>
       </c>
       <c r="L29" s="22"/>
       <c r="M29" s="22"/>
@@ -13549,10 +13560,10 @@
       <c r="P29" s="22"/>
       <c r="Q29" s="22"/>
       <c r="R29" s="22"/>
-      <c r="S29" s="22" t="s">
+      <c r="S29" s="22"/>
+      <c r="T29" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="T29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
@@ -13568,37 +13579,83 @@
         <v>198</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>30</v>
-      </c>
-      <c r="F30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="15" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I30" s="15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="J30" s="15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K30" s="15" t="n">
-        <v>0.05</v>
+        <v>20</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="14" t="n">
+        <v>2</v>
       </c>
       <c r="L30" s="22"/>
       <c r="M30" s="22"/>
       <c r="N30" s="22"/>
-      <c r="O30" s="22" t="s">
-        <v>199</v>
-      </c>
+      <c r="O30" s="22"/>
       <c r="P30" s="22"/>
       <c r="Q30" s="22"/>
       <c r="R30" s="22"/>
-      <c r="S30" s="22"/>
+      <c r="S30" s="22" t="s">
+        <v>199</v>
+      </c>
       <c r="T30" s="22"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J31" s="15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K31" s="15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L31" s="22"/>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22"/>
+      <c r="R31" s="22"/>
+      <c r="S31" s="22"/>
+      <c r="T31" s="22"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -13638,22 +13695,22 @@
         <v>126</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D1" s="16" t="s">
         <v>124</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I1" s="16" t="s">
         <v>138</v>
@@ -13661,7 +13718,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B2" s="11" t="n">
         <v>1</v>
@@ -13670,13 +13727,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G2" s="14" t="n">
         <v>1</v>
@@ -13685,12 +13742,12 @@
         <v>6</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B3" s="11" t="n">
         <v>1</v>
@@ -13699,13 +13756,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>290</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>287</v>
       </c>
       <c r="G3" s="14" t="n">
         <v>2</v>
@@ -13717,7 +13774,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>1</v>
@@ -13726,13 +13783,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G4" s="14" t="n">
         <v>3</v>
@@ -13744,7 +13801,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>1</v>
@@ -13753,10 +13810,10 @@
         <v>4</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F5" s="11"/>
       <c r="G5" s="14" t="n">
@@ -13766,12 +13823,12 @@
         <v>6</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>1</v>
@@ -13780,13 +13837,13 @@
         <v>5</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>5</v>
@@ -13798,7 +13855,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>1</v>
@@ -13807,13 +13864,13 @@
         <v>6</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>6</v>
@@ -13822,12 +13879,12 @@
         <v>20</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>1</v>
@@ -13836,13 +13893,13 @@
         <v>7</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>7</v>
@@ -13854,7 +13911,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>1</v>
@@ -13863,13 +13920,13 @@
         <v>8</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>8</v>
@@ -13878,12 +13935,12 @@
         <v>20</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>1</v>
@@ -13892,13 +13949,13 @@
         <v>9</v>
       </c>
       <c r="D10" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>310</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>307</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>9</v>
@@ -13907,12 +13964,12 @@
         <v>20</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B11" s="11" t="n">
         <v>1</v>
@@ -13921,13 +13978,13 @@
         <v>10</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>9</v>
@@ -13939,7 +13996,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B12" s="11" t="n">
         <v>1</v>
@@ -13948,13 +14005,13 @@
         <v>11</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>10</v>
@@ -13966,7 +14023,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B13" s="11" t="n">
         <v>1</v>
@@ -13975,13 +14032,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>11</v>
@@ -13990,12 +14047,12 @@
         <v>20</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B14" s="11" t="n">
         <v>1</v>
@@ -14004,13 +14061,13 @@
         <v>13</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>12</v>
@@ -14019,12 +14076,12 @@
         <v>20</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B15" s="11" t="n">
         <v>1</v>
@@ -14033,13 +14090,13 @@
         <v>14</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>12</v>
@@ -14051,7 +14108,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>1</v>
@@ -14060,13 +14117,13 @@
         <v>15</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>13</v>
@@ -14075,12 +14132,12 @@
         <v>6</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B17" s="11" t="n">
         <v>2</v>
@@ -14089,13 +14146,13 @@
         <v>1</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>14</v>
@@ -14107,7 +14164,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B18" s="11" t="n">
         <v>2</v>
@@ -14116,10 +14173,10 @@
         <v>2</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="14" t="n">
@@ -14129,12 +14186,12 @@
         <v>0</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B19" s="11" t="n">
         <v>2</v>
@@ -14143,13 +14200,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>15</v>
@@ -14161,7 +14218,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B20" s="11" t="n">
         <v>2</v>
@@ -14170,13 +14227,13 @@
         <v>4</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G20" s="14" t="n">
         <v>16</v>
@@ -14185,12 +14242,12 @@
         <v>20</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B21" s="11" t="n">
         <v>2</v>
@@ -14199,13 +14256,13 @@
         <v>5</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>17</v>
@@ -14217,7 +14274,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B22" s="11" t="n">
         <v>2</v>
@@ -14226,13 +14283,13 @@
         <v>6</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>18</v>
@@ -14244,7 +14301,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B23" s="11" t="n">
         <v>2</v>
@@ -14253,13 +14310,13 @@
         <v>7</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>19</v>
@@ -14268,12 +14325,12 @@
         <v>20</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B24" s="11" t="n">
         <v>2</v>
@@ -14282,13 +14339,13 @@
         <v>8</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>20</v>
@@ -14297,12 +14354,12 @@
         <v>20</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B25" s="11" t="n">
         <v>2</v>
@@ -14311,13 +14368,13 @@
         <v>9</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>19</v>
@@ -14326,12 +14383,12 @@
         <v>20</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B26" s="11" t="n">
         <v>2</v>
@@ -14340,13 +14397,13 @@
         <v>10</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G26" s="14" t="n">
         <v>20</v>
@@ -14358,7 +14415,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B27" s="11" t="n">
         <v>2</v>
@@ -14367,13 +14424,13 @@
         <v>11</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>21</v>
@@ -14382,12 +14439,12 @@
         <v>20</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B28" s="11" t="n">
         <v>2</v>
@@ -14396,13 +14453,13 @@
         <v>12</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>22</v>
@@ -14411,12 +14468,12 @@
         <v>20</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B29" s="11" t="n">
         <v>2</v>
@@ -14425,13 +14482,13 @@
         <v>13</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>22</v>
@@ -14443,7 +14500,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B30" s="11" t="n">
         <v>2</v>
@@ -14452,13 +14509,13 @@
         <v>14</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>23</v>
@@ -14470,7 +14527,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B31" s="11" t="n">
         <v>2</v>
@@ -14479,13 +14536,13 @@
         <v>15</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>24</v>
@@ -14497,7 +14554,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B32" s="11" t="n">
         <v>2</v>
@@ -14506,13 +14563,13 @@
         <v>16</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>24</v>
@@ -14521,12 +14578,12 @@
         <v>6</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B33" s="11" t="n">
         <v>3</v>
@@ -14535,13 +14592,13 @@
         <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>25</v>
@@ -14553,7 +14610,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B34" s="11" t="n">
         <v>3</v>
@@ -14562,10 +14619,10 @@
         <v>2</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F34" s="11"/>
       <c r="G34" s="14" t="n">
@@ -14575,12 +14632,12 @@
         <v>0</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B35" s="11" t="n">
         <v>3</v>
@@ -14589,13 +14646,13 @@
         <v>3</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>26</v>
@@ -14607,7 +14664,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B36" s="11" t="n">
         <v>3</v>
@@ -14616,13 +14673,13 @@
         <v>4</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G36" s="14" t="n">
         <v>27</v>
@@ -14631,12 +14688,12 @@
         <v>20</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B37" s="11" t="n">
         <v>3</v>
@@ -14645,13 +14702,13 @@
         <v>5</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>28</v>
@@ -14660,12 +14717,12 @@
         <v>20</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B38" s="11" t="n">
         <v>3</v>
@@ -14674,13 +14731,13 @@
         <v>6</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G38" s="14" t="n">
         <v>29</v>
@@ -14689,12 +14746,12 @@
         <v>20</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B39" s="11" t="n">
         <v>3</v>
@@ -14703,13 +14760,13 @@
         <v>7</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>28</v>
@@ -14721,7 +14778,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B40" s="11" t="n">
         <v>3</v>
@@ -14730,13 +14787,13 @@
         <v>8</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>29</v>
@@ -14748,7 +14805,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B41" s="11" t="n">
         <v>3</v>
@@ -14757,13 +14814,13 @@
         <v>9</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>30</v>
@@ -14772,12 +14829,12 @@
         <v>20</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B42" s="11" t="n">
         <v>3</v>
@@ -14786,13 +14843,13 @@
         <v>10</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G42" s="14" t="n">
         <v>30</v>
@@ -14801,12 +14858,12 @@
         <v>6</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B43" s="11" t="n">
         <v>3</v>
@@ -14815,13 +14872,13 @@
         <v>11</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>31</v>
@@ -14833,7 +14890,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B44" s="11" t="n">
         <v>3</v>
@@ -14842,13 +14899,13 @@
         <v>12</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G44" s="14" t="n">
         <v>32</v>
@@ -14857,12 +14914,12 @@
         <v>20</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B45" s="11" t="n">
         <v>3</v>
@@ -14871,13 +14928,13 @@
         <v>13</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G45" s="14" t="n">
         <v>33</v>
@@ -14889,7 +14946,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B46" s="11" t="n">
         <v>3</v>
@@ -14898,13 +14955,13 @@
         <v>14</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G46" s="14" t="n">
         <v>34</v>
@@ -14913,12 +14970,12 @@
         <v>20</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B47" s="11" t="n">
         <v>3</v>
@@ -14927,13 +14984,13 @@
         <v>15</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>35</v>
@@ -14942,12 +14999,12 @@
         <v>20</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B48" s="11" t="n">
         <v>3</v>
@@ -14956,13 +15013,13 @@
         <v>16</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G48" s="14" t="n">
         <v>35</v>
@@ -14974,7 +15031,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B49" s="11" t="n">
         <v>3</v>
@@ -14983,13 +15040,13 @@
         <v>17</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>36</v>
@@ -14998,7 +15055,7 @@
         <v>6</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15014,7 +15071,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="23" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -15027,13 +15084,13 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="24" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -15450,7 +15507,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15490,13 +15547,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B3" s="20" t="s">
         <v>139</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -15515,13 +15572,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B4" s="21" t="n">
         <v>6</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -15540,13 +15597,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B5" s="26" t="n">
         <v>1.115</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -15565,13 +15622,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>1.2</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -15590,13 +15647,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B7" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -15615,13 +15672,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B8" s="27" t="n">
         <v>0.02</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -15640,13 +15697,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B9" s="27" t="n">
         <v>0.003</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -15665,13 +15722,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B10" s="14" t="n">
         <v>4</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -15690,13 +15747,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B11" s="14" t="n">
         <v>12</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -15715,7 +15772,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B12" s="14" t="n">
         <v>20</v>
@@ -15738,13 +15795,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B13" s="21" t="n">
         <v>2.5</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -15763,13 +15820,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B14" s="14" t="n">
         <v>15</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -15788,7 +15845,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B15" s="28" t="n">
         <f aca="false">INDEX(귀신!$F:$F,MATCH($B$3,귀신!$A:$A,0))</f>
@@ -15812,7 +15869,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B16" s="28" t="n">
         <f aca="false">INDEX(귀신!$G:$G,MATCH($B$3,귀신!$A:$A,0))</f>
@@ -15836,7 +15893,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B17" s="29" t="n">
         <f aca="false">INDEX(귀신!$H:$H,MATCH($B$3,귀신!$A:$A,0))</f>
@@ -15860,7 +15917,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B18" s="28" t="n">
         <f aca="false">INDEX(귀신!$J:$J,MATCH($B$3,귀신!$A:$A,0))</f>
@@ -15909,25 +15966,25 @@
         <v>116</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E20" s="30" t="s">
         <v>221</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G20" s="30" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="H20" s="30" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="I20" s="30" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="J20" s="30" t="s">
         <v>118</v>
@@ -15936,22 +15993,22 @@
         <v>131</v>
       </c>
       <c r="L20" s="30" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="M20" s="30" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="N20" s="30" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="O20" s="30" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="P20" s="30" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="Q20" s="31" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Docs/Balance/귀살_밸런스.xlsx
+++ b/Docs/Balance/귀살_밸런스.xlsx
@@ -854,7 +854,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="457">
   <si>
     <r>
       <rPr>
@@ -4042,6 +4042,87 @@
   </si>
   <si>
     <t xml:space="preserve">ResourceOnHit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minion_damage</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">소환물 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">MinionDamagePct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minion_health</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">소환물 체력 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">MinionHealthPct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">curse_effect</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저주 효과 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CurseEffectPct</t>
   </si>
   <si>
     <t xml:space="preserve">max_resource</t>
@@ -7525,11 +7606,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="68993882"/>
-        <c:axId val="73737917"/>
+        <c:axId val="21919977"/>
+        <c:axId val="28314007"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="68993882"/>
+        <c:axId val="21919977"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7595,7 +7676,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73737917"/>
+        <c:crossAx val="28314007"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7603,7 +7684,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73737917"/>
+        <c:axId val="28314007"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7679,7 +7760,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68993882"/>
+        <c:crossAx val="21919977"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8527,11 +8608,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="35607910"/>
-        <c:axId val="14767814"/>
+        <c:axId val="32089847"/>
+        <c:axId val="22183460"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="35607910"/>
+        <c:axId val="32089847"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8597,7 +8678,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14767814"/>
+        <c:crossAx val="22183460"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8605,7 +8686,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="14767814"/>
+        <c:axId val="22183460"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8681,7 +8762,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35607910"/>
+        <c:crossAx val="32089847"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12121,7 +12202,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T31"/>
+  <dimension ref="A1:T34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
@@ -13202,34 +13283,34 @@
         <v>255</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="G22" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="H22" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="I22" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="J22" s="14" t="n">
-        <v>21</v>
-      </c>
-      <c r="K22" s="14" t="n">
-        <v>30</v>
+      <c r="F22" s="15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J22" s="15" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K22" s="15" t="n">
+        <v>0.35</v>
       </c>
       <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="22" t="s">
+      <c r="M22" s="22" t="s">
         <v>199</v>
       </c>
+      <c r="N22" s="22"/>
       <c r="O22" s="22"/>
       <c r="P22" s="22"/>
       <c r="Q22" s="22"/>
@@ -13247,34 +13328,36 @@
         <v>257</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>83</v>
+        <v>258</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E23" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G23" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" s="21" t="n">
-        <v>3</v>
+      <c r="F23" s="15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J23" s="15" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K23" s="15" t="n">
+        <v>0.35</v>
       </c>
       <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
+      <c r="M23" s="22" t="s">
+        <v>199</v>
+      </c>
       <c r="N23" s="22"/>
       <c r="O23" s="22"/>
       <c r="P23" s="22"/>
@@ -13283,43 +13366,41 @@
       <c r="S23" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="T23" s="22" t="s">
-        <v>199</v>
-      </c>
+      <c r="T23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E24" s="14" t="n">
         <v>10</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="J24" s="15" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="K24" s="15" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="L24" s="22"/>
       <c r="M24" s="22" t="s">
@@ -13335,42 +13416,40 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>198</v>
       </c>
       <c r="E25" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="F25" s="15" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G25" s="15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H25" s="15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I25" s="15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J25" s="15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K25" s="15" t="n">
-        <v>0.12</v>
+      <c r="H25" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>30</v>
       </c>
       <c r="L25" s="22"/>
-      <c r="M25" s="22" t="s">
-        <v>199</v>
-      </c>
+      <c r="M25" s="22"/>
       <c r="N25" s="22" t="s">
         <v>199</v>
       </c>
@@ -13378,42 +13457,44 @@
       <c r="P25" s="22"/>
       <c r="Q25" s="22"/>
       <c r="R25" s="22"/>
-      <c r="S25" s="22"/>
+      <c r="S25" s="22" t="s">
+        <v>199</v>
+      </c>
       <c r="T25" s="22"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>266</v>
+        <v>83</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E26" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G26" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="15" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G26" s="15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H26" s="15" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I26" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J26" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K26" s="15" t="n">
-        <v>0.15</v>
+      <c r="H26" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="L26" s="22"/>
       <c r="M26" s="22"/>
@@ -13421,11 +13502,13 @@
       <c r="O26" s="22"/>
       <c r="P26" s="22"/>
       <c r="Q26" s="22"/>
-      <c r="R26" s="22" t="s">
+      <c r="R26" s="22"/>
+      <c r="S26" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="S26" s="22"/>
-      <c r="T26" s="22"/>
+      <c r="T26" s="22" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
@@ -13438,37 +13521,37 @@
         <v>269</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F27" s="15" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G27" s="15" t="n">
         <v>0.05</v>
       </c>
-      <c r="G27" s="15" t="n">
-        <v>0.1</v>
-      </c>
       <c r="H27" s="15" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="J27" s="15" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="K27" s="15" t="n">
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="L27" s="22"/>
-      <c r="M27" s="22"/>
+      <c r="M27" s="22" t="s">
+        <v>199</v>
+      </c>
       <c r="N27" s="22"/>
       <c r="O27" s="22"/>
       <c r="P27" s="22"/>
-      <c r="Q27" s="22" t="s">
-        <v>199</v>
-      </c>
+      <c r="Q27" s="22"/>
       <c r="R27" s="22"/>
       <c r="S27" s="22"/>
       <c r="T27" s="22"/>
@@ -13487,37 +13570,39 @@
         <v>198</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F28" s="15" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G28" s="15" t="n">
         <v>0.05</v>
       </c>
-      <c r="G28" s="15" t="n">
-        <v>0.1</v>
-      </c>
       <c r="H28" s="15" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="J28" s="15" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="K28" s="15" t="n">
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="22"/>
+      <c r="M28" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="N28" s="22" t="s">
+        <v>199</v>
+      </c>
       <c r="O28" s="22"/>
       <c r="P28" s="22"/>
       <c r="Q28" s="22"/>
       <c r="R28" s="22"/>
       <c r="S28" s="22"/>
-      <c r="T28" s="22" t="s">
-        <v>199</v>
-      </c>
+      <c r="T28" s="22"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
@@ -13530,28 +13615,28 @@
         <v>275</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E29" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="15" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I29" s="15" t="n">
         <v>0.1</v>
       </c>
-      <c r="G29" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I29" s="15" t="n">
-        <v>0.4</v>
-      </c>
       <c r="J29" s="15" t="n">
-        <v>0.41</v>
+        <v>0.1</v>
       </c>
       <c r="K29" s="15" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="L29" s="22"/>
       <c r="M29" s="22"/>
@@ -13559,11 +13644,11 @@
       <c r="O29" s="22"/>
       <c r="P29" s="22"/>
       <c r="Q29" s="22"/>
-      <c r="R29" s="22"/>
+      <c r="R29" s="22" t="s">
+        <v>199</v>
+      </c>
       <c r="S29" s="22"/>
-      <c r="T29" s="22" t="s">
-        <v>199</v>
-      </c>
+      <c r="T29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
@@ -13576,39 +13661,39 @@
         <v>278</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" s="14" t="n">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J30" s="15" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K30" s="15" t="n">
+        <v>0.3</v>
       </c>
       <c r="L30" s="22"/>
       <c r="M30" s="22"/>
       <c r="N30" s="22"/>
       <c r="O30" s="22"/>
       <c r="P30" s="22"/>
-      <c r="Q30" s="22"/>
+      <c r="Q30" s="22" t="s">
+        <v>199</v>
+      </c>
       <c r="R30" s="22"/>
-      <c r="S30" s="22" t="s">
-        <v>199</v>
-      </c>
+      <c r="S30" s="22"/>
       <c r="T30" s="22"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13625,37 +13710,175 @@
         <v>198</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>0.01</v>
+        <v>0.11</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="J31" s="15" t="n">
-        <v>0.02</v>
+        <v>0.21</v>
       </c>
       <c r="K31" s="15" t="n">
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="L31" s="22"/>
       <c r="M31" s="22"/>
       <c r="N31" s="22"/>
-      <c r="O31" s="22" t="s">
-        <v>199</v>
-      </c>
+      <c r="O31" s="22"/>
       <c r="P31" s="22"/>
       <c r="Q31" s="22"/>
       <c r="R31" s="22"/>
       <c r="S31" s="22"/>
-      <c r="T31" s="22"/>
+      <c r="T31" s="22" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G32" s="15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J32" s="15" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K32" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L32" s="22"/>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22"/>
+      <c r="R32" s="22"/>
+      <c r="S32" s="22"/>
+      <c r="T32" s="22" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" s="22"/>
+      <c r="M33" s="22"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22"/>
+      <c r="R33" s="22"/>
+      <c r="S33" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="T33" s="22"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="F34" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J34" s="15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K34" s="15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L34" s="22"/>
+      <c r="M34" s="22"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="22"/>
+      <c r="R34" s="22"/>
+      <c r="S34" s="22"/>
+      <c r="T34" s="22"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -13695,22 +13918,22 @@
         <v>126</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="D1" s="16" t="s">
         <v>124</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="I1" s="16" t="s">
         <v>138</v>
@@ -13718,7 +13941,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B2" s="11" t="n">
         <v>1</v>
@@ -13727,13 +13950,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="G2" s="14" t="n">
         <v>1</v>
@@ -13742,12 +13965,12 @@
         <v>6</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="B3" s="11" t="n">
         <v>1</v>
@@ -13756,13 +13979,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="G3" s="14" t="n">
         <v>2</v>
@@ -13774,7 +13997,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>1</v>
@@ -13783,13 +14006,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="G4" s="14" t="n">
         <v>3</v>
@@ -13801,7 +14024,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>1</v>
@@ -13810,10 +14033,10 @@
         <v>4</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="F5" s="11"/>
       <c r="G5" s="14" t="n">
@@ -13823,12 +14046,12 @@
         <v>6</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>1</v>
@@ -13837,13 +14060,13 @@
         <v>5</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>5</v>
@@ -13855,7 +14078,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>1</v>
@@ -13864,13 +14087,13 @@
         <v>6</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>6</v>
@@ -13879,12 +14102,12 @@
         <v>20</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>1</v>
@@ -13893,13 +14116,13 @@
         <v>7</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>7</v>
@@ -13911,7 +14134,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>1</v>
@@ -13920,13 +14143,13 @@
         <v>8</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>8</v>
@@ -13935,12 +14158,12 @@
         <v>20</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>1</v>
@@ -13949,13 +14172,13 @@
         <v>9</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>9</v>
@@ -13964,12 +14187,12 @@
         <v>20</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B11" s="11" t="n">
         <v>1</v>
@@ -13978,13 +14201,13 @@
         <v>10</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>9</v>
@@ -13996,7 +14219,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B12" s="11" t="n">
         <v>1</v>
@@ -14005,13 +14228,13 @@
         <v>11</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>10</v>
@@ -14023,7 +14246,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="B13" s="11" t="n">
         <v>1</v>
@@ -14032,13 +14255,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>11</v>
@@ -14047,12 +14270,12 @@
         <v>20</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="B14" s="11" t="n">
         <v>1</v>
@@ -14061,13 +14284,13 @@
         <v>13</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>12</v>
@@ -14076,12 +14299,12 @@
         <v>20</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="B15" s="11" t="n">
         <v>1</v>
@@ -14090,13 +14313,13 @@
         <v>14</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>12</v>
@@ -14108,7 +14331,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>1</v>
@@ -14117,13 +14340,13 @@
         <v>15</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>13</v>
@@ -14132,12 +14355,12 @@
         <v>6</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="B17" s="11" t="n">
         <v>2</v>
@@ -14146,13 +14369,13 @@
         <v>1</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>14</v>
@@ -14164,7 +14387,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B18" s="11" t="n">
         <v>2</v>
@@ -14173,10 +14396,10 @@
         <v>2</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="14" t="n">
@@ -14186,12 +14409,12 @@
         <v>0</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="B19" s="11" t="n">
         <v>2</v>
@@ -14200,13 +14423,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>15</v>
@@ -14218,7 +14441,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="B20" s="11" t="n">
         <v>2</v>
@@ -14227,13 +14450,13 @@
         <v>4</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="G20" s="14" t="n">
         <v>16</v>
@@ -14242,12 +14465,12 @@
         <v>20</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B21" s="11" t="n">
         <v>2</v>
@@ -14256,13 +14479,13 @@
         <v>5</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>17</v>
@@ -14274,7 +14497,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B22" s="11" t="n">
         <v>2</v>
@@ -14283,13 +14506,13 @@
         <v>6</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>18</v>
@@ -14301,7 +14524,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B23" s="11" t="n">
         <v>2</v>
@@ -14310,13 +14533,13 @@
         <v>7</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>19</v>
@@ -14325,12 +14548,12 @@
         <v>20</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="B24" s="11" t="n">
         <v>2</v>
@@ -14339,13 +14562,13 @@
         <v>8</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>20</v>
@@ -14354,12 +14577,12 @@
         <v>20</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="B25" s="11" t="n">
         <v>2</v>
@@ -14368,13 +14591,13 @@
         <v>9</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>19</v>
@@ -14383,12 +14606,12 @@
         <v>20</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B26" s="11" t="n">
         <v>2</v>
@@ -14397,13 +14620,13 @@
         <v>10</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="G26" s="14" t="n">
         <v>20</v>
@@ -14415,7 +14638,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="B27" s="11" t="n">
         <v>2</v>
@@ -14424,13 +14647,13 @@
         <v>11</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>21</v>
@@ -14439,12 +14662,12 @@
         <v>20</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="B28" s="11" t="n">
         <v>2</v>
@@ -14453,13 +14676,13 @@
         <v>12</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>22</v>
@@ -14468,12 +14691,12 @@
         <v>20</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="B29" s="11" t="n">
         <v>2</v>
@@ -14482,13 +14705,13 @@
         <v>13</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>22</v>
@@ -14500,7 +14723,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="B30" s="11" t="n">
         <v>2</v>
@@ -14509,13 +14732,13 @@
         <v>14</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>23</v>
@@ -14527,7 +14750,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="B31" s="11" t="n">
         <v>2</v>
@@ -14536,13 +14759,13 @@
         <v>15</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>24</v>
@@ -14554,7 +14777,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="B32" s="11" t="n">
         <v>2</v>
@@ -14563,13 +14786,13 @@
         <v>16</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>24</v>
@@ -14578,12 +14801,12 @@
         <v>6</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="B33" s="11" t="n">
         <v>3</v>
@@ -14592,13 +14815,13 @@
         <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>25</v>
@@ -14610,7 +14833,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="B34" s="11" t="n">
         <v>3</v>
@@ -14619,10 +14842,10 @@
         <v>2</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="F34" s="11"/>
       <c r="G34" s="14" t="n">
@@ -14632,12 +14855,12 @@
         <v>0</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="B35" s="11" t="n">
         <v>3</v>
@@ -14646,13 +14869,13 @@
         <v>3</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>26</v>
@@ -14664,7 +14887,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="B36" s="11" t="n">
         <v>3</v>
@@ -14673,13 +14896,13 @@
         <v>4</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="G36" s="14" t="n">
         <v>27</v>
@@ -14688,12 +14911,12 @@
         <v>20</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="B37" s="11" t="n">
         <v>3</v>
@@ -14702,13 +14925,13 @@
         <v>5</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>28</v>
@@ -14717,12 +14940,12 @@
         <v>20</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="B38" s="11" t="n">
         <v>3</v>
@@ -14731,13 +14954,13 @@
         <v>6</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="G38" s="14" t="n">
         <v>29</v>
@@ -14746,12 +14969,12 @@
         <v>20</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B39" s="11" t="n">
         <v>3</v>
@@ -14760,13 +14983,13 @@
         <v>7</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>28</v>
@@ -14778,7 +15001,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B40" s="11" t="n">
         <v>3</v>
@@ -14787,13 +15010,13 @@
         <v>8</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>29</v>
@@ -14805,7 +15028,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B41" s="11" t="n">
         <v>3</v>
@@ -14814,13 +15037,13 @@
         <v>9</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>30</v>
@@ -14829,12 +15052,12 @@
         <v>20</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="B42" s="11" t="n">
         <v>3</v>
@@ -14843,13 +15066,13 @@
         <v>10</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="G42" s="14" t="n">
         <v>30</v>
@@ -14858,12 +15081,12 @@
         <v>6</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="B43" s="11" t="n">
         <v>3</v>
@@ -14872,13 +15095,13 @@
         <v>11</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>31</v>
@@ -14890,7 +15113,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B44" s="11" t="n">
         <v>3</v>
@@ -14899,13 +15122,13 @@
         <v>12</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="G44" s="14" t="n">
         <v>32</v>
@@ -14914,12 +15137,12 @@
         <v>20</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="B45" s="11" t="n">
         <v>3</v>
@@ -14928,13 +15151,13 @@
         <v>13</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="G45" s="14" t="n">
         <v>33</v>
@@ -14946,7 +15169,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="B46" s="11" t="n">
         <v>3</v>
@@ -14955,13 +15178,13 @@
         <v>14</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="G46" s="14" t="n">
         <v>34</v>
@@ -14970,12 +15193,12 @@
         <v>20</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="B47" s="11" t="n">
         <v>3</v>
@@ -14984,13 +15207,13 @@
         <v>15</v>
       </c>
       <c r="D47" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="F47" s="13" t="s">
         <v>400</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>294</v>
-      </c>
-      <c r="F47" s="13" t="s">
-        <v>391</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>35</v>
@@ -14999,12 +15222,12 @@
         <v>20</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="B48" s="11" t="n">
         <v>3</v>
@@ -15013,13 +15236,13 @@
         <v>16</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="G48" s="14" t="n">
         <v>35</v>
@@ -15031,7 +15254,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="B49" s="11" t="n">
         <v>3</v>
@@ -15040,13 +15263,13 @@
         <v>17</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>36</v>
@@ -15055,7 +15278,7 @@
         <v>6</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15071,7 +15294,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="23" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -15084,13 +15307,13 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="24" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -15507,7 +15730,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15547,13 +15770,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="B3" s="20" t="s">
         <v>139</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -15572,13 +15795,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="B4" s="21" t="n">
         <v>6</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -15597,13 +15820,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="B5" s="26" t="n">
         <v>1.115</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -15622,13 +15845,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>1.2</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -15647,13 +15870,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="B7" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -15672,13 +15895,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="B8" s="27" t="n">
         <v>0.02</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -15697,13 +15920,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="B9" s="27" t="n">
         <v>0.003</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -15722,13 +15945,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="B10" s="14" t="n">
         <v>4</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -15747,13 +15970,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="B11" s="14" t="n">
         <v>12</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -15772,7 +15995,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="B12" s="14" t="n">
         <v>20</v>
@@ -15795,13 +16018,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="B13" s="21" t="n">
         <v>2.5</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -15820,13 +16043,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="B14" s="14" t="n">
         <v>15</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -15845,7 +16068,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="B15" s="28" t="n">
         <f aca="false">INDEX(귀신!$F:$F,MATCH($B$3,귀신!$A:$A,0))</f>
@@ -15869,7 +16092,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="B16" s="28" t="n">
         <f aca="false">INDEX(귀신!$G:$G,MATCH($B$3,귀신!$A:$A,0))</f>
@@ -15893,7 +16116,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="B17" s="29" t="n">
         <f aca="false">INDEX(귀신!$H:$H,MATCH($B$3,귀신!$A:$A,0))</f>
@@ -15917,7 +16140,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B18" s="28" t="n">
         <f aca="false">INDEX(귀신!$J:$J,MATCH($B$3,귀신!$A:$A,0))</f>
@@ -15966,25 +16189,25 @@
         <v>116</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="E20" s="30" t="s">
         <v>221</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="G20" s="30" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="H20" s="30" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="I20" s="30" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="J20" s="30" t="s">
         <v>118</v>
@@ -15993,22 +16216,22 @@
         <v>131</v>
       </c>
       <c r="L20" s="30" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="M20" s="30" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="N20" s="30" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="O20" s="30" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="P20" s="30" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="Q20" s="31" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Docs/Balance/귀살_밸런스.xlsx
+++ b/Docs/Balance/귀살_밸런스.xlsx
@@ -14,7 +14,8 @@
     <sheet name="귀신" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="옵션" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="지역" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="전투시뮬" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="용병" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="전투시뮬" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -853,8 +854,270 @@
 </comments>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">레벨 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">기준</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">. </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">실제 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">= BaseHealth + HealthPerLevel × </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">레벨 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">+ </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">장비 체력</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">레벨 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">기준 무기 평균 피해</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">. </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">실제 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">= </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">이 값 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">× </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">무기 피해 성장 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">전투시뮬의 무기 피해 성장 가정과 같은 방식</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">). </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">목표는 플레이어 피해의 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">20~30%</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">고용 비용</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">엽전</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">) = </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">이 값 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">× </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">플레이어 레벨</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="499">
   <si>
     <r>
       <rPr>
@@ -1518,6 +1781,104 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">용병</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용병 종류</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">성향별 기본 체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무기 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공격 간격</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고용 비용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">게임으로 내보내는 시트</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">전투시뮬</t>
   </si>
   <si>
@@ -1802,6 +2163,23 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용병</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">)</t>
     </r>
     <r>
@@ -3130,6 +3508,185 @@
     <t xml:space="preserve">최대 플레이어 레벨</t>
   </si>
   <si>
+    <t xml:space="preserve">SummonCap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마리</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">소환물 최대 동시 수 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">성능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">AllyEntityCap</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아군 개체 최대 수 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">소환물 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용병</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">MercReviveSeconds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">초</t>
+  </si>
+  <si>
+    <t xml:space="preserve">용병이 쓰러진 뒤 자동 부활까지 걸리는 시간</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MercDamageShareTarget</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">목표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용병 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">플레이어 피해의 이 비율 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(20~30%)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">RiftAreaLevelBase</t>
   </si>
   <si>
@@ -5287,6 +5844,342 @@
   </si>
   <si>
     <t xml:space="preserve">BossMonsterLevel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UnlockAct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BaseWeaponDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HireCostPerLevel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunter_archer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">착호갑사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">사수</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">활 연사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">맞은 적 둔화</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">hunter_gunner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포수</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화승총</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일직선 관통</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">swordsman_shield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">떠돌이 검객</t>
+  </si>
+  <si>
+    <t xml:space="preserve">등패수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근접 탱커</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">도발</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">귀신의 공격을 끌어들임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단단함</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">swordsman_dual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">살수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근접 딜러</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">쌍검 빠른 연타</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주변 베기</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">healer_acupuncture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">의원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">침술사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회복</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주기적 플레이어 회복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">위급 시 큰 회복</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">healer_herbalist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">약초꾼</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">버프</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">독</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">탕약 버프</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공격력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이동 속도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적에게 독</t>
+    </r>
   </si>
   <si>
     <r>
@@ -7606,11 +8499,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="21919977"/>
-        <c:axId val="28314007"/>
+        <c:axId val="55042150"/>
+        <c:axId val="89022049"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="21919977"/>
+        <c:axId val="55042150"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7676,7 +8569,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28314007"/>
+        <c:crossAx val="89022049"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7684,7 +8577,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28314007"/>
+        <c:axId val="89022049"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7760,7 +8653,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21919977"/>
+        <c:crossAx val="55042150"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8608,11 +9501,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="32089847"/>
-        <c:axId val="22183460"/>
+        <c:axId val="34178072"/>
+        <c:axId val="59234441"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="32089847"/>
+        <c:axId val="34178072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8678,7 +9571,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22183460"/>
+        <c:crossAx val="59234441"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8686,7 +9579,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="22183460"/>
+        <c:axId val="59234441"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8762,7 +9655,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32089847"/>
+        <c:crossAx val="34178072"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9059,7 +9952,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -9168,7 +10061,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
@@ -9176,25 +10069,25 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3"/>
-      <c r="B17" s="7"/>
+    <row r="17" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>23</v>
-      </c>
+      <c r="A18" s="3"/>
       <c r="B18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="7" t="s">
+      <c r="A19" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
         <v>26</v>
       </c>
@@ -9206,36 +10099,44 @@
       <c r="A21" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3"/>
-      <c r="B23" s="7"/>
-    </row>
-    <row r="24" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
+      <c r="A23" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B23" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3"/>
+      <c r="B24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
         <v>34</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -9254,7 +10155,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -9265,494 +10166,550 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B2" s="12" t="n">
         <v>1.12</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>1.09</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" s="14" t="n">
         <v>15</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B5" s="14" t="n">
         <v>50</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>0.85</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B8" s="15" t="n">
         <v>0.8</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B9" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>0.05</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B12" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B13" s="15" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B14" s="15" t="n">
         <v>0.4</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B15" s="15" t="n">
         <v>0.4</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B16" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B17" s="15" t="n">
         <v>0.03</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B18" s="15" t="n">
         <v>0.45</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B19" s="14" t="n">
         <v>100</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B20" s="14" t="n">
         <v>10</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B21" s="14" t="n">
         <v>100</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B22" s="14" t="n">
         <v>2</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B23" s="14" t="n">
         <v>5</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B24" s="14" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B25" s="14" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>3</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B28" s="14" t="n">
         <v>2</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B29" s="14" t="n">
         <v>3</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B30" s="14" t="n">
         <v>250</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B31" s="14" t="n">
         <v>100</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B32" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B33" s="14" t="n">
         <v>5</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B34" s="12" t="n">
         <v>0.2</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B35" s="14" t="n">
         <v>50</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B36" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="C36" s="11"/>
+        <v>6</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>114</v>
+      </c>
       <c r="D36" s="13" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B37" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" s="15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C40" s="11"/>
+      <c r="D40" s="13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B41" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="11"/>
-      <c r="D37" s="13" t="s">
-        <v>114</v>
+      <c r="C41" s="11"/>
+      <c r="D41" s="13" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -9785,28 +10742,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11661,72 +12618,72 @@
   <sheetData>
     <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="N1" s="16" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="O1" s="16" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="P1" s="16" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="D2" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="F2" s="20" t="n">
         <v>30</v>
@@ -11738,7 +12695,7 @@
         <v>1.5</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="J2" s="20" t="n">
         <v>5</v>
@@ -11762,24 +12719,24 @@
         <v>50</v>
       </c>
       <c r="Q2" s="13" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="F3" s="20" t="n">
         <v>24</v>
@@ -11791,7 +12748,7 @@
         <v>1.2</v>
       </c>
       <c r="I3" s="20" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="J3" s="20" t="n">
         <v>3</v>
@@ -11818,19 +12775,19 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="F4" s="20" t="n">
         <v>36</v>
@@ -11842,7 +12799,7 @@
         <v>1.5</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="J4" s="20" t="n">
         <v>5</v>
@@ -11866,24 +12823,24 @@
         <v>65</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="F5" s="20" t="n">
         <v>18</v>
@@ -11895,7 +12852,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="J5" s="20" t="n">
         <v>2</v>
@@ -11919,24 +12876,24 @@
         <v>35</v>
       </c>
       <c r="Q5" s="13" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="F6" s="20" t="n">
         <v>20</v>
@@ -11948,7 +12905,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J6" s="20" t="n">
         <v>0</v>
@@ -11972,24 +12929,24 @@
         <v>45</v>
       </c>
       <c r="Q6" s="13" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="F7" s="20" t="n">
         <v>90</v>
@@ -12001,7 +12958,7 @@
         <v>2.5</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="J7" s="20" t="n">
         <v>25</v>
@@ -12025,24 +12982,24 @@
         <v>120</v>
       </c>
       <c r="Q7" s="13" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="F8" s="20" t="n">
         <v>120</v>
@@ -12054,7 +13011,7 @@
         <v>2.5</v>
       </c>
       <c r="I8" s="20" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="J8" s="20" t="n">
         <v>40</v>
@@ -12081,19 +13038,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F9" s="20" t="n">
         <v>80</v>
@@ -12105,7 +13062,7 @@
         <v>1.5</v>
       </c>
       <c r="I9" s="20" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="J9" s="20" t="n">
         <v>10</v>
@@ -12129,24 +13086,24 @@
         <v>200</v>
       </c>
       <c r="Q9" s="13" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="F10" s="20" t="n">
         <v>1500</v>
@@ -12158,7 +13115,7 @@
         <v>1.8</v>
       </c>
       <c r="I10" s="20" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="J10" s="20" t="n">
         <v>30</v>
@@ -12182,7 +13139,7 @@
         <v>2000</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -12216,78 +13173,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="N1" s="16" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="O1" s="16" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="P1" s="16" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="R1" s="16" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="S1" s="16" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="T1" s="16" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E2" s="14" t="n">
         <v>1</v>
@@ -12313,35 +13270,35 @@
       <c r="L2" s="22"/>
       <c r="M2" s="22"/>
       <c r="N2" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="O2" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="P2" s="22"/>
       <c r="Q2" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="R2" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="S2" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="T2" s="22"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>1</v>
@@ -12365,35 +13322,35 @@
         <v>0.2</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="22"/>
       <c r="O3" s="22"/>
       <c r="P3" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="Q3" s="22"/>
       <c r="R3" s="22"/>
       <c r="S3" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="T3" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E4" s="14" t="n">
         <v>1</v>
@@ -12417,7 +13374,7 @@
         <v>0.8</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
@@ -12430,16 +13387,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E5" s="14" t="n">
         <v>5</v>
@@ -12464,7 +13421,7 @@
       </c>
       <c r="L5" s="22"/>
       <c r="M5" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="N5" s="22"/>
       <c r="O5" s="22"/>
@@ -12472,22 +13429,22 @@
       <c r="Q5" s="22"/>
       <c r="R5" s="22"/>
       <c r="S5" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="T5" s="22"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E6" s="14" t="n">
         <v>5</v>
@@ -12512,7 +13469,7 @@
       </c>
       <c r="L6" s="22"/>
       <c r="M6" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="N6" s="22"/>
       <c r="O6" s="22"/>
@@ -12520,22 +13477,22 @@
       <c r="Q6" s="22"/>
       <c r="R6" s="22"/>
       <c r="S6" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="T6" s="22"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E7" s="14" t="n">
         <v>5</v>
@@ -12559,7 +13516,7 @@
         <v>35</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="M7" s="22"/>
       <c r="N7" s="22"/>
@@ -12572,16 +13529,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>5</v>
@@ -12605,13 +13562,13 @@
         <v>0.15</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="M8" s="22"/>
       <c r="N8" s="22"/>
       <c r="O8" s="22"/>
       <c r="P8" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="Q8" s="22"/>
       <c r="R8" s="22"/>
@@ -12620,16 +13577,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>5</v>
@@ -12657,29 +13614,29 @@
       <c r="N9" s="22"/>
       <c r="O9" s="22"/>
       <c r="P9" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="Q9" s="22"/>
       <c r="R9" s="22"/>
       <c r="S9" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="T9" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>5</v>
@@ -12703,7 +13660,7 @@
         <v>0.35</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -12712,24 +13669,24 @@
       <c r="Q10" s="22"/>
       <c r="R10" s="22"/>
       <c r="S10" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="T10" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>1</v>
@@ -12755,33 +13712,33 @@
       <c r="L11" s="22"/>
       <c r="M11" s="22"/>
       <c r="N11" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="O11" s="22"/>
       <c r="P11" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="Q11" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="R11" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="S11" s="22"/>
       <c r="T11" s="22"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>1</v>
@@ -12808,7 +13765,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
       <c r="O12" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="P12" s="22"/>
       <c r="Q12" s="22"/>
@@ -12818,16 +13775,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>1</v>
@@ -12853,37 +13810,37 @@
       <c r="L13" s="22"/>
       <c r="M13" s="22"/>
       <c r="N13" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="O13" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="P13" s="22"/>
       <c r="Q13" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="R13" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="S13" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="T13" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>1</v>
@@ -12909,37 +13866,37 @@
       <c r="L14" s="22"/>
       <c r="M14" s="22"/>
       <c r="N14" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="O14" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="P14" s="22"/>
       <c r="Q14" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="R14" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="S14" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="T14" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E15" s="14" t="n">
         <v>1</v>
@@ -12965,37 +13922,37 @@
       <c r="L15" s="22"/>
       <c r="M15" s="22"/>
       <c r="N15" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="O15" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="P15" s="22"/>
       <c r="Q15" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="R15" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="S15" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="T15" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>1</v>
@@ -13021,37 +13978,37 @@
       <c r="L16" s="22"/>
       <c r="M16" s="22"/>
       <c r="N16" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="O16" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="P16" s="22"/>
       <c r="Q16" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="R16" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="S16" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="T16" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>15</v>
@@ -13082,22 +14039,22 @@
       <c r="Q17" s="22"/>
       <c r="R17" s="22"/>
       <c r="S17" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="T17" s="22"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E18" s="14" t="n">
         <v>10</v>
@@ -13124,7 +14081,7 @@
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
       <c r="O18" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="P18" s="22"/>
       <c r="Q18" s="22"/>
@@ -13134,16 +14091,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>1</v>
@@ -13170,7 +14127,7 @@
       <c r="M19" s="22"/>
       <c r="N19" s="22"/>
       <c r="O19" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="P19" s="22"/>
       <c r="Q19" s="22"/>
@@ -13180,16 +14137,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E20" s="14" t="n">
         <v>1</v>
@@ -13213,7 +14170,7 @@
         <v>25</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
@@ -13226,16 +14183,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E21" s="14" t="n">
         <v>5</v>
@@ -13259,13 +14216,13 @@
         <v>5</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="M21" s="22"/>
       <c r="N21" s="22"/>
       <c r="O21" s="22"/>
       <c r="P21" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="Q21" s="22"/>
       <c r="R21" s="22"/>
@@ -13274,16 +14231,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E22" s="14" t="n">
         <v>5</v>
@@ -13308,7 +14265,7 @@
       </c>
       <c r="L22" s="22"/>
       <c r="M22" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="N22" s="22"/>
       <c r="O22" s="22"/>
@@ -13316,22 +14273,22 @@
       <c r="Q22" s="22"/>
       <c r="R22" s="22"/>
       <c r="S22" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="T22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E23" s="14" t="n">
         <v>5</v>
@@ -13356,7 +14313,7 @@
       </c>
       <c r="L23" s="22"/>
       <c r="M23" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="N23" s="22"/>
       <c r="O23" s="22"/>
@@ -13364,22 +14321,22 @@
       <c r="Q23" s="22"/>
       <c r="R23" s="22"/>
       <c r="S23" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="T23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E24" s="14" t="n">
         <v>10</v>
@@ -13404,7 +14361,7 @@
       </c>
       <c r="L24" s="22"/>
       <c r="M24" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="N24" s="22"/>
       <c r="O24" s="22"/>
@@ -13416,16 +14373,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E25" s="14" t="n">
         <v>1</v>
@@ -13451,29 +14408,29 @@
       <c r="L25" s="22"/>
       <c r="M25" s="22"/>
       <c r="N25" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="O25" s="22"/>
       <c r="P25" s="22"/>
       <c r="Q25" s="22"/>
       <c r="R25" s="22"/>
       <c r="S25" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="T25" s="22"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E26" s="14" t="n">
         <v>5</v>
@@ -13504,24 +14461,24 @@
       <c r="Q26" s="22"/>
       <c r="R26" s="22"/>
       <c r="S26" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="T26" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E27" s="14" t="n">
         <v>10</v>
@@ -13546,7 +14503,7 @@
       </c>
       <c r="L27" s="22"/>
       <c r="M27" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="N27" s="22"/>
       <c r="O27" s="22"/>
@@ -13558,16 +14515,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E28" s="14" t="n">
         <v>10</v>
@@ -13592,10 +14549,10 @@
       </c>
       <c r="L28" s="22"/>
       <c r="M28" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="N28" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="O28" s="22"/>
       <c r="P28" s="22"/>
@@ -13606,16 +14563,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E29" s="14" t="n">
         <v>1</v>
@@ -13645,23 +14602,23 @@
       <c r="P29" s="22"/>
       <c r="Q29" s="22"/>
       <c r="R29" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="S29" s="22"/>
       <c r="T29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E30" s="14" t="n">
         <v>5</v>
@@ -13690,7 +14647,7 @@
       <c r="O30" s="22"/>
       <c r="P30" s="22"/>
       <c r="Q30" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="R30" s="22"/>
       <c r="S30" s="22"/>
@@ -13698,16 +14655,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E31" s="14" t="n">
         <v>5</v>
@@ -13739,21 +14696,21 @@
       <c r="R31" s="22"/>
       <c r="S31" s="22"/>
       <c r="T31" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E32" s="14" t="n">
         <v>1</v>
@@ -13785,21 +14742,21 @@
       <c r="R32" s="22"/>
       <c r="S32" s="22"/>
       <c r="T32" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E33" s="14" t="n">
         <v>20</v>
@@ -13830,22 +14787,22 @@
       <c r="Q33" s="22"/>
       <c r="R33" s="22"/>
       <c r="S33" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="T33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E34" s="14" t="n">
         <v>30</v>
@@ -13872,7 +14829,7 @@
       <c r="M34" s="22"/>
       <c r="N34" s="22"/>
       <c r="O34" s="22" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="P34" s="22"/>
       <c r="Q34" s="22"/>
@@ -13912,36 +14869,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="B2" s="11" t="n">
         <v>1</v>
@@ -13950,13 +14907,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="G2" s="14" t="n">
         <v>1</v>
@@ -13965,12 +14922,12 @@
         <v>6</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="B3" s="11" t="n">
         <v>1</v>
@@ -13979,13 +14936,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="G3" s="14" t="n">
         <v>2</v>
@@ -13997,7 +14954,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>1</v>
@@ -14006,13 +14963,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="G4" s="14" t="n">
         <v>3</v>
@@ -14024,7 +14981,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>1</v>
@@ -14033,10 +14990,10 @@
         <v>4</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="F5" s="11"/>
       <c r="G5" s="14" t="n">
@@ -14046,12 +15003,12 @@
         <v>6</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>1</v>
@@ -14060,13 +15017,13 @@
         <v>5</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>5</v>
@@ -14078,7 +15035,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>1</v>
@@ -14087,13 +15044,13 @@
         <v>6</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>6</v>
@@ -14102,12 +15059,12 @@
         <v>20</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>1</v>
@@ -14116,13 +15073,13 @@
         <v>7</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>7</v>
@@ -14134,7 +15091,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>1</v>
@@ -14143,13 +15100,13 @@
         <v>8</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>8</v>
@@ -14158,12 +15115,12 @@
         <v>20</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>1</v>
@@ -14172,13 +15129,13 @@
         <v>9</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>9</v>
@@ -14187,12 +15144,12 @@
         <v>20</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="B11" s="11" t="n">
         <v>1</v>
@@ -14201,13 +15158,13 @@
         <v>10</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>9</v>
@@ -14219,7 +15176,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B12" s="11" t="n">
         <v>1</v>
@@ -14228,13 +15185,13 @@
         <v>11</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>10</v>
@@ -14246,7 +15203,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B13" s="11" t="n">
         <v>1</v>
@@ -14255,13 +15212,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>11</v>
@@ -14270,12 +15227,12 @@
         <v>20</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="B14" s="11" t="n">
         <v>1</v>
@@ -14284,13 +15241,13 @@
         <v>13</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>12</v>
@@ -14299,12 +15256,12 @@
         <v>20</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="B15" s="11" t="n">
         <v>1</v>
@@ -14313,13 +15270,13 @@
         <v>14</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>12</v>
@@ -14331,7 +15288,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>1</v>
@@ -14340,13 +15297,13 @@
         <v>15</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>13</v>
@@ -14355,12 +15312,12 @@
         <v>6</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B17" s="11" t="n">
         <v>2</v>
@@ -14369,13 +15326,13 @@
         <v>1</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>14</v>
@@ -14387,7 +15344,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B18" s="11" t="n">
         <v>2</v>
@@ -14396,10 +15353,10 @@
         <v>2</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="14" t="n">
@@ -14409,12 +15366,12 @@
         <v>0</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="B19" s="11" t="n">
         <v>2</v>
@@ -14423,13 +15380,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>15</v>
@@ -14441,7 +15398,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B20" s="11" t="n">
         <v>2</v>
@@ -14450,13 +15407,13 @@
         <v>4</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="G20" s="14" t="n">
         <v>16</v>
@@ -14465,12 +15422,12 @@
         <v>20</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B21" s="11" t="n">
         <v>2</v>
@@ -14479,13 +15436,13 @@
         <v>5</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>17</v>
@@ -14497,7 +15454,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B22" s="11" t="n">
         <v>2</v>
@@ -14506,13 +15463,13 @@
         <v>6</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>18</v>
@@ -14524,7 +15481,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="B23" s="11" t="n">
         <v>2</v>
@@ -14533,13 +15490,13 @@
         <v>7</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>19</v>
@@ -14548,12 +15505,12 @@
         <v>20</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B24" s="11" t="n">
         <v>2</v>
@@ -14562,13 +15519,13 @@
         <v>8</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>20</v>
@@ -14577,12 +15534,12 @@
         <v>20</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="B25" s="11" t="n">
         <v>2</v>
@@ -14591,13 +15548,13 @@
         <v>9</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>19</v>
@@ -14606,12 +15563,12 @@
         <v>20</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="B26" s="11" t="n">
         <v>2</v>
@@ -14620,13 +15577,13 @@
         <v>10</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="G26" s="14" t="n">
         <v>20</v>
@@ -14638,7 +15595,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B27" s="11" t="n">
         <v>2</v>
@@ -14647,13 +15604,13 @@
         <v>11</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>21</v>
@@ -14662,12 +15619,12 @@
         <v>20</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="B28" s="11" t="n">
         <v>2</v>
@@ -14676,13 +15633,13 @@
         <v>12</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>22</v>
@@ -14691,12 +15648,12 @@
         <v>20</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="B29" s="11" t="n">
         <v>2</v>
@@ -14705,13 +15662,13 @@
         <v>13</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>22</v>
@@ -14723,7 +15680,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="B30" s="11" t="n">
         <v>2</v>
@@ -14732,13 +15689,13 @@
         <v>14</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>23</v>
@@ -14750,7 +15707,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="B31" s="11" t="n">
         <v>2</v>
@@ -14759,13 +15716,13 @@
         <v>15</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>24</v>
@@ -14777,7 +15734,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="B32" s="11" t="n">
         <v>2</v>
@@ -14786,13 +15743,13 @@
         <v>16</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>24</v>
@@ -14801,12 +15758,12 @@
         <v>6</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="B33" s="11" t="n">
         <v>3</v>
@@ -14815,13 +15772,13 @@
         <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>25</v>
@@ -14833,7 +15790,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="B34" s="11" t="n">
         <v>3</v>
@@ -14842,10 +15799,10 @@
         <v>2</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="F34" s="11"/>
       <c r="G34" s="14" t="n">
@@ -14855,12 +15812,12 @@
         <v>0</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="B35" s="11" t="n">
         <v>3</v>
@@ -14869,13 +15826,13 @@
         <v>3</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>26</v>
@@ -14887,7 +15844,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="B36" s="11" t="n">
         <v>3</v>
@@ -14896,13 +15853,13 @@
         <v>4</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="G36" s="14" t="n">
         <v>27</v>
@@ -14911,12 +15868,12 @@
         <v>20</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="B37" s="11" t="n">
         <v>3</v>
@@ -14925,13 +15882,13 @@
         <v>5</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>28</v>
@@ -14940,12 +15897,12 @@
         <v>20</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="B38" s="11" t="n">
         <v>3</v>
@@ -14954,13 +15911,13 @@
         <v>6</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="G38" s="14" t="n">
         <v>29</v>
@@ -14969,12 +15926,12 @@
         <v>20</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="B39" s="11" t="n">
         <v>3</v>
@@ -14983,13 +15940,13 @@
         <v>7</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>28</v>
@@ -15001,7 +15958,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="B40" s="11" t="n">
         <v>3</v>
@@ -15010,13 +15967,13 @@
         <v>8</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>29</v>
@@ -15028,7 +15985,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="B41" s="11" t="n">
         <v>3</v>
@@ -15037,13 +15994,13 @@
         <v>9</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>30</v>
@@ -15052,12 +16009,12 @@
         <v>20</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="B42" s="11" t="n">
         <v>3</v>
@@ -15066,13 +16023,13 @@
         <v>10</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="G42" s="14" t="n">
         <v>30</v>
@@ -15081,12 +16038,12 @@
         <v>6</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="B43" s="11" t="n">
         <v>3</v>
@@ -15095,13 +16052,13 @@
         <v>11</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>31</v>
@@ -15113,7 +16070,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="B44" s="11" t="n">
         <v>3</v>
@@ -15122,13 +16079,13 @@
         <v>12</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="G44" s="14" t="n">
         <v>32</v>
@@ -15137,12 +16094,12 @@
         <v>20</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="B45" s="11" t="n">
         <v>3</v>
@@ -15151,13 +16108,13 @@
         <v>13</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="G45" s="14" t="n">
         <v>33</v>
@@ -15169,7 +16126,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="B46" s="11" t="n">
         <v>3</v>
@@ -15178,13 +16135,13 @@
         <v>14</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="G46" s="14" t="n">
         <v>34</v>
@@ -15193,12 +16150,12 @@
         <v>20</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="B47" s="11" t="n">
         <v>3</v>
@@ -15207,13 +16164,13 @@
         <v>15</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>35</v>
@@ -15222,12 +16179,12 @@
         <v>20</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="B48" s="11" t="n">
         <v>3</v>
@@ -15236,13 +16193,13 @@
         <v>16</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="G48" s="14" t="n">
         <v>35</v>
@@ -15254,7 +16211,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="B49" s="11" t="n">
         <v>3</v>
@@ -15263,13 +16220,13 @@
         <v>17</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>36</v>
@@ -15278,7 +16235,7 @@
         <v>6</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15294,7 +16251,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="23" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -15307,13 +16264,13 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="24" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -15327,7 +16284,7 @@
         <v>1</v>
       </c>
       <c r="B53" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A53</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A53</f>
         <v>14</v>
       </c>
       <c r="C53" s="18" t="n">
@@ -15346,7 +16303,7 @@
         <v>2</v>
       </c>
       <c r="B54" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A54</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A54</f>
         <v>16</v>
       </c>
       <c r="C54" s="18" t="n">
@@ -15365,7 +16322,7 @@
         <v>3</v>
       </c>
       <c r="B55" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A55</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A55</f>
         <v>18</v>
       </c>
       <c r="C55" s="18" t="n">
@@ -15384,7 +16341,7 @@
         <v>4</v>
       </c>
       <c r="B56" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A56</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A56</f>
         <v>20</v>
       </c>
       <c r="C56" s="18" t="n">
@@ -15403,7 +16360,7 @@
         <v>5</v>
       </c>
       <c r="B57" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A57</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A57</f>
         <v>22</v>
       </c>
       <c r="C57" s="18" t="n">
@@ -15422,7 +16379,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A58</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A58</f>
         <v>24</v>
       </c>
       <c r="C58" s="18" t="n">
@@ -15441,7 +16398,7 @@
         <v>7</v>
       </c>
       <c r="B59" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A59</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A59</f>
         <v>26</v>
       </c>
       <c r="C59" s="18" t="n">
@@ -15460,7 +16417,7 @@
         <v>8</v>
       </c>
       <c r="B60" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A60</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A60</f>
         <v>28</v>
       </c>
       <c r="C60" s="18" t="n">
@@ -15479,7 +16436,7 @@
         <v>9</v>
       </c>
       <c r="B61" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A61</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A61</f>
         <v>30</v>
       </c>
       <c r="C61" s="18" t="n">
@@ -15498,7 +16455,7 @@
         <v>10</v>
       </c>
       <c r="B62" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A62</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A62</f>
         <v>32</v>
       </c>
       <c r="C62" s="18" t="n">
@@ -15517,7 +16474,7 @@
         <v>11</v>
       </c>
       <c r="B63" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A63</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A63</f>
         <v>34</v>
       </c>
       <c r="C63" s="18" t="n">
@@ -15536,7 +16493,7 @@
         <v>12</v>
       </c>
       <c r="B64" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A64</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A64</f>
         <v>36</v>
       </c>
       <c r="C64" s="18" t="n">
@@ -15555,7 +16512,7 @@
         <v>13</v>
       </c>
       <c r="B65" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A65</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A65</f>
         <v>38</v>
       </c>
       <c r="C65" s="18" t="n">
@@ -15574,7 +16531,7 @@
         <v>14</v>
       </c>
       <c r="B66" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A66</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A66</f>
         <v>40</v>
       </c>
       <c r="C66" s="18" t="n">
@@ -15593,7 +16550,7 @@
         <v>15</v>
       </c>
       <c r="B67" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A67</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A67</f>
         <v>42</v>
       </c>
       <c r="C67" s="18" t="n">
@@ -15612,7 +16569,7 @@
         <v>16</v>
       </c>
       <c r="B68" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A68</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A68</f>
         <v>44</v>
       </c>
       <c r="C68" s="18" t="n">
@@ -15631,7 +16588,7 @@
         <v>17</v>
       </c>
       <c r="B69" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A69</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A69</f>
         <v>46</v>
       </c>
       <c r="C69" s="18" t="n">
@@ -15650,7 +16607,7 @@
         <v>18</v>
       </c>
       <c r="B70" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A70</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A70</f>
         <v>48</v>
       </c>
       <c r="C70" s="18" t="n">
@@ -15669,7 +16626,7 @@
         <v>19</v>
       </c>
       <c r="B71" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A71</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A71</f>
         <v>50</v>
       </c>
       <c r="C71" s="18" t="n">
@@ -15688,7 +16645,7 @@
         <v>20</v>
       </c>
       <c r="B72" s="18" t="n">
-        <f aca="false">상수!$B$36+상수!$B$37*A72</f>
+        <f aca="false">상수!$B$40+상수!$B$41*A72</f>
         <v>52</v>
       </c>
       <c r="C72" s="18" t="n">
@@ -15719,6 +16676,327 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2" s="20" t="n">
+        <v>80</v>
+      </c>
+      <c r="G2" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" s="21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="K2" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="L2" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="F3" s="20" t="n">
+        <v>80</v>
+      </c>
+      <c r="G3" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="K3" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="L3" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="F4" s="20" t="n">
+        <v>140</v>
+      </c>
+      <c r="G4" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="K4" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>448</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>110</v>
+      </c>
+      <c r="G5" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="H5" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="K5" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="M5" s="13" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>452</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>454</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="G6" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H6" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="K6" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>452</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>458</v>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="G7" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="K7" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="L7" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>459</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:Q70"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -15730,7 +17008,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>418</v>
+        <v>460</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15770,13 +17048,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>419</v>
+        <v>461</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>420</v>
+        <v>462</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -15795,13 +17073,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>421</v>
+        <v>463</v>
       </c>
       <c r="B4" s="21" t="n">
         <v>6</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>422</v>
+        <v>464</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -15820,13 +17098,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>423</v>
+        <v>465</v>
       </c>
       <c r="B5" s="26" t="n">
         <v>1.115</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>424</v>
+        <v>466</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -15845,13 +17123,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>425</v>
+        <v>467</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>1.2</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>426</v>
+        <v>468</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -15870,13 +17148,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>427</v>
+        <v>469</v>
       </c>
       <c r="B7" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>428</v>
+        <v>470</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -15895,13 +17173,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>429</v>
+        <v>471</v>
       </c>
       <c r="B8" s="27" t="n">
         <v>0.02</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>430</v>
+        <v>472</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -15920,13 +17198,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>431</v>
+        <v>473</v>
       </c>
       <c r="B9" s="27" t="n">
         <v>0.003</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>432</v>
+        <v>474</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -15945,13 +17223,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>433</v>
+        <v>475</v>
       </c>
       <c r="B10" s="14" t="n">
         <v>4</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>434</v>
+        <v>476</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -15970,13 +17248,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>435</v>
+        <v>477</v>
       </c>
       <c r="B11" s="14" t="n">
         <v>12</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>436</v>
+        <v>478</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -15995,7 +17273,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>437</v>
+        <v>479</v>
       </c>
       <c r="B12" s="14" t="n">
         <v>20</v>
@@ -16018,13 +17296,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>438</v>
+        <v>480</v>
       </c>
       <c r="B13" s="21" t="n">
         <v>2.5</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>439</v>
+        <v>481</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -16043,13 +17321,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>440</v>
+        <v>482</v>
       </c>
       <c r="B14" s="14" t="n">
         <v>15</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>439</v>
+        <v>481</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -16068,7 +17346,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>441</v>
+        <v>483</v>
       </c>
       <c r="B15" s="28" t="n">
         <f aca="false">INDEX(귀신!$F:$F,MATCH($B$3,귀신!$A:$A,0))</f>
@@ -16092,7 +17370,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>442</v>
+        <v>484</v>
       </c>
       <c r="B16" s="28" t="n">
         <f aca="false">INDEX(귀신!$G:$G,MATCH($B$3,귀신!$A:$A,0))</f>
@@ -16116,7 +17394,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>443</v>
+        <v>485</v>
       </c>
       <c r="B17" s="29" t="n">
         <f aca="false">INDEX(귀신!$H:$H,MATCH($B$3,귀신!$A:$A,0))</f>
@@ -16140,7 +17418,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>444</v>
+        <v>486</v>
       </c>
       <c r="B18" s="28" t="n">
         <f aca="false">INDEX(귀신!$J:$J,MATCH($B$3,귀신!$A:$A,0))</f>
@@ -16183,55 +17461,55 @@
     </row>
     <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="30" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>445</v>
+        <v>487</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>446</v>
+        <v>488</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>447</v>
+        <v>489</v>
       </c>
       <c r="G20" s="30" t="s">
-        <v>448</v>
+        <v>490</v>
       </c>
       <c r="H20" s="30" t="s">
-        <v>449</v>
+        <v>491</v>
       </c>
       <c r="I20" s="30" t="s">
-        <v>450</v>
+        <v>492</v>
       </c>
       <c r="J20" s="30" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="K20" s="30" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="L20" s="30" t="s">
-        <v>451</v>
+        <v>493</v>
       </c>
       <c r="M20" s="30" t="s">
-        <v>452</v>
+        <v>494</v>
       </c>
       <c r="N20" s="30" t="s">
-        <v>453</v>
+        <v>495</v>
       </c>
       <c r="O20" s="30" t="s">
-        <v>454</v>
+        <v>496</v>
       </c>
       <c r="P20" s="30" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="Q20" s="31" t="s">
-        <v>456</v>
+        <v>498</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Docs/Balance/귀살_밸런스.xlsx
+++ b/Docs/Balance/귀살_밸런스.xlsx
@@ -18,8 +18,10 @@
     <sheet name="드랍" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="등급확률" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="경제" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="경제시뮬" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="전투시뮬" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="난이도" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="균열" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="경제시뮬" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="전투시뮬" sheetId="14" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,6 +33,314 @@
 </file>
 
 <file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">지역 레벨 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">= max(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">원래 지역 레벨</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">플레이어 레벨 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">+ </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">이 값</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">). </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">빈칸 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">= </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">보정 없음</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">모든 저항에 더하는 값 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(−20% = </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">저항 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">20%p </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">감소</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments12.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">균열 주인이 나타나기까지 필요한 원한 게이지 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">일반 귀신 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">1 = 1</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">점</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">정예 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">= 5</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">점</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">이름 있는 정예 </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">= 15</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">점 가정</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">이 단계의 상한을 여는 조건</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">. </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="WenQuanYi Zen Hei"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">상한 안에서는 시련 균열 성공으로 한 단계씩 해금</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments13.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Unknown Author</author>
@@ -1547,7 +1857,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="640">
   <si>
     <r>
       <rPr>
@@ -2586,6 +2896,236 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">난이도</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">세계 난이도 평시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">흉몽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">말세</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">해금 조건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">지역 레벨 보정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">저항 감점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보상 배율</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">게임으로 내보내는 시트</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">균열</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">귀문 균열 단계별 지역 레벨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원한 게이지 양</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시련 제한 시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">변형 개수 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">균열 변형 목록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">게임으로 내보내는 시트</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">경제시뮬</t>
   </si>
   <si>
@@ -3087,6 +3627,40 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">난이도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">균열</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">)</t>
     </r>
     <r>
@@ -8098,6 +8672,322 @@
   </si>
   <si>
     <t xml:space="preserve">무기가 떨어질 때 지금 직업이 쓸 수 있는 무기일 확률</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unlock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MinLevelOverPlayer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ResistPenalty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UniqueSetMult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExpMult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExtraEliteAffixes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">평시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">처음부터</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nightmare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">흉몽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">엔딩</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apocalypse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">말세</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시련 균열 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">단계</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GuardianLevel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HatredRequired</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TrialTimeLimitSec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ModifierCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UnlockedBy</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">막 클리어</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">막 클리어</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">균열 변형 목록</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ModId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">귀신이 빠름</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">귀신 이동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공격 속도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+25%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">poison_trail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">독 장판</t>
+  </si>
+  <si>
+    <t xml:space="preserve">죽은 귀신이 독 장판을 남김</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold_dokkaebi</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">금 도깨비 출현 확률 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×5</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">darkness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어둠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시야가 좁아짐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">double_hatred</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원한 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">원한 게이지 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배로 빨리 참</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">elite_pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정예 무리</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정예 출현 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×2</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">GoldPerNormalKill</t>
@@ -9351,6 +10241,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
@@ -9358,13 +10255,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="맑은 고딕"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF008000"/>
       <name val="맑은 고딕"/>
       <family val="0"/>
       <charset val="1"/>
@@ -9571,11 +10461,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="170" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9587,11 +10481,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9603,7 +10493,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10487,11 +11377,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="33971747"/>
-        <c:axId val="43927630"/>
+        <c:axId val="92772662"/>
+        <c:axId val="2059074"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="33971747"/>
+        <c:axId val="92772662"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10557,7 +11447,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43927630"/>
+        <c:crossAx val="2059074"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10565,7 +11455,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43927630"/>
+        <c:axId val="2059074"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10641,7 +11531,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33971747"/>
+        <c:crossAx val="92772662"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11489,11 +12379,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="22322214"/>
-        <c:axId val="89796400"/>
+        <c:axId val="38162008"/>
+        <c:axId val="38309920"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="22322214"/>
+        <c:axId val="38162008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11559,7 +12449,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89796400"/>
+        <c:crossAx val="38309920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11567,7 +12457,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89796400"/>
+        <c:axId val="38309920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11643,7 +12533,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22322214"/>
+        <c:crossAx val="38162008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11940,7 +12830,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -12089,7 +12979,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="29.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
         <v>31</v>
       </c>
@@ -12098,40 +12988,40 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
-      <c r="B22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="7"/>
+      <c r="B22" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="7" t="s">
+      <c r="A24" s="3"/>
+      <c r="B24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
         <v>40</v>
       </c>
@@ -12139,24 +13029,40 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3"/>
-      <c r="B28" s="7"/>
-    </row>
-    <row r="29" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
+    <row r="28" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="B28" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="s">
+        <v>44</v>
+      </c>
       <c r="B29" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>44</v>
+      <c r="A30" s="3"/>
+      <c r="B30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -12186,252 +13092,252 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B2" s="25" t="n">
         <v>10</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B3" s="15" t="n">
         <v>0.25</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B4" s="25" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>0.6</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="13" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B6" s="25" t="n">
         <v>10</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B7" s="25" t="n">
         <v>40</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B9" s="25" t="n">
         <v>100</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B11" s="25" t="n">
         <v>60</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B12" s="25" t="n">
         <v>5000</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>2</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B14" s="25" t="n">
         <v>500</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>2</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B16" s="15" t="n">
         <v>0.05</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B17" s="25" t="n">
         <v>100</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B18" s="15" t="n">
         <v>0.7</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>
@@ -12446,6 +13352,847 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>551</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>552</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>553</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>482</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>555</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>556</v>
+      </c>
+      <c r="D2" s="20"/>
+      <c r="E2" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>559</v>
+      </c>
+      <c r="D3" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F3" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G3" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I3" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>560</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>562</v>
+      </c>
+      <c r="D4" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F4" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G4" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I4" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J4" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="16" t="s">
+        <v>563</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>564</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>565</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>566</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A2</f>
+        <v>14</v>
+      </c>
+      <c r="C2" s="18" t="n">
+        <f aca="false">B2+상수!$B$29</f>
+        <v>17</v>
+      </c>
+      <c r="D2" s="14" t="n">
+        <v>320</v>
+      </c>
+      <c r="E2" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F2" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A3</f>
+        <v>16</v>
+      </c>
+      <c r="C3" s="18" t="n">
+        <f aca="false">B3+상수!$B$29</f>
+        <v>19</v>
+      </c>
+      <c r="D3" s="14" t="n">
+        <v>340</v>
+      </c>
+      <c r="E3" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A4</f>
+        <v>18</v>
+      </c>
+      <c r="C4" s="18" t="n">
+        <f aca="false">B4+상수!$B$29</f>
+        <v>21</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>360</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A5</f>
+        <v>20</v>
+      </c>
+      <c r="C5" s="18" t="n">
+        <f aca="false">B5+상수!$B$29</f>
+        <v>23</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>380</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A6</f>
+        <v>22</v>
+      </c>
+      <c r="C6" s="18" t="n">
+        <f aca="false">B6+상수!$B$29</f>
+        <v>25</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A7</f>
+        <v>24</v>
+      </c>
+      <c r="C7" s="18" t="n">
+        <f aca="false">B7+상수!$B$29</f>
+        <v>27</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>420</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A8</f>
+        <v>26</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <f aca="false">B8+상수!$B$29</f>
+        <v>29</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>440</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A9</f>
+        <v>28</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <f aca="false">B9+상수!$B$29</f>
+        <v>31</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>460</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A10</f>
+        <v>30</v>
+      </c>
+      <c r="C10" s="18" t="n">
+        <f aca="false">B10+상수!$B$29</f>
+        <v>33</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>480</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A11</f>
+        <v>32</v>
+      </c>
+      <c r="C11" s="18" t="n">
+        <f aca="false">B11+상수!$B$29</f>
+        <v>35</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A12</f>
+        <v>34</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <f aca="false">B12+상수!$B$29</f>
+        <v>37</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>520</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A13</f>
+        <v>36</v>
+      </c>
+      <c r="C13" s="18" t="n">
+        <f aca="false">B13+상수!$B$29</f>
+        <v>39</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>540</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A14</f>
+        <v>38</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <f aca="false">B14+상수!$B$29</f>
+        <v>41</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>560</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A15</f>
+        <v>40</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <f aca="false">B15+상수!$B$29</f>
+        <v>43</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>580</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A16</f>
+        <v>42</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <f aca="false">B16+상수!$B$29</f>
+        <v>45</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A17</f>
+        <v>44</v>
+      </c>
+      <c r="C17" s="18" t="n">
+        <f aca="false">B17+상수!$B$29</f>
+        <v>47</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>620</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A18</f>
+        <v>46</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <f aca="false">B18+상수!$B$29</f>
+        <v>49</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>640</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A19</f>
+        <v>48</v>
+      </c>
+      <c r="C19" s="18" t="n">
+        <f aca="false">B19+상수!$B$29</f>
+        <v>51</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>660</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A20</f>
+        <v>50</v>
+      </c>
+      <c r="C20" s="18" t="n">
+        <f aca="false">B20+상수!$B$29</f>
+        <v>53</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>680</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="26" t="n">
+        <f aca="false">상수!$B$40+상수!$B$41*A21</f>
+        <v>52</v>
+      </c>
+      <c r="C21" s="18" t="n">
+        <f aca="false">B21+상수!$B$29</f>
+        <v>55</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>700</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="23" t="s">
+        <v>571</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="24" t="s">
+        <v>572</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>573</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>576</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="s">
+        <v>577</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>578</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>579</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11" t="s">
+        <v>580</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>495</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>581</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>583</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>584</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>586</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>587</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>589</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>590</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -12467,44 +14214,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>545</v>
+        <v>591</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>546</v>
+        <v>592</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>547</v>
+        <v>593</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>548</v>
+        <v>594</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>549</v>
+        <v>595</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>550</v>
+        <v>596</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>551</v>
+        <v>597</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>552</v>
+        <v>598</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>553</v>
+        <v>599</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>554</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="26" t="n">
+      <c r="B2" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A2)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>4.8</v>
       </c>
@@ -12549,7 +14296,7 @@
       <c r="A3" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="26" t="n">
+      <c r="B3" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A3)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>6.6</v>
       </c>
@@ -12594,7 +14341,7 @@
       <c r="A4" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="26" t="n">
+      <c r="B4" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A4)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>8.4</v>
       </c>
@@ -12639,7 +14386,7 @@
       <c r="A5" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="26" t="n">
+      <c r="B5" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A5)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>10.2</v>
       </c>
@@ -12684,7 +14431,7 @@
       <c r="A6" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A6)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>12</v>
       </c>
@@ -12729,7 +14476,7 @@
       <c r="A7" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="26" t="n">
+      <c r="B7" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A7)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>13.8</v>
       </c>
@@ -12774,7 +14521,7 @@
       <c r="A8" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="n">
+      <c r="B8" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A8)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>15.6</v>
       </c>
@@ -12819,7 +14566,7 @@
       <c r="A9" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="26" t="n">
+      <c r="B9" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A9)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>17.4</v>
       </c>
@@ -12864,7 +14611,7 @@
       <c r="A10" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="26" t="n">
+      <c r="B10" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A10)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>19.2</v>
       </c>
@@ -12909,7 +14656,7 @@
       <c r="A11" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="26" t="n">
+      <c r="B11" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A11)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>21</v>
       </c>
@@ -12954,7 +14701,7 @@
       <c r="A12" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="26" t="n">
+      <c r="B12" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A12)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>22.8</v>
       </c>
@@ -12999,7 +14746,7 @@
       <c r="A13" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="26" t="n">
+      <c r="B13" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A13)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>24.6</v>
       </c>
@@ -13044,7 +14791,7 @@
       <c r="A14" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="26" t="n">
+      <c r="B14" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A14)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>26.4</v>
       </c>
@@ -13089,7 +14836,7 @@
       <c r="A15" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="26" t="n">
+      <c r="B15" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A15)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>28.2</v>
       </c>
@@ -13134,7 +14881,7 @@
       <c r="A16" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A16)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>30</v>
       </c>
@@ -13179,7 +14926,7 @@
       <c r="A17" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="26" t="n">
+      <c r="B17" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A17)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>31.8</v>
       </c>
@@ -13224,7 +14971,7 @@
       <c r="A18" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A18)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>33.6</v>
       </c>
@@ -13269,7 +15016,7 @@
       <c r="A19" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="26" t="n">
+      <c r="B19" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A19)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>35.4</v>
       </c>
@@ -13314,7 +15061,7 @@
       <c r="A20" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="26" t="n">
+      <c r="B20" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A20)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>37.2</v>
       </c>
@@ -13359,7 +15106,7 @@
       <c r="A21" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="26" t="n">
+      <c r="B21" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A21)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>39</v>
       </c>
@@ -13404,7 +15151,7 @@
       <c r="A22" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="26" t="n">
+      <c r="B22" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A22)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>40.8</v>
       </c>
@@ -13449,7 +15196,7 @@
       <c r="A23" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="26" t="n">
+      <c r="B23" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A23)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>42.6</v>
       </c>
@@ -13494,7 +15241,7 @@
       <c r="A24" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A24)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>44.4</v>
       </c>
@@ -13539,7 +15286,7 @@
       <c r="A25" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="26" t="n">
+      <c r="B25" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A25)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>46.2</v>
       </c>
@@ -13584,7 +15331,7 @@
       <c r="A26" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="26" t="n">
+      <c r="B26" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A26)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>48</v>
       </c>
@@ -13629,7 +15376,7 @@
       <c r="A27" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A27)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>49.8</v>
       </c>
@@ -13674,7 +15421,7 @@
       <c r="A28" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="26" t="n">
+      <c r="B28" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A28)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>51.6</v>
       </c>
@@ -13719,7 +15466,7 @@
       <c r="A29" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="26" t="n">
+      <c r="B29" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A29)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>53.4</v>
       </c>
@@ -13764,7 +15511,7 @@
       <c r="A30" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A30)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>55.2</v>
       </c>
@@ -13809,7 +15556,7 @@
       <c r="A31" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="26" t="n">
+      <c r="B31" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A31)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>57</v>
       </c>
@@ -13854,7 +15601,7 @@
       <c r="A32" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="26" t="n">
+      <c r="B32" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A32)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>58.8</v>
       </c>
@@ -13899,7 +15646,7 @@
       <c r="A33" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="26" t="n">
+      <c r="B33" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A33)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>60.6</v>
       </c>
@@ -13944,7 +15691,7 @@
       <c r="A34" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="26" t="n">
+      <c r="B34" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A34)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>62.4</v>
       </c>
@@ -13989,7 +15736,7 @@
       <c r="A35" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="26" t="n">
+      <c r="B35" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A35)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>64.2</v>
       </c>
@@ -14034,7 +15781,7 @@
       <c r="A36" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="26" t="n">
+      <c r="B36" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A36)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>66</v>
       </c>
@@ -14079,7 +15826,7 @@
       <c r="A37" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="26" t="n">
+      <c r="B37" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A37)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>67.8</v>
       </c>
@@ -14124,7 +15871,7 @@
       <c r="A38" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="26" t="n">
+      <c r="B38" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A38)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>69.6</v>
       </c>
@@ -14169,7 +15916,7 @@
       <c r="A39" s="11" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="26" t="n">
+      <c r="B39" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A39)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>71.4</v>
       </c>
@@ -14214,7 +15961,7 @@
       <c r="A40" s="11" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="26" t="n">
+      <c r="B40" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A40)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>73.2</v>
       </c>
@@ -14259,7 +16006,7 @@
       <c r="A41" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="26" t="n">
+      <c r="B41" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A41)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>75</v>
       </c>
@@ -14304,7 +16051,7 @@
       <c r="A42" s="11" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="26" t="n">
+      <c r="B42" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A42)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>76.8</v>
       </c>
@@ -14349,7 +16096,7 @@
       <c r="A43" s="11" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="26" t="n">
+      <c r="B43" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A43)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>78.6</v>
       </c>
@@ -14394,7 +16141,7 @@
       <c r="A44" s="11" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="26" t="n">
+      <c r="B44" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A44)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>80.4</v>
       </c>
@@ -14439,7 +16186,7 @@
       <c r="A45" s="11" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="26" t="n">
+      <c r="B45" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A45)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>82.2</v>
       </c>
@@ -14484,7 +16231,7 @@
       <c r="A46" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="26" t="n">
+      <c r="B46" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A46)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>84</v>
       </c>
@@ -14529,7 +16276,7 @@
       <c r="A47" s="11" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="26" t="n">
+      <c r="B47" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A47)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>85.8</v>
       </c>
@@ -14574,7 +16321,7 @@
       <c r="A48" s="11" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="26" t="n">
+      <c r="B48" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A48)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>87.6</v>
       </c>
@@ -14619,7 +16366,7 @@
       <c r="A49" s="11" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="26" t="n">
+      <c r="B49" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A49)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>89.4</v>
       </c>
@@ -14664,7 +16411,7 @@
       <c r="A50" s="11" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="26" t="n">
+      <c r="B50" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A50)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>91.2</v>
       </c>
@@ -14709,7 +16456,7 @@
       <c r="A51" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="26" t="n">
+      <c r="B51" s="27" t="n">
         <f aca="false">경제!$B$4*(1+경제!$B$5*A51)*INDEX(드랍!$H:$H,MATCH("Normal",드랍!$A:$A,0))</f>
         <v>93</v>
       </c>
@@ -14762,7 +16509,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -14778,7 +16525,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>555</v>
+        <v>601</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -14818,13 +16565,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>556</v>
+        <v>602</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>557</v>
+        <v>163</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>603</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -14843,13 +16590,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>558</v>
+        <v>604</v>
       </c>
       <c r="B4" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="C4" s="27" t="s">
-        <v>559</v>
+      <c r="C4" s="28" t="s">
+        <v>605</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -14868,13 +16615,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="B5" s="28" t="n">
+        <v>606</v>
+      </c>
+      <c r="B5" s="29" t="n">
         <v>1.115</v>
       </c>
-      <c r="C5" s="27" t="s">
-        <v>561</v>
+      <c r="C5" s="28" t="s">
+        <v>607</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -14893,13 +16640,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>562</v>
+        <v>608</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>1.2</v>
       </c>
-      <c r="C6" s="27" t="s">
-        <v>563</v>
+      <c r="C6" s="28" t="s">
+        <v>609</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -14918,13 +16665,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>564</v>
+        <v>610</v>
       </c>
       <c r="B7" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="27" t="s">
-        <v>565</v>
+      <c r="C7" s="28" t="s">
+        <v>611</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -14943,13 +16690,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="B8" s="29" t="n">
+        <v>612</v>
+      </c>
+      <c r="B8" s="30" t="n">
         <v>0.02</v>
       </c>
-      <c r="C8" s="27" t="s">
-        <v>567</v>
+      <c r="C8" s="28" t="s">
+        <v>613</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -14968,13 +16715,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="B9" s="29" t="n">
+        <v>614</v>
+      </c>
+      <c r="B9" s="30" t="n">
         <v>0.003</v>
       </c>
-      <c r="C9" s="27" t="s">
-        <v>569</v>
+      <c r="C9" s="28" t="s">
+        <v>615</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -14993,13 +16740,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>570</v>
+        <v>616</v>
       </c>
       <c r="B10" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="27" t="s">
-        <v>571</v>
+      <c r="C10" s="28" t="s">
+        <v>617</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -15018,13 +16765,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>572</v>
+        <v>618</v>
       </c>
       <c r="B11" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="C11" s="27" t="s">
-        <v>573</v>
+      <c r="C11" s="28" t="s">
+        <v>619</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -15043,12 +16790,12 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>574</v>
+        <v>620</v>
       </c>
       <c r="B12" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="C12" s="27"/>
+      <c r="C12" s="28"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -15066,13 +16813,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>575</v>
+        <v>621</v>
       </c>
       <c r="B13" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="C13" s="27" t="s">
-        <v>576</v>
+      <c r="C13" s="28" t="s">
+        <v>622</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -15091,13 +16838,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>577</v>
+        <v>623</v>
       </c>
       <c r="B14" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="C14" s="27" t="s">
-        <v>576</v>
+      <c r="C14" s="28" t="s">
+        <v>622</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -15116,9 +16863,9 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>578</v>
-      </c>
-      <c r="B15" s="30" t="n">
+        <v>624</v>
+      </c>
+      <c r="B15" s="26" t="n">
         <f aca="false">INDEX(귀신!$F:$F,MATCH($B$3,귀신!$A:$A,0))</f>
         <v>30</v>
       </c>
@@ -15140,9 +16887,9 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>579</v>
-      </c>
-      <c r="B16" s="30" t="n">
+        <v>625</v>
+      </c>
+      <c r="B16" s="26" t="n">
         <f aca="false">INDEX(귀신!$G:$G,MATCH($B$3,귀신!$A:$A,0))</f>
         <v>5</v>
       </c>
@@ -15164,7 +16911,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>580</v>
+        <v>626</v>
       </c>
       <c r="B17" s="31" t="n">
         <f aca="false">INDEX(귀신!$H:$H,MATCH($B$3,귀신!$A:$A,0))</f>
@@ -15188,9 +16935,9 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>581</v>
-      </c>
-      <c r="B18" s="30" t="n">
+        <v>627</v>
+      </c>
+      <c r="B18" s="26" t="n">
         <f aca="false">INDEX(귀신!$J:$J,MATCH($B$3,귀신!$A:$A,0))</f>
         <v>5</v>
       </c>
@@ -15231,55 +16978,55 @@
     </row>
     <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>582</v>
+        <v>628</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>583</v>
+        <v>629</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F20" s="32" t="s">
-        <v>584</v>
+        <v>630</v>
       </c>
       <c r="G20" s="32" t="s">
-        <v>585</v>
+        <v>631</v>
       </c>
       <c r="H20" s="32" t="s">
-        <v>586</v>
+        <v>632</v>
       </c>
       <c r="I20" s="32" t="s">
-        <v>587</v>
+        <v>633</v>
       </c>
       <c r="J20" s="32" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="K20" s="32" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L20" s="32" t="s">
-        <v>588</v>
+        <v>634</v>
       </c>
       <c r="M20" s="32" t="s">
-        <v>589</v>
+        <v>635</v>
       </c>
       <c r="N20" s="32" t="s">
-        <v>590</v>
+        <v>636</v>
       </c>
       <c r="O20" s="32" t="s">
-        <v>591</v>
+        <v>637</v>
       </c>
       <c r="P20" s="32" t="s">
-        <v>592</v>
+        <v>638</v>
       </c>
       <c r="Q20" s="33" t="s">
-        <v>593</v>
+        <v>639</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18760,550 +20507,550 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B2" s="12" t="n">
         <v>1.12</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>1.09</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B4" s="14" t="n">
         <v>15</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B5" s="14" t="n">
         <v>50</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="13" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B6" s="15" t="n">
         <v>0.85</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B7" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B8" s="15" t="n">
         <v>0.8</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B9" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B10" s="15" t="n">
         <v>0.05</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B11" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B12" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B13" s="15" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B14" s="15" t="n">
         <v>0.4</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B15" s="15" t="n">
         <v>0.4</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B16" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B17" s="15" t="n">
         <v>0.03</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B18" s="15" t="n">
         <v>0.45</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B19" s="14" t="n">
         <v>100</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="13" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B20" s="14" t="n">
         <v>10</v>
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="13" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B21" s="14" t="n">
         <v>100</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="13" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B22" s="14" t="n">
         <v>2</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="13" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B23" s="14" t="n">
         <v>5</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B24" s="14" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="13" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B25" s="14" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="13" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>3</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B28" s="14" t="n">
         <v>2</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B29" s="14" t="n">
         <v>3</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B30" s="14" t="n">
         <v>250</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="13" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B31" s="14" t="n">
         <v>100</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="13" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B32" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="13" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B33" s="14" t="n">
         <v>5</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B34" s="12" t="n">
         <v>0.2</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B35" s="14" t="n">
         <v>50</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B36" s="14" t="n">
         <v>6</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B37" s="14" t="n">
         <v>7</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B38" s="14" t="n">
         <v>30</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B39" s="15" t="n">
         <v>0.25</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B40" s="14" t="n">
         <v>12</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="13" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B41" s="14" t="n">
         <v>2</v>
       </c>
       <c r="C41" s="11"/>
       <c r="D41" s="13" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -19336,28 +21083,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21212,72 +22959,72 @@
   <sheetData>
     <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="N1" s="16" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="O1" s="16" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="P1" s="16" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D2" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F2" s="20" t="n">
         <v>30</v>
@@ -21289,7 +23036,7 @@
         <v>1.5</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J2" s="20" t="n">
         <v>5</v>
@@ -21313,24 +23060,24 @@
         <v>50</v>
       </c>
       <c r="Q2" s="13" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>164</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>160</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F3" s="20" t="n">
         <v>24</v>
@@ -21342,7 +23089,7 @@
         <v>1.2</v>
       </c>
       <c r="I3" s="20" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J3" s="20" t="n">
         <v>3</v>
@@ -21369,19 +23116,19 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F4" s="20" t="n">
         <v>36</v>
@@ -21393,7 +23140,7 @@
         <v>1.5</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J4" s="20" t="n">
         <v>5</v>
@@ -21417,24 +23164,24 @@
         <v>65</v>
       </c>
       <c r="Q4" s="13" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F5" s="20" t="n">
         <v>18</v>
@@ -21446,7 +23193,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J5" s="20" t="n">
         <v>2</v>
@@ -21470,24 +23217,24 @@
         <v>35</v>
       </c>
       <c r="Q5" s="13" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F6" s="20" t="n">
         <v>20</v>
@@ -21499,7 +23246,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J6" s="20" t="n">
         <v>0</v>
@@ -21523,24 +23270,24 @@
         <v>45</v>
       </c>
       <c r="Q6" s="13" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F7" s="20" t="n">
         <v>90</v>
@@ -21552,7 +23299,7 @@
         <v>2.5</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J7" s="20" t="n">
         <v>25</v>
@@ -21576,24 +23323,24 @@
         <v>120</v>
       </c>
       <c r="Q7" s="13" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F8" s="20" t="n">
         <v>120</v>
@@ -21605,7 +23352,7 @@
         <v>2.5</v>
       </c>
       <c r="I8" s="20" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J8" s="20" t="n">
         <v>40</v>
@@ -21632,19 +23379,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F9" s="20" t="n">
         <v>80</v>
@@ -21656,7 +23403,7 @@
         <v>1.5</v>
       </c>
       <c r="I9" s="20" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J9" s="20" t="n">
         <v>10</v>
@@ -21680,24 +23427,24 @@
         <v>200</v>
       </c>
       <c r="Q9" s="13" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F10" s="20" t="n">
         <v>1500</v>
@@ -21709,7 +23456,7 @@
         <v>1.8</v>
       </c>
       <c r="I10" s="20" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J10" s="20" t="n">
         <v>30</v>
@@ -21733,7 +23480,7 @@
         <v>2000</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -21767,78 +23514,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="N1" s="16" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="O1" s="16" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="P1" s="16" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="R1" s="16" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="S1" s="16" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="T1" s="16" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E2" s="14" t="n">
         <v>1</v>
@@ -21864,35 +23611,35 @@
       <c r="L2" s="22"/>
       <c r="M2" s="22"/>
       <c r="N2" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="O2" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="P2" s="22"/>
       <c r="Q2" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="R2" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="S2" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T2" s="22"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>1</v>
@@ -21916,35 +23663,35 @@
         <v>0.2</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="22"/>
       <c r="O3" s="22"/>
       <c r="P3" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q3" s="22"/>
       <c r="R3" s="22"/>
       <c r="S3" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T3" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E4" s="14" t="n">
         <v>1</v>
@@ -21968,7 +23715,7 @@
         <v>0.8</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
@@ -21981,16 +23728,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>227</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>223</v>
       </c>
       <c r="E5" s="14" t="n">
         <v>5</v>
@@ -22015,7 +23762,7 @@
       </c>
       <c r="L5" s="22"/>
       <c r="M5" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N5" s="22"/>
       <c r="O5" s="22"/>
@@ -22023,22 +23770,22 @@
       <c r="Q5" s="22"/>
       <c r="R5" s="22"/>
       <c r="S5" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T5" s="22"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E6" s="14" t="n">
         <v>5</v>
@@ -22063,7 +23810,7 @@
       </c>
       <c r="L6" s="22"/>
       <c r="M6" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N6" s="22"/>
       <c r="O6" s="22"/>
@@ -22071,22 +23818,22 @@
       <c r="Q6" s="22"/>
       <c r="R6" s="22"/>
       <c r="S6" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T6" s="22"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E7" s="14" t="n">
         <v>5</v>
@@ -22110,7 +23857,7 @@
         <v>35</v>
       </c>
       <c r="L7" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="M7" s="22"/>
       <c r="N7" s="22"/>
@@ -22123,16 +23870,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>5</v>
@@ -22156,13 +23903,13 @@
         <v>0.15</v>
       </c>
       <c r="L8" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="M8" s="22"/>
       <c r="N8" s="22"/>
       <c r="O8" s="22"/>
       <c r="P8" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q8" s="22"/>
       <c r="R8" s="22"/>
@@ -22171,16 +23918,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>5</v>
@@ -22208,29 +23955,29 @@
       <c r="N9" s="22"/>
       <c r="O9" s="22"/>
       <c r="P9" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q9" s="22"/>
       <c r="R9" s="22"/>
       <c r="S9" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T9" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>5</v>
@@ -22254,7 +24001,7 @@
         <v>0.35</v>
       </c>
       <c r="L10" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
@@ -22263,24 +24010,24 @@
       <c r="Q10" s="22"/>
       <c r="R10" s="22"/>
       <c r="S10" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T10" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>1</v>
@@ -22306,33 +24053,33 @@
       <c r="L11" s="22"/>
       <c r="M11" s="22"/>
       <c r="N11" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="O11" s="22"/>
       <c r="P11" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q11" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="R11" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="S11" s="22"/>
       <c r="T11" s="22"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>1</v>
@@ -22359,7 +24106,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
       <c r="O12" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="P12" s="22"/>
       <c r="Q12" s="22"/>
@@ -22369,16 +24116,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>1</v>
@@ -22404,37 +24151,37 @@
       <c r="L13" s="22"/>
       <c r="M13" s="22"/>
       <c r="N13" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="O13" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="P13" s="22"/>
       <c r="Q13" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="R13" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="S13" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T13" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>1</v>
@@ -22460,37 +24207,37 @@
       <c r="L14" s="22"/>
       <c r="M14" s="22"/>
       <c r="N14" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="O14" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="P14" s="22"/>
       <c r="Q14" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="R14" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="S14" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T14" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E15" s="14" t="n">
         <v>1</v>
@@ -22516,37 +24263,37 @@
       <c r="L15" s="22"/>
       <c r="M15" s="22"/>
       <c r="N15" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="O15" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="P15" s="22"/>
       <c r="Q15" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="R15" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="S15" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T15" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>1</v>
@@ -22572,37 +24319,37 @@
       <c r="L16" s="22"/>
       <c r="M16" s="22"/>
       <c r="N16" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="O16" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="P16" s="22"/>
       <c r="Q16" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="R16" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="S16" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T16" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>15</v>
@@ -22633,22 +24380,22 @@
       <c r="Q17" s="22"/>
       <c r="R17" s="22"/>
       <c r="S17" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T17" s="22"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E18" s="14" t="n">
         <v>10</v>
@@ -22675,7 +24422,7 @@
       <c r="M18" s="22"/>
       <c r="N18" s="22"/>
       <c r="O18" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="P18" s="22"/>
       <c r="Q18" s="22"/>
@@ -22685,16 +24432,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E19" s="14" t="n">
         <v>1</v>
@@ -22721,7 +24468,7 @@
       <c r="M19" s="22"/>
       <c r="N19" s="22"/>
       <c r="O19" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="P19" s="22"/>
       <c r="Q19" s="22"/>
@@ -22731,16 +24478,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E20" s="14" t="n">
         <v>1</v>
@@ -22764,7 +24511,7 @@
         <v>25</v>
       </c>
       <c r="L20" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
@@ -22777,16 +24524,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E21" s="14" t="n">
         <v>5</v>
@@ -22810,13 +24557,13 @@
         <v>5</v>
       </c>
       <c r="L21" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="M21" s="22"/>
       <c r="N21" s="22"/>
       <c r="O21" s="22"/>
       <c r="P21" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q21" s="22"/>
       <c r="R21" s="22"/>
@@ -22825,16 +24572,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E22" s="14" t="n">
         <v>5</v>
@@ -22859,7 +24606,7 @@
       </c>
       <c r="L22" s="22"/>
       <c r="M22" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N22" s="22"/>
       <c r="O22" s="22"/>
@@ -22867,22 +24614,22 @@
       <c r="Q22" s="22"/>
       <c r="R22" s="22"/>
       <c r="S22" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E23" s="14" t="n">
         <v>5</v>
@@ -22907,7 +24654,7 @@
       </c>
       <c r="L23" s="22"/>
       <c r="M23" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N23" s="22"/>
       <c r="O23" s="22"/>
@@ -22915,22 +24662,22 @@
       <c r="Q23" s="22"/>
       <c r="R23" s="22"/>
       <c r="S23" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E24" s="14" t="n">
         <v>10</v>
@@ -22955,7 +24702,7 @@
       </c>
       <c r="L24" s="22"/>
       <c r="M24" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N24" s="22"/>
       <c r="O24" s="22"/>
@@ -22967,16 +24714,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E25" s="14" t="n">
         <v>1</v>
@@ -23002,29 +24749,29 @@
       <c r="L25" s="22"/>
       <c r="M25" s="22"/>
       <c r="N25" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="O25" s="22"/>
       <c r="P25" s="22"/>
       <c r="Q25" s="22"/>
       <c r="R25" s="22"/>
       <c r="S25" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T25" s="22"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E26" s="14" t="n">
         <v>5</v>
@@ -23055,24 +24802,24 @@
       <c r="Q26" s="22"/>
       <c r="R26" s="22"/>
       <c r="S26" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T26" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E27" s="14" t="n">
         <v>10</v>
@@ -23097,7 +24844,7 @@
       </c>
       <c r="L27" s="22"/>
       <c r="M27" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N27" s="22"/>
       <c r="O27" s="22"/>
@@ -23109,16 +24856,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E28" s="14" t="n">
         <v>10</v>
@@ -23143,10 +24890,10 @@
       </c>
       <c r="L28" s="22"/>
       <c r="M28" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N28" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="O28" s="22"/>
       <c r="P28" s="22"/>
@@ -23157,16 +24904,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E29" s="14" t="n">
         <v>1</v>
@@ -23196,23 +24943,23 @@
       <c r="P29" s="22"/>
       <c r="Q29" s="22"/>
       <c r="R29" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="S29" s="22"/>
       <c r="T29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E30" s="14" t="n">
         <v>5</v>
@@ -23241,7 +24988,7 @@
       <c r="O30" s="22"/>
       <c r="P30" s="22"/>
       <c r="Q30" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="R30" s="22"/>
       <c r="S30" s="22"/>
@@ -23249,16 +24996,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E31" s="14" t="n">
         <v>5</v>
@@ -23290,21 +25037,21 @@
       <c r="R31" s="22"/>
       <c r="S31" s="22"/>
       <c r="T31" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E32" s="14" t="n">
         <v>1</v>
@@ -23336,21 +25083,21 @@
       <c r="R32" s="22"/>
       <c r="S32" s="22"/>
       <c r="T32" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E33" s="14" t="n">
         <v>20</v>
@@ -23381,22 +25128,22 @@
       <c r="Q33" s="22"/>
       <c r="R33" s="22"/>
       <c r="S33" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E34" s="14" t="n">
         <v>30</v>
@@ -23423,7 +25170,7 @@
       <c r="M34" s="22"/>
       <c r="N34" s="22"/>
       <c r="O34" s="22" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="P34" s="22"/>
       <c r="Q34" s="22"/>
@@ -23463,36 +25210,36 @@
   <sheetData>
     <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B2" s="11" t="n">
         <v>1</v>
@@ -23501,13 +25248,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="G2" s="14" t="n">
         <v>1</v>
@@ -23516,12 +25263,12 @@
         <v>6</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B3" s="11" t="n">
         <v>1</v>
@@ -23530,13 +25277,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E3" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>323</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>319</v>
       </c>
       <c r="G3" s="14" t="n">
         <v>2</v>
@@ -23548,7 +25295,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>1</v>
@@ -23557,13 +25304,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G4" s="14" t="n">
         <v>3</v>
@@ -23575,7 +25322,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>1</v>
@@ -23584,10 +25331,10 @@
         <v>4</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F5" s="11"/>
       <c r="G5" s="14" t="n">
@@ -23597,12 +25344,12 @@
         <v>6</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>1</v>
@@ -23611,13 +25358,13 @@
         <v>5</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>5</v>
@@ -23629,7 +25376,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>1</v>
@@ -23638,13 +25385,13 @@
         <v>6</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>6</v>
@@ -23653,12 +25400,12 @@
         <v>20</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>1</v>
@@ -23667,13 +25414,13 @@
         <v>7</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G8" s="14" t="n">
         <v>7</v>
@@ -23685,7 +25432,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>1</v>
@@ -23694,13 +25441,13 @@
         <v>8</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>8</v>
@@ -23709,12 +25456,12 @@
         <v>20</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>1</v>
@@ -23723,13 +25470,13 @@
         <v>9</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>9</v>
@@ -23738,12 +25485,12 @@
         <v>20</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B11" s="11" t="n">
         <v>1</v>
@@ -23752,13 +25499,13 @@
         <v>10</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>9</v>
@@ -23770,7 +25517,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B12" s="11" t="n">
         <v>1</v>
@@ -23779,13 +25526,13 @@
         <v>11</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>10</v>
@@ -23797,7 +25544,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B13" s="11" t="n">
         <v>1</v>
@@ -23806,13 +25553,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>11</v>
@@ -23821,12 +25568,12 @@
         <v>20</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B14" s="11" t="n">
         <v>1</v>
@@ -23835,13 +25582,13 @@
         <v>13</v>
       </c>
       <c r="D14" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="F14" s="13" t="s">
         <v>351</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>347</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>12</v>
@@ -23850,12 +25597,12 @@
         <v>20</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B15" s="11" t="n">
         <v>1</v>
@@ -23864,13 +25611,13 @@
         <v>14</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>12</v>
@@ -23882,7 +25629,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>1</v>
@@ -23891,13 +25638,13 @@
         <v>15</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>13</v>
@@ -23906,12 +25653,12 @@
         <v>6</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B17" s="11" t="n">
         <v>2</v>
@@ -23920,13 +25667,13 @@
         <v>1</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>14</v>
@@ -23938,7 +25685,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B18" s="11" t="n">
         <v>2</v>
@@ -23947,10 +25694,10 @@
         <v>2</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="14" t="n">
@@ -23960,12 +25707,12 @@
         <v>0</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B19" s="11" t="n">
         <v>2</v>
@@ -23974,13 +25721,13 @@
         <v>3</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>15</v>
@@ -23992,7 +25739,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B20" s="11" t="n">
         <v>2</v>
@@ -24001,13 +25748,13 @@
         <v>4</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="G20" s="14" t="n">
         <v>16</v>
@@ -24016,12 +25763,12 @@
         <v>20</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B21" s="11" t="n">
         <v>2</v>
@@ -24030,13 +25777,13 @@
         <v>5</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>17</v>
@@ -24048,7 +25795,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B22" s="11" t="n">
         <v>2</v>
@@ -24057,13 +25804,13 @@
         <v>6</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>18</v>
@@ -24075,7 +25822,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B23" s="11" t="n">
         <v>2</v>
@@ -24084,13 +25831,13 @@
         <v>7</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>19</v>
@@ -24099,12 +25846,12 @@
         <v>20</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B24" s="11" t="n">
         <v>2</v>
@@ -24113,13 +25860,13 @@
         <v>8</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>20</v>
@@ -24128,12 +25875,12 @@
         <v>20</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B25" s="11" t="n">
         <v>2</v>
@@ -24142,13 +25889,13 @@
         <v>9</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>19</v>
@@ -24157,12 +25904,12 @@
         <v>20</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B26" s="11" t="n">
         <v>2</v>
@@ -24171,13 +25918,13 @@
         <v>10</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="G26" s="14" t="n">
         <v>20</v>
@@ -24189,7 +25936,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B27" s="11" t="n">
         <v>2</v>
@@ -24198,13 +25945,13 @@
         <v>11</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>21</v>
@@ -24213,12 +25960,12 @@
         <v>20</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B28" s="11" t="n">
         <v>2</v>
@@ -24227,13 +25974,13 @@
         <v>12</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>22</v>
@@ -24242,12 +25989,12 @@
         <v>20</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B29" s="11" t="n">
         <v>2</v>
@@ -24256,13 +26003,13 @@
         <v>13</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>22</v>
@@ -24274,7 +26021,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B30" s="11" t="n">
         <v>2</v>
@@ -24283,13 +26030,13 @@
         <v>14</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>23</v>
@@ -24301,7 +26048,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B31" s="11" t="n">
         <v>2</v>
@@ -24310,13 +26057,13 @@
         <v>15</v>
       </c>
       <c r="D31" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="F31" s="13" t="s">
         <v>391</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>387</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>24</v>
@@ -24328,7 +26075,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B32" s="11" t="n">
         <v>2</v>
@@ -24337,13 +26084,13 @@
         <v>16</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>24</v>
@@ -24352,12 +26099,12 @@
         <v>6</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B33" s="11" t="n">
         <v>3</v>
@@ -24366,13 +26113,13 @@
         <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>25</v>
@@ -24384,7 +26131,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B34" s="11" t="n">
         <v>3</v>
@@ -24393,10 +26140,10 @@
         <v>2</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F34" s="11"/>
       <c r="G34" s="14" t="n">
@@ -24406,12 +26153,12 @@
         <v>0</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B35" s="11" t="n">
         <v>3</v>
@@ -24420,13 +26167,13 @@
         <v>3</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E35" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="F35" s="13" t="s">
         <v>323</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>319</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>26</v>
@@ -24438,7 +26185,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B36" s="11" t="n">
         <v>3</v>
@@ -24447,13 +26194,13 @@
         <v>4</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="G36" s="14" t="n">
         <v>27</v>
@@ -24462,12 +26209,12 @@
         <v>20</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B37" s="11" t="n">
         <v>3</v>
@@ -24476,13 +26223,13 @@
         <v>5</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>28</v>
@@ -24491,12 +26238,12 @@
         <v>20</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B38" s="11" t="n">
         <v>3</v>
@@ -24505,13 +26252,13 @@
         <v>6</v>
       </c>
       <c r="D38" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="F38" s="13" t="s">
         <v>407</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>403</v>
       </c>
       <c r="G38" s="14" t="n">
         <v>29</v>
@@ -24520,12 +26267,12 @@
         <v>20</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B39" s="11" t="n">
         <v>3</v>
@@ -24534,13 +26281,13 @@
         <v>7</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>28</v>
@@ -24552,7 +26299,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="B40" s="11" t="n">
         <v>3</v>
@@ -24561,13 +26308,13 @@
         <v>8</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>29</v>
@@ -24579,7 +26326,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B41" s="11" t="n">
         <v>3</v>
@@ -24588,13 +26335,13 @@
         <v>9</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>30</v>
@@ -24603,12 +26350,12 @@
         <v>20</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B42" s="11" t="n">
         <v>3</v>
@@ -24617,13 +26364,13 @@
         <v>10</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="G42" s="14" t="n">
         <v>30</v>
@@ -24632,12 +26379,12 @@
         <v>6</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B43" s="11" t="n">
         <v>3</v>
@@ -24646,13 +26393,13 @@
         <v>11</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>31</v>
@@ -24664,7 +26411,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B44" s="11" t="n">
         <v>3</v>
@@ -24673,13 +26420,13 @@
         <v>12</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="G44" s="14" t="n">
         <v>32</v>
@@ -24688,12 +26435,12 @@
         <v>20</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B45" s="11" t="n">
         <v>3</v>
@@ -24702,13 +26449,13 @@
         <v>13</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="G45" s="14" t="n">
         <v>33</v>
@@ -24720,7 +26467,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B46" s="11" t="n">
         <v>3</v>
@@ -24729,13 +26476,13 @@
         <v>14</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="G46" s="14" t="n">
         <v>34</v>
@@ -24744,12 +26491,12 @@
         <v>20</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B47" s="11" t="n">
         <v>3</v>
@@ -24758,13 +26505,13 @@
         <v>15</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>35</v>
@@ -24773,12 +26520,12 @@
         <v>20</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B48" s="11" t="n">
         <v>3</v>
@@ -24787,13 +26534,13 @@
         <v>16</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="G48" s="14" t="n">
         <v>35</v>
@@ -24805,7 +26552,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B49" s="11" t="n">
         <v>3</v>
@@ -24814,13 +26561,13 @@
         <v>17</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>36</v>
@@ -24829,7 +26576,7 @@
         <v>6</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24845,7 +26592,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="23" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -24858,13 +26605,13 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="24" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -25289,60 +27036,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D2" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F2" s="20" t="n">
         <v>80</v>
@@ -25357,7 +27104,7 @@
         <v>0.8</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K2" s="20" t="n">
         <v>12</v>
@@ -25366,24 +27113,24 @@
         <v>30</v>
       </c>
       <c r="M2" s="13" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F3" s="20" t="n">
         <v>80</v>
@@ -25398,7 +27145,7 @@
         <v>2</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K3" s="20" t="n">
         <v>14</v>
@@ -25407,24 +27154,24 @@
         <v>30</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>2</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="F4" s="20" t="n">
         <v>140</v>
@@ -25439,7 +27186,7 @@
         <v>1.2</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K4" s="20" t="n">
         <v>2</v>
@@ -25448,24 +27195,24 @@
         <v>40</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>455</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>451</v>
-      </c>
       <c r="C5" s="13" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>2</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F5" s="20" t="n">
         <v>110</v>
@@ -25480,7 +27227,7 @@
         <v>0.6</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K5" s="20" t="n">
         <v>2</v>
@@ -25489,24 +27236,24 @@
         <v>40</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>3</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F6" s="20" t="n">
         <v>90</v>
@@ -25521,7 +27268,7 @@
         <v>1.5</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K6" s="20" t="n">
         <v>8</v>
@@ -25530,24 +27277,24 @@
         <v>50</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>464</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>460</v>
-      </c>
       <c r="C7" s="13" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>3</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F7" s="20" t="n">
         <v>90</v>
@@ -25562,7 +27309,7 @@
         <v>1.5</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="K7" s="20" t="n">
         <v>8</v>
@@ -25571,7 +27318,7 @@
         <v>50</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -25608,48 +27355,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C2" s="15" t="n">
         <v>0.12</v>
@@ -25680,10 +27427,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C3" s="15" t="n">
         <v>1</v>
@@ -25711,15 +27458,15 @@
       </c>
       <c r="K3" s="20"/>
       <c r="L3" s="11" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C4" s="15" t="n">
         <v>1</v>
@@ -25746,16 +27493,16 @@
         <v>2</v>
       </c>
       <c r="K4" s="20" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="L4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>1</v>
@@ -25782,18 +27529,18 @@
         <v>4</v>
       </c>
       <c r="K5" s="20" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C6" s="15" t="n">
         <v>1</v>
@@ -25820,16 +27567,16 @@
         <v>3</v>
       </c>
       <c r="K6" s="20" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="L6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C7" s="15" t="n">
         <v>0.03</v>
@@ -25886,27 +27633,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C2" s="21" t="n">
         <v>60</v>
@@ -25915,15 +27662,15 @@
         <v>1</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C3" s="21" t="n">
         <v>30</v>
@@ -25932,15 +27679,15 @@
         <v>2</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C4" s="21" t="n">
         <v>8.5</v>
@@ -25949,15 +27696,15 @@
         <v>4</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C5" s="21" t="n">
         <v>1.2</v>
@@ -25966,15 +27713,15 @@
         <v>8</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C6" s="21" t="n">
         <v>0.3</v>
@@ -25983,7 +27730,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>
